--- a/research/traditional_assets/database/data/nigeria/nigeria_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_real_estate_general_diversified.xlsx
@@ -588,46 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.192</v>
-      </c>
-      <c r="E2">
-        <v>1.277</v>
+        <v>-0.302</v>
       </c>
       <c r="G2">
-        <v>-0.5852417302798981</v>
+        <v>-1.49</v>
       </c>
       <c r="H2">
-        <v>-0.5852417302798981</v>
+        <v>-1.49</v>
       </c>
       <c r="I2">
-        <v>-0.7226463104325699</v>
+        <v>-1.51</v>
       </c>
       <c r="J2">
-        <v>-0.3613231552162849</v>
+        <v>-1.51</v>
       </c>
       <c r="K2">
-        <v>4.23</v>
+        <v>-4.67</v>
       </c>
       <c r="L2">
-        <v>1.076335877862596</v>
+        <v>-2.335</v>
       </c>
       <c r="M2">
-        <v>0.038</v>
+        <v>0.003</v>
       </c>
       <c r="N2">
-        <v>0.0007102803738317756</v>
+        <v>7.957559681697613e-05</v>
       </c>
       <c r="O2">
-        <v>0.008983451536643025</v>
+        <v>-0.0006423982869379015</v>
       </c>
       <c r="P2">
-        <v>0.038</v>
+        <v>0.003</v>
       </c>
       <c r="Q2">
-        <v>0.0007102803738317756</v>
+        <v>7.957559681697613e-05</v>
       </c>
       <c r="R2">
-        <v>0.008983451536643025</v>
+        <v>-0.0006423982869379015</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +633,52 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.36</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.1375700934579439</v>
-      </c>
-      <c r="W2">
-        <v>-5.58047493403694</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.08399642144278631</v>
-      </c>
-      <c r="Y2">
-        <v>-5.664471355479726</v>
-      </c>
-      <c r="Z2">
-        <v>0.07701050321366987</v>
-      </c>
-      <c r="AA2">
-        <v>-0.02782567800595705</v>
+        <v>0.1303832867949439</v>
       </c>
       <c r="AB2">
-        <v>0.07732212506506603</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1051478030710231</v>
+        <v>0.1303832867949439</v>
       </c>
       <c r="AD2">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.2109144542772862</v>
-      </c>
-      <c r="AI2">
-        <v>0.3695090439276486</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.1148246194573131</v>
-      </c>
-      <c r="AK2">
-        <v>0.221442246330568</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AM2">
-        <v>2.433</v>
+        <v>1.617</v>
       </c>
       <c r="AN2">
-        <v>-5.088967971530249</v>
+        <v>-0</v>
       </c>
       <c r="AO2">
-        <v>-1.113725490196078</v>
+        <v>-1.632432432432432</v>
       </c>
       <c r="AP2">
-        <v>-2.469750889679716</v>
+        <v>-0</v>
       </c>
       <c r="AQ2">
-        <v>-1.167283189478011</v>
+        <v>-1.867656153370439</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +698,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.192</v>
-      </c>
-      <c r="E3">
-        <v>1.277</v>
+        <v>-0.302</v>
       </c>
       <c r="G3">
-        <v>-0.5852417302798981</v>
+        <v>-1.49</v>
       </c>
       <c r="H3">
-        <v>-0.5852417302798981</v>
+        <v>-1.49</v>
       </c>
       <c r="I3">
-        <v>-0.7226463104325699</v>
+        <v>-1.51</v>
       </c>
       <c r="J3">
-        <v>-0.3613231552162849</v>
+        <v>-1.51</v>
       </c>
       <c r="K3">
-        <v>4.23</v>
+        <v>-4.67</v>
       </c>
       <c r="L3">
-        <v>1.076335877862596</v>
+        <v>-2.335</v>
       </c>
       <c r="M3">
-        <v>0.038</v>
+        <v>0.003</v>
       </c>
       <c r="N3">
-        <v>0.0007102803738317756</v>
+        <v>7.957559681697613e-05</v>
       </c>
       <c r="O3">
-        <v>0.008983451536643025</v>
+        <v>-0.0006423982869379015</v>
       </c>
       <c r="P3">
-        <v>0.038</v>
+        <v>0.003</v>
       </c>
       <c r="Q3">
-        <v>0.0007102803738317756</v>
+        <v>7.957559681697613e-05</v>
       </c>
       <c r="R3">
-        <v>0.008983451536643025</v>
+        <v>-0.0006423982869379015</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +743,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.36</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.1375700934579439</v>
-      </c>
-      <c r="W3">
-        <v>-5.58047493403694</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.08399642144278631</v>
-      </c>
-      <c r="Y3">
-        <v>-5.664471355479726</v>
-      </c>
-      <c r="Z3">
-        <v>0.07701050321366987</v>
-      </c>
-      <c r="AA3">
-        <v>-0.02782567800595705</v>
+        <v>0.1303832867949439</v>
       </c>
       <c r="AB3">
-        <v>0.07732212506506603</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1051478030710231</v>
+        <v>0.1303832867949439</v>
       </c>
       <c r="AD3">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.2109144542772862</v>
-      </c>
-      <c r="AI3">
-        <v>0.3695090439276486</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.1148246194573131</v>
-      </c>
-      <c r="AK3">
-        <v>0.221442246330568</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AM3">
-        <v>2.433</v>
+        <v>1.617</v>
       </c>
       <c r="AN3">
-        <v>-5.088967971530249</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-1.113725490196078</v>
+        <v>-1.632432432432432</v>
       </c>
       <c r="AP3">
-        <v>-2.469750889679716</v>
+        <v>-0</v>
       </c>
       <c r="AQ3">
-        <v>-1.167283189478011</v>
+        <v>-1.867656153370439</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/nigeria/nigeria_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_real_estate_general_diversified.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ngse_updc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,97 +590,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.302</v>
+        <v>0.217</v>
       </c>
       <c r="G2">
-        <v>-1.49</v>
+        <v>0.1584362139917695</v>
       </c>
       <c r="H2">
-        <v>-1.49</v>
+        <v>0.1584362139917695</v>
       </c>
       <c r="I2">
-        <v>-1.51</v>
+        <v>0.1015432098765432</v>
       </c>
       <c r="J2">
-        <v>-1.51</v>
+        <v>0.06797065810164274</v>
       </c>
       <c r="K2">
-        <v>-4.67</v>
+        <v>0.443</v>
       </c>
       <c r="L2">
-        <v>-2.335</v>
+        <v>0.0455761316872428</v>
       </c>
       <c r="M2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>7.957559681697613e-05</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.0006423982869379015</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>7.957559681697613e-05</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.0006423982869379015</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.2191011235955056</v>
+      </c>
+      <c r="W2">
+        <v>0.02331578947368421</v>
       </c>
       <c r="X2">
-        <v>0.1303832867949439</v>
+        <v>0.134280061199721</v>
+      </c>
+      <c r="Y2">
+        <v>-0.1109642717260368</v>
+      </c>
+      <c r="Z2">
+        <v>0.3919354838709678</v>
+      </c>
+      <c r="AA2">
+        <v>0.02664011277209546</v>
       </c>
       <c r="AB2">
-        <v>0.1303832867949439</v>
+        <v>0.1267632724692125</v>
+      </c>
+      <c r="AC2">
+        <v>-0.100123159697117</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>0.4000000000000004</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.1896813353566009</v>
+      </c>
+      <c r="AI2">
+        <v>0.373134328358209</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>0.01476014760147603</v>
+      </c>
+      <c r="AK2">
+        <v>0.03669724770642205</v>
       </c>
       <c r="AL2">
-        <v>1.85</v>
+        <v>0.495</v>
       </c>
       <c r="AM2">
-        <v>1.617</v>
+        <v>0.255</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
+        <v>5.580357142857142</v>
       </c>
       <c r="AO2">
-        <v>-1.632432432432432</v>
+        <v>1.993939393939394</v>
       </c>
       <c r="AP2">
-        <v>-0</v>
+        <v>0.3571428571428574</v>
       </c>
       <c r="AQ2">
-        <v>-1.867656153370439</v>
+        <v>3.870588235294118</v>
       </c>
     </row>
     <row r="3">
@@ -689,7 +709,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UACN Property Development Company Plc (NGSE:UPDC)</t>
+          <t>UPDC Plc (NGSE:UPDC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -698,97 +718,8887 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.302</v>
+        <v>0.217</v>
       </c>
       <c r="G3">
-        <v>-1.49</v>
+        <v>0.1584362139917695</v>
       </c>
       <c r="H3">
-        <v>-1.49</v>
+        <v>0.1584362139917695</v>
       </c>
       <c r="I3">
-        <v>-1.51</v>
+        <v>0.1015432098765432</v>
       </c>
       <c r="J3">
-        <v>-1.51</v>
+        <v>0.06797065810164274</v>
       </c>
       <c r="K3">
-        <v>-4.67</v>
+        <v>0.443</v>
       </c>
       <c r="L3">
-        <v>-2.335</v>
+        <v>0.0455761316872428</v>
       </c>
       <c r="M3">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>7.957559681697613e-05</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.0006423982869379015</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>7.957559681697613e-05</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.0006423982869379015</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>5.85</v>
+      </c>
+      <c r="V3">
+        <v>0.2191011235955056</v>
+      </c>
+      <c r="W3">
+        <v>0.02331578947368421</v>
+      </c>
+      <c r="X3">
+        <v>0.134280061199721</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1109642717260368</v>
+      </c>
+      <c r="Z3">
+        <v>0.3919354838709678</v>
+      </c>
+      <c r="AA3">
+        <v>0.02664011277209546</v>
+      </c>
+      <c r="AB3">
+        <v>0.1267632724692125</v>
+      </c>
+      <c r="AC3">
+        <v>-0.100123159697117</v>
+      </c>
+      <c r="AD3">
+        <v>6.25</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>6.25</v>
+      </c>
+      <c r="AG3">
+        <v>0.4000000000000004</v>
+      </c>
+      <c r="AH3">
+        <v>0.1896813353566009</v>
+      </c>
+      <c r="AI3">
+        <v>0.373134328358209</v>
+      </c>
+      <c r="AJ3">
+        <v>0.01476014760147603</v>
+      </c>
+      <c r="AK3">
+        <v>0.03669724770642205</v>
+      </c>
+      <c r="AL3">
+        <v>0.495</v>
+      </c>
+      <c r="AM3">
+        <v>0.255</v>
+      </c>
+      <c r="AN3">
+        <v>5.580357142857142</v>
+      </c>
+      <c r="AO3">
+        <v>1.993939393939394</v>
+      </c>
+      <c r="AP3">
+        <v>0.3571428571428574</v>
+      </c>
+      <c r="AQ3">
+        <v>3.870588235294118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UPDC Plc (NGSE:UPDC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NGSE:UPDC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (General/Diversified)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.99393939393939</v>
+      </c>
+      <c r="F2">
+        <v>4.50608763495766</v>
+      </c>
+      <c r="G2">
+        <v>5.58035714285714</v>
+      </c>
+      <c r="H2">
+        <v>5.29553571428571</v>
+      </c>
+      <c r="I2">
+        <v>0.189681335356601</v>
+      </c>
+      <c r="J2">
+        <v>0.18</v>
+      </c>
+      <c r="K2">
+        <v>26.7</v>
+      </c>
+      <c r="L2">
+        <v>30.8626551914706</v>
+      </c>
+      <c r="M2">
+        <v>27.1</v>
+      </c>
+      <c r="N2">
+        <v>30.9436551914706</v>
+      </c>
+      <c r="O2">
+        <v>6.25</v>
+      </c>
+      <c r="P2">
+        <v>5.931</v>
+      </c>
+      <c r="Q2">
+        <v>0.126763272469213</v>
+      </c>
+      <c r="R2">
+        <v>0.115836945673203</v>
+      </c>
+      <c r="S2">
+        <v>0.09465155101248041</v>
+      </c>
+      <c r="T2">
+        <v>0.03563</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.134280061199721</v>
+      </c>
+      <c r="X2">
+        <v>0.133443348381955</v>
+      </c>
+      <c r="Y2">
+        <v>0.613359987351453</v>
+      </c>
+      <c r="Z2">
+        <v>0.607984978612738</v>
+      </c>
+      <c r="AA2">
+        <v>6.25</v>
+      </c>
+      <c r="AB2">
+        <v>0.1352165014464005</v>
+      </c>
+      <c r="AC2">
+        <v>1.993939393939394</v>
+      </c>
+      <c r="AD2">
+        <v>6.25</v>
+      </c>
+      <c r="AE2">
+        <v>0.495</v>
+      </c>
+      <c r="AF2">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>1.12</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>26.7</v>
+      </c>
+      <c r="AK2">
+        <v>0.1556672478946873</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.3</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>0.4719999999999995</v>
+      </c>
+      <c r="AR2">
+        <v>0.495</v>
+      </c>
+      <c r="AS2">
+        <v>6.25</v>
+      </c>
+      <c r="AT2">
+        <v>5.85</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1208375747074031</v>
+      </c>
+      <c r="C2">
+        <v>34.90747387605968</v>
+      </c>
+      <c r="D2">
+        <v>29.05747387605967</v>
+      </c>
+      <c r="E2">
+        <v>-6.25</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>5.85</v>
+      </c>
+      <c r="H2">
+        <v>26.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K2">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L2">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="O2">
+        <v>0.4081</v>
+      </c>
+      <c r="P2">
+        <v>0.9522333333333333</v>
+      </c>
+      <c r="Q2">
+        <v>1.085233333333333</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1208375747074031</v>
+      </c>
+      <c r="T2">
+        <v>0.5270060068313374</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03129</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1205163619832809</v>
+      </c>
+      <c r="C3">
+        <v>34.69219372277469</v>
+      </c>
+      <c r="D3">
+        <v>29.17169372277469</v>
+      </c>
+      <c r="E3">
+        <v>-5.9205</v>
+      </c>
+      <c r="F3">
+        <v>0.3295</v>
+      </c>
+      <c r="G3">
+        <v>5.85</v>
+      </c>
+      <c r="H3">
+        <v>26.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K3">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L3">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M3">
+        <v>0.01472865</v>
+      </c>
+      <c r="N3">
+        <v>1.345604683333333</v>
+      </c>
+      <c r="O3">
+        <v>0.403681405</v>
+      </c>
+      <c r="P3">
+        <v>0.9419232783333333</v>
+      </c>
+      <c r="Q3">
+        <v>1.074923278333333</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1214176383669504</v>
+      </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.5307323119301448</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.0447</v>
       </c>
       <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0.1303832867949439</v>
-      </c>
-      <c r="AB3">
-        <v>0.1303832867949439</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>1.85</v>
-      </c>
-      <c r="AM3">
-        <v>1.617</v>
-      </c>
-      <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AO3">
-        <v>-1.632432432432432</v>
-      </c>
-      <c r="AP3">
-        <v>-0</v>
-      </c>
-      <c r="AQ3">
-        <v>-1.867656153370439</v>
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03129</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>92.35967541718577</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1201951492591587</v>
+      </c>
+      <c r="C4">
+        <v>34.47781506960234</v>
+      </c>
+      <c r="D4">
+        <v>29.28681506960234</v>
+      </c>
+      <c r="E4">
+        <v>-5.591</v>
+      </c>
+      <c r="F4">
+        <v>0.659</v>
+      </c>
+      <c r="G4">
+        <v>5.85</v>
+      </c>
+      <c r="H4">
+        <v>26.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K4">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L4">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M4">
+        <v>0.0294573</v>
+      </c>
+      <c r="N4">
+        <v>1.330876033333333</v>
+      </c>
+      <c r="O4">
+        <v>0.3992628099999999</v>
+      </c>
+      <c r="P4">
+        <v>0.9316132233333332</v>
+      </c>
+      <c r="Q4">
+        <v>1.064613223333333</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.122009540060366</v>
+      </c>
+      <c r="T4">
+        <v>0.534534664071785</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03129</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>46.17983770859288</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1198739365350364</v>
+      </c>
+      <c r="C5">
+        <v>34.26434863169914</v>
+      </c>
+      <c r="D5">
+        <v>29.40284863169914</v>
+      </c>
+      <c r="E5">
+        <v>-5.2615</v>
+      </c>
+      <c r="F5">
+        <v>0.9885</v>
+      </c>
+      <c r="G5">
+        <v>5.85</v>
+      </c>
+      <c r="H5">
+        <v>26.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K5">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L5">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M5">
+        <v>0.04418595000000001</v>
+      </c>
+      <c r="N5">
+        <v>1.316147383333333</v>
+      </c>
+      <c r="O5">
+        <v>0.3948442149999999</v>
+      </c>
+      <c r="P5">
+        <v>0.9213031683333333</v>
+      </c>
+      <c r="Q5">
+        <v>1.054303168333333</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1226136459124087</v>
+      </c>
+      <c r="T5">
+        <v>0.5384154152266549</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03129</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>30.78655847239525</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1195527238109143</v>
+      </c>
+      <c r="C6">
+        <v>34.05180529470974</v>
+      </c>
+      <c r="D6">
+        <v>29.51980529470973</v>
+      </c>
+      <c r="E6">
+        <v>-4.932</v>
+      </c>
+      <c r="F6">
+        <v>1.318</v>
+      </c>
+      <c r="G6">
+        <v>5.85</v>
+      </c>
+      <c r="H6">
+        <v>26.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K6">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L6">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M6">
+        <v>0.0589146</v>
+      </c>
+      <c r="N6">
+        <v>1.301418733333333</v>
+      </c>
+      <c r="O6">
+        <v>0.3904256199999999</v>
+      </c>
+      <c r="P6">
+        <v>0.9109931133333332</v>
+      </c>
+      <c r="Q6">
+        <v>1.043993113333333</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1232303373030357</v>
+      </c>
+      <c r="T6">
+        <v>0.542377015363918</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03129</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>23.08991885429644</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.119231511086792</v>
+      </c>
+      <c r="C7">
+        <v>33.8401961181712</v>
+      </c>
+      <c r="D7">
+        <v>29.6376961181712</v>
+      </c>
+      <c r="E7">
+        <v>-4.6025</v>
+      </c>
+      <c r="F7">
+        <v>1.6475</v>
+      </c>
+      <c r="G7">
+        <v>5.85</v>
+      </c>
+      <c r="H7">
+        <v>26.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K7">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L7">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M7">
+        <v>0.07364325000000002</v>
+      </c>
+      <c r="N7">
+        <v>1.286690083333333</v>
+      </c>
+      <c r="O7">
+        <v>0.3860070249999999</v>
+      </c>
+      <c r="P7">
+        <v>0.9006830583333333</v>
+      </c>
+      <c r="Q7">
+        <v>1.033683058333333</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1238600116703074</v>
+      </c>
+      <c r="T7">
+        <v>0.546422017609334</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03129</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>18.47193508343715</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1189102983626698</v>
+      </c>
+      <c r="C8">
+        <v>33.6295323389992</v>
+      </c>
+      <c r="D8">
+        <v>29.7565323389992</v>
+      </c>
+      <c r="E8">
+        <v>-4.273</v>
+      </c>
+      <c r="F8">
+        <v>1.977</v>
+      </c>
+      <c r="G8">
+        <v>5.85</v>
+      </c>
+      <c r="H8">
+        <v>26.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K8">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L8">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M8">
+        <v>0.08837190000000002</v>
+      </c>
+      <c r="N8">
+        <v>1.271961433333333</v>
+      </c>
+      <c r="O8">
+        <v>0.3815884299999999</v>
+      </c>
+      <c r="P8">
+        <v>0.8903730033333332</v>
+      </c>
+      <c r="Q8">
+        <v>1.023373003333333</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1245030833645424</v>
+      </c>
+      <c r="T8">
+        <v>0.5505530837323119</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03129</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>15.39327923619762</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1185890856385476</v>
+      </c>
+      <c r="C9">
+        <v>33.41982537505854</v>
+      </c>
+      <c r="D9">
+        <v>29.87632537505853</v>
+      </c>
+      <c r="E9">
+        <v>-3.9435</v>
+      </c>
+      <c r="F9">
+        <v>2.3065</v>
+      </c>
+      <c r="G9">
+        <v>5.85</v>
+      </c>
+      <c r="H9">
+        <v>26.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K9">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L9">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M9">
+        <v>0.10310055</v>
+      </c>
+      <c r="N9">
+        <v>1.257232783333333</v>
+      </c>
+      <c r="O9">
+        <v>0.377169835</v>
+      </c>
+      <c r="P9">
+        <v>0.8800629483333333</v>
+      </c>
+      <c r="Q9">
+        <v>1.013062948333333</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1251599845575781</v>
+      </c>
+      <c r="T9">
+        <v>0.554772989986967</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03129</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>13.19423934531225</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1183294729144254</v>
+      </c>
+      <c r="C10">
+        <v>33.1878524167092</v>
+      </c>
+      <c r="D10">
+        <v>29.9738524167092</v>
+      </c>
+      <c r="E10">
+        <v>-3.614</v>
+      </c>
+      <c r="F10">
+        <v>2.636</v>
+      </c>
+      <c r="G10">
+        <v>5.85</v>
+      </c>
+      <c r="H10">
+        <v>26.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K10">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L10">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M10">
+        <v>0.1207288</v>
+      </c>
+      <c r="N10">
+        <v>1.239604533333333</v>
+      </c>
+      <c r="O10">
+        <v>0.3718813599999999</v>
+      </c>
+      <c r="P10">
+        <v>0.8677231733333333</v>
+      </c>
+      <c r="Q10">
+        <v>1.000723173333333</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.125831166211332</v>
+      </c>
+      <c r="T10">
+        <v>0.5590846333341145</v>
+      </c>
+      <c r="U10">
+        <v>0.0458</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03206</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.26767874221671</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1180159601903032</v>
+      </c>
+      <c r="C11">
+        <v>32.97697982589574</v>
+      </c>
+      <c r="D11">
+        <v>30.09247982589574</v>
+      </c>
+      <c r="E11">
+        <v>-3.2845</v>
+      </c>
+      <c r="F11">
+        <v>2.9655</v>
+      </c>
+      <c r="G11">
+        <v>5.85</v>
+      </c>
+      <c r="H11">
+        <v>26.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K11">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L11">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M11">
+        <v>0.1358199</v>
+      </c>
+      <c r="N11">
+        <v>1.224513433333333</v>
+      </c>
+      <c r="O11">
+        <v>0.3673540299999999</v>
+      </c>
+      <c r="P11">
+        <v>0.8571594033333332</v>
+      </c>
+      <c r="Q11">
+        <v>0.9901594033333333</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1265170991102233</v>
+      </c>
+      <c r="T11">
+        <v>0.5634910380735069</v>
+      </c>
+      <c r="U11">
+        <v>0.0458</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03206</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>10.01571443752597</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.117856447466181</v>
+      </c>
+      <c r="C12">
+        <v>32.70819762420908</v>
+      </c>
+      <c r="D12">
+        <v>30.15319762420909</v>
+      </c>
+      <c r="E12">
+        <v>-2.955</v>
+      </c>
+      <c r="F12">
+        <v>3.295</v>
+      </c>
+      <c r="G12">
+        <v>5.85</v>
+      </c>
+      <c r="H12">
+        <v>26.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K12">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L12">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M12">
+        <v>0.15816</v>
+      </c>
+      <c r="N12">
+        <v>1.202173333333333</v>
+      </c>
+      <c r="O12">
+        <v>0.3606519999999999</v>
+      </c>
+      <c r="P12">
+        <v>0.8415213333333331</v>
+      </c>
+      <c r="Q12">
+        <v>0.9745213333333332</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1272182749624233</v>
+      </c>
+      <c r="T12">
+        <v>0.5679953629182192</v>
+      </c>
+      <c r="U12">
+        <v>0.048</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.0336</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.600994773225423</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1175583347420588</v>
+      </c>
+      <c r="C13">
+        <v>32.49283223503077</v>
+      </c>
+      <c r="D13">
+        <v>30.26733223503077</v>
+      </c>
+      <c r="E13">
+        <v>-2.6255</v>
+      </c>
+      <c r="F13">
+        <v>3.6245</v>
+      </c>
+      <c r="G13">
+        <v>5.85</v>
+      </c>
+      <c r="H13">
+        <v>26.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K13">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L13">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M13">
+        <v>0.173976</v>
+      </c>
+      <c r="N13">
+        <v>1.186357333333333</v>
+      </c>
+      <c r="O13">
+        <v>0.3559071999999999</v>
+      </c>
+      <c r="P13">
+        <v>0.8304501333333332</v>
+      </c>
+      <c r="Q13">
+        <v>0.9634501333333333</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1279352075753469</v>
+      </c>
+      <c r="T13">
+        <v>0.5726009085459587</v>
+      </c>
+      <c r="U13">
+        <v>0.048</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.0336</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>7.819086157477657</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1173862220179366</v>
+      </c>
+      <c r="C14">
+        <v>32.22962111963568</v>
+      </c>
+      <c r="D14">
+        <v>30.33362111963568</v>
+      </c>
+      <c r="E14">
+        <v>-2.296</v>
+      </c>
+      <c r="F14">
+        <v>3.954</v>
+      </c>
+      <c r="G14">
+        <v>5.85</v>
+      </c>
+      <c r="H14">
+        <v>26.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K14">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L14">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M14">
+        <v>0.195723</v>
+      </c>
+      <c r="N14">
+        <v>1.164610333333333</v>
+      </c>
+      <c r="O14">
+        <v>0.3493830999999999</v>
+      </c>
+      <c r="P14">
+        <v>0.8152272333333332</v>
+      </c>
+      <c r="Q14">
+        <v>0.9482272333333334</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1286684341112916</v>
+      </c>
+      <c r="T14">
+        <v>0.5773111256652378</v>
+      </c>
+      <c r="U14">
+        <v>0.0495</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.03465</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>6.950298806646807</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1170986092938144</v>
+      </c>
+      <c r="C15">
+        <v>32.01154500674421</v>
+      </c>
+      <c r="D15">
+        <v>30.44504500674422</v>
+      </c>
+      <c r="E15">
+        <v>-1.9665</v>
+      </c>
+      <c r="F15">
+        <v>4.2835</v>
+      </c>
+      <c r="G15">
+        <v>5.85</v>
+      </c>
+      <c r="H15">
+        <v>26.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K15">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L15">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M15">
+        <v>0.21203325</v>
+      </c>
+      <c r="N15">
+        <v>1.148300083333333</v>
+      </c>
+      <c r="O15">
+        <v>0.344490025</v>
+      </c>
+      <c r="P15">
+        <v>0.8038100583333332</v>
+      </c>
+      <c r="Q15">
+        <v>0.9368100583333333</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1294185164296717</v>
+      </c>
+      <c r="T15">
+        <v>0.5821296236378335</v>
+      </c>
+      <c r="U15">
+        <v>0.0495</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.03465</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.415660436904746</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1169481965696921</v>
+      </c>
+      <c r="C16">
+        <v>31.74064293166759</v>
+      </c>
+      <c r="D16">
+        <v>30.50364293166759</v>
+      </c>
+      <c r="E16">
+        <v>-1.637</v>
+      </c>
+      <c r="F16">
+        <v>4.613</v>
+      </c>
+      <c r="G16">
+        <v>5.85</v>
+      </c>
+      <c r="H16">
+        <v>26.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K16">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L16">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M16">
+        <v>0.2348017</v>
+      </c>
+      <c r="N16">
+        <v>1.125531633333333</v>
+      </c>
+      <c r="O16">
+        <v>0.33765949</v>
+      </c>
+      <c r="P16">
+        <v>0.7878721433333332</v>
+      </c>
+      <c r="Q16">
+        <v>0.9208721433333333</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1301860425228978</v>
+      </c>
+      <c r="T16">
+        <v>0.5870601797028153</v>
+      </c>
+      <c r="U16">
+        <v>0.0509</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.03563</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.793541244945557</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1166703838455699</v>
+      </c>
+      <c r="C17">
+        <v>31.51996864588655</v>
+      </c>
+      <c r="D17">
+        <v>30.61246864588654</v>
+      </c>
+      <c r="E17">
+        <v>-1.3075</v>
+      </c>
+      <c r="F17">
+        <v>4.9425</v>
+      </c>
+      <c r="G17">
+        <v>5.85</v>
+      </c>
+      <c r="H17">
+        <v>26.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K17">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L17">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M17">
+        <v>0.25157325</v>
+      </c>
+      <c r="N17">
+        <v>1.108760083333333</v>
+      </c>
+      <c r="O17">
+        <v>0.3326280249999999</v>
+      </c>
+      <c r="P17">
+        <v>0.7761320583333331</v>
+      </c>
+      <c r="Q17">
+        <v>0.9091320583333332</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1309716280536117</v>
+      </c>
+      <c r="T17">
+        <v>0.592106748851679</v>
+      </c>
+      <c r="U17">
+        <v>0.0509</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.03563</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.407305161949186</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1163925711214477</v>
+      </c>
+      <c r="C18">
+        <v>31.30007364007223</v>
+      </c>
+      <c r="D18">
+        <v>30.72207364007223</v>
+      </c>
+      <c r="E18">
+        <v>-0.9779999999999998</v>
+      </c>
+      <c r="F18">
+        <v>5.272</v>
+      </c>
+      <c r="G18">
+        <v>5.85</v>
+      </c>
+      <c r="H18">
+        <v>26.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K18">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L18">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M18">
+        <v>0.2683448</v>
+      </c>
+      <c r="N18">
+        <v>1.091988533333333</v>
+      </c>
+      <c r="O18">
+        <v>0.32759656</v>
+      </c>
+      <c r="P18">
+        <v>0.7643919733333333</v>
+      </c>
+      <c r="Q18">
+        <v>0.8973919733333334</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1317759180017235</v>
+      </c>
+      <c r="T18">
+        <v>0.597273474408849</v>
+      </c>
+      <c r="U18">
+        <v>0.0509</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.03563</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.069348589327363</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1161147583973255</v>
+      </c>
+      <c r="C19">
+        <v>31.08096631471231</v>
+      </c>
+      <c r="D19">
+        <v>30.83246631471231</v>
+      </c>
+      <c r="E19">
+        <v>-0.6484999999999994</v>
+      </c>
+      <c r="F19">
+        <v>5.601500000000001</v>
+      </c>
+      <c r="G19">
+        <v>5.85</v>
+      </c>
+      <c r="H19">
+        <v>26.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K19">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L19">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M19">
+        <v>0.28511635</v>
+      </c>
+      <c r="N19">
+        <v>1.075216983333333</v>
+      </c>
+      <c r="O19">
+        <v>0.3225650949999999</v>
+      </c>
+      <c r="P19">
+        <v>0.7526518883333333</v>
+      </c>
+      <c r="Q19">
+        <v>0.8856518883333334</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1325995884305127</v>
+      </c>
+      <c r="T19">
+        <v>0.6025646993770352</v>
+      </c>
+      <c r="U19">
+        <v>0.0509</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.03563</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.771151613484577</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1158369456732033</v>
+      </c>
+      <c r="C20">
+        <v>30.86265519147063</v>
+      </c>
+      <c r="D20">
+        <v>30.94365519147063</v>
+      </c>
+      <c r="E20">
+        <v>-0.319</v>
+      </c>
+      <c r="F20">
+        <v>5.931</v>
+      </c>
+      <c r="G20">
+        <v>5.85</v>
+      </c>
+      <c r="H20">
+        <v>26.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K20">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L20">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M20">
+        <v>0.3018879</v>
+      </c>
+      <c r="N20">
+        <v>1.058445433333333</v>
+      </c>
+      <c r="O20">
+        <v>0.3175336299999999</v>
+      </c>
+      <c r="P20">
+        <v>0.7409118033333332</v>
+      </c>
+      <c r="Q20">
+        <v>0.8739118033333333</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1334433483819553</v>
+      </c>
+      <c r="T20">
+        <v>0.6079849786127379</v>
+      </c>
+      <c r="U20">
+        <v>0.0509</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.03563</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.506087634957655</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1159049329490811</v>
+      </c>
+      <c r="C21">
+        <v>30.50587062300394</v>
+      </c>
+      <c r="D21">
+        <v>30.91637062300394</v>
+      </c>
+      <c r="E21">
+        <v>0.0105000000000004</v>
+      </c>
+      <c r="F21">
+        <v>6.2605</v>
+      </c>
+      <c r="G21">
+        <v>5.85</v>
+      </c>
+      <c r="H21">
+        <v>26.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K21">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L21">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M21">
+        <v>0.33493675</v>
+      </c>
+      <c r="N21">
+        <v>1.025396583333333</v>
+      </c>
+      <c r="O21">
+        <v>0.307618975</v>
+      </c>
+      <c r="P21">
+        <v>0.7177776083333332</v>
+      </c>
+      <c r="Q21">
+        <v>0.8507776083333333</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1343079419124458</v>
+      </c>
+      <c r="T21">
+        <v>0.6135390919036433</v>
+      </c>
+      <c r="U21">
+        <v>0.0535</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.03745</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.06146334594019</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1160233202249589</v>
+      </c>
+      <c r="C22">
+        <v>30.12897425507487</v>
+      </c>
+      <c r="D22">
+        <v>30.86897425507487</v>
+      </c>
+      <c r="E22">
+        <v>0.3400000000000007</v>
+      </c>
+      <c r="F22">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="G22">
+        <v>5.85</v>
+      </c>
+      <c r="H22">
+        <v>26.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K22">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L22">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M22">
+        <v>0.370358</v>
+      </c>
+      <c r="N22">
+        <v>0.9899753333333332</v>
+      </c>
+      <c r="O22">
+        <v>0.2969925999999999</v>
+      </c>
+      <c r="P22">
+        <v>0.6929827333333333</v>
+      </c>
+      <c r="Q22">
+        <v>0.8259827333333334</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1351941502811986</v>
+      </c>
+      <c r="T22">
+        <v>0.6192320580268215</v>
+      </c>
+      <c r="U22">
+        <v>0.0562</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.03934</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.673022678957476</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1164735075008367</v>
+      </c>
+      <c r="C23">
+        <v>29.62056100812406</v>
+      </c>
+      <c r="D23">
+        <v>30.69006100812405</v>
+      </c>
+      <c r="E23">
+        <v>0.6695000000000002</v>
+      </c>
+      <c r="F23">
+        <v>6.9195</v>
+      </c>
+      <c r="G23">
+        <v>5.85</v>
+      </c>
+      <c r="H23">
+        <v>26.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K23">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L23">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M23">
+        <v>0.42139755</v>
+      </c>
+      <c r="N23">
+        <v>0.9389357833333332</v>
+      </c>
+      <c r="O23">
+        <v>0.281680735</v>
+      </c>
+      <c r="P23">
+        <v>0.6572550483333333</v>
+      </c>
+      <c r="Q23">
+        <v>0.7902550483333334</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1361027943048566</v>
+      </c>
+      <c r="T23">
+        <v>0.6250691498746368</v>
+      </c>
+      <c r="U23">
+        <v>0.0609</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.04263</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.228147228984443</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1162656947767145</v>
+      </c>
+      <c r="C24">
+        <v>29.37339145387759</v>
+      </c>
+      <c r="D24">
+        <v>30.7723914538776</v>
+      </c>
+      <c r="E24">
+        <v>0.9990000000000006</v>
+      </c>
+      <c r="F24">
+        <v>7.249000000000001</v>
+      </c>
+      <c r="G24">
+        <v>5.85</v>
+      </c>
+      <c r="H24">
+        <v>26.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K24">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L24">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M24">
+        <v>0.4414641</v>
+      </c>
+      <c r="N24">
+        <v>0.9188692333333331</v>
+      </c>
+      <c r="O24">
+        <v>0.2756607699999999</v>
+      </c>
+      <c r="P24">
+        <v>0.6432084633333333</v>
+      </c>
+      <c r="Q24">
+        <v>0.7762084633333334</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1370347368932237</v>
+      </c>
+      <c r="T24">
+        <v>0.6310559107441911</v>
+      </c>
+      <c r="U24">
+        <v>0.0609</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.04263</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.081413264030604</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1175551820525923</v>
+      </c>
+      <c r="C25">
+        <v>28.54004388227771</v>
+      </c>
+      <c r="D25">
+        <v>30.26854388227771</v>
+      </c>
+      <c r="E25">
+        <v>1.328500000000001</v>
+      </c>
+      <c r="F25">
+        <v>7.578500000000001</v>
+      </c>
+      <c r="G25">
+        <v>5.85</v>
+      </c>
+      <c r="H25">
+        <v>26.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K25">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L25">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M25">
+        <v>0.5320107000000001</v>
+      </c>
+      <c r="N25">
+        <v>0.8283226333333331</v>
+      </c>
+      <c r="O25">
+        <v>0.2484967899999999</v>
+      </c>
+      <c r="P25">
+        <v>0.5798258433333332</v>
+      </c>
+      <c r="Q25">
+        <v>0.7128258433333333</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1379908857825874</v>
+      </c>
+      <c r="T25">
+        <v>0.6371981718960715</v>
+      </c>
+      <c r="U25">
+        <v>0.0702</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.04914</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.556966116157688</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.11820206932847</v>
+      </c>
+      <c r="C26">
+        <v>27.96394658245428</v>
+      </c>
+      <c r="D26">
+        <v>30.02194658245428</v>
+      </c>
+      <c r="E26">
+        <v>1.658</v>
+      </c>
+      <c r="F26">
+        <v>7.908</v>
+      </c>
+      <c r="G26">
+        <v>5.85</v>
+      </c>
+      <c r="H26">
+        <v>26.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K26">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L26">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M26">
+        <v>0.5923092</v>
+      </c>
+      <c r="N26">
+        <v>0.7680241333333332</v>
+      </c>
+      <c r="O26">
+        <v>0.23040724</v>
+      </c>
+      <c r="P26">
+        <v>0.5376168933333332</v>
+      </c>
+      <c r="Q26">
+        <v>0.6706168933333333</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.138972196484829</v>
+      </c>
+      <c r="T26">
+        <v>0.6435020714993172</v>
+      </c>
+      <c r="U26">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V26">
+        <v>0.3</v>
+      </c>
+      <c r="W26">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.296660820620941</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1180922566043479</v>
+      </c>
+      <c r="C27">
+        <v>27.67602430868952</v>
+      </c>
+      <c r="D27">
+        <v>30.06352430868952</v>
+      </c>
+      <c r="E27">
+        <v>1.987500000000001</v>
+      </c>
+      <c r="F27">
+        <v>8.237500000000001</v>
+      </c>
+      <c r="G27">
+        <v>5.85</v>
+      </c>
+      <c r="H27">
+        <v>26.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K27">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L27">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M27">
+        <v>0.61698875</v>
+      </c>
+      <c r="N27">
+        <v>0.7433445833333332</v>
+      </c>
+      <c r="O27">
+        <v>0.2230033749999999</v>
+      </c>
+      <c r="P27">
+        <v>0.5203412083333332</v>
+      </c>
+      <c r="Q27">
+        <v>0.6533412083333333</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1399796754724638</v>
+      </c>
+      <c r="T27">
+        <v>0.6499740750919828</v>
+      </c>
+      <c r="U27">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V27">
+        <v>0.3</v>
+      </c>
+      <c r="W27">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.204794387796103</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1179824438802256</v>
+      </c>
+      <c r="C28">
+        <v>27.3882173575432</v>
+      </c>
+      <c r="D28">
+        <v>30.1052173575432</v>
+      </c>
+      <c r="E28">
+        <v>2.317</v>
+      </c>
+      <c r="F28">
+        <v>8.567</v>
+      </c>
+      <c r="G28">
+        <v>5.85</v>
+      </c>
+      <c r="H28">
+        <v>26.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K28">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L28">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M28">
+        <v>0.6416683</v>
+      </c>
+      <c r="N28">
+        <v>0.7186650333333332</v>
+      </c>
+      <c r="O28">
+        <v>0.21559951</v>
+      </c>
+      <c r="P28">
+        <v>0.5030655233333332</v>
+      </c>
+      <c r="Q28">
+        <v>0.6360655233333333</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1410143836219265</v>
+      </c>
+      <c r="T28">
+        <v>0.6566209977006663</v>
+      </c>
+      <c r="U28">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V28">
+        <v>0.3</v>
+      </c>
+      <c r="W28">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.1199946036501</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1178726311561034</v>
+      </c>
+      <c r="C29">
+        <v>27.10052620948082</v>
+      </c>
+      <c r="D29">
+        <v>30.14702620948082</v>
+      </c>
+      <c r="E29">
+        <v>2.646500000000001</v>
+      </c>
+      <c r="F29">
+        <v>8.896500000000001</v>
+      </c>
+      <c r="G29">
+        <v>5.85</v>
+      </c>
+      <c r="H29">
+        <v>26.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K29">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L29">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M29">
+        <v>0.6663478500000001</v>
+      </c>
+      <c r="N29">
+        <v>0.6939854833333331</v>
+      </c>
+      <c r="O29">
+        <v>0.2081956449999999</v>
+      </c>
+      <c r="P29">
+        <v>0.4857898383333332</v>
+      </c>
+      <c r="Q29">
+        <v>0.6187898383333332</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1420774399398677</v>
+      </c>
+      <c r="T29">
+        <v>0.6634500277780809</v>
+      </c>
+      <c r="U29">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V29">
+        <v>0.3</v>
+      </c>
+      <c r="W29">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.041476284996392</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1209576184319812</v>
+      </c>
+      <c r="C30">
+        <v>25.63901685920003</v>
+      </c>
+      <c r="D30">
+        <v>29.01501685920003</v>
+      </c>
+      <c r="E30">
+        <v>2.976000000000001</v>
+      </c>
+      <c r="F30">
+        <v>9.226000000000001</v>
+      </c>
+      <c r="G30">
+        <v>5.85</v>
+      </c>
+      <c r="H30">
+        <v>26.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K30">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L30">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M30">
+        <v>0.8414112000000001</v>
+      </c>
+      <c r="N30">
+        <v>0.518922133333333</v>
+      </c>
+      <c r="O30">
+        <v>0.1556766399999999</v>
+      </c>
+      <c r="P30">
+        <v>0.3632454933333331</v>
+      </c>
+      <c r="Q30">
+        <v>0.4962454933333332</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1431700255999739</v>
+      </c>
+      <c r="T30">
+        <v>0.6704687531354236</v>
+      </c>
+      <c r="U30">
+        <v>0.0912</v>
+      </c>
+      <c r="V30">
+        <v>0.3</v>
+      </c>
+      <c r="W30">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>1.616728340831846</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.120961905707859</v>
+      </c>
+      <c r="C31">
+        <v>25.30800283173436</v>
+      </c>
+      <c r="D31">
+        <v>29.01350283173437</v>
+      </c>
+      <c r="E31">
+        <v>3.3055</v>
+      </c>
+      <c r="F31">
+        <v>9.5555</v>
+      </c>
+      <c r="G31">
+        <v>5.85</v>
+      </c>
+      <c r="H31">
+        <v>26.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K31">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L31">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M31">
+        <v>0.8714616000000001</v>
+      </c>
+      <c r="N31">
+        <v>0.4888717333333331</v>
+      </c>
+      <c r="O31">
+        <v>0.1466615199999999</v>
+      </c>
+      <c r="P31">
+        <v>0.3422102133333332</v>
+      </c>
+      <c r="Q31">
+        <v>0.4752102133333333</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1442933883209282</v>
+      </c>
+      <c r="T31">
+        <v>0.6776851890662127</v>
+      </c>
+      <c r="U31">
+        <v>0.0912</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>1.560979087699714</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1209661929837368</v>
+      </c>
+      <c r="C32">
+        <v>24.97698896226684</v>
+      </c>
+      <c r="D32">
+        <v>29.01198896226684</v>
+      </c>
+      <c r="E32">
+        <v>3.635</v>
+      </c>
+      <c r="F32">
+        <v>9.885</v>
+      </c>
+      <c r="G32">
+        <v>5.85</v>
+      </c>
+      <c r="H32">
+        <v>26.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K32">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L32">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M32">
+        <v>0.901512</v>
+      </c>
+      <c r="N32">
+        <v>0.4588213333333332</v>
+      </c>
+      <c r="O32">
+        <v>0.1376463999999999</v>
+      </c>
+      <c r="P32">
+        <v>0.3211749333333332</v>
+      </c>
+      <c r="Q32">
+        <v>0.4541749333333334</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.145448847119624</v>
+      </c>
+      <c r="T32">
+        <v>0.6851078088807386</v>
+      </c>
+      <c r="U32">
+        <v>0.0912</v>
+      </c>
+      <c r="V32">
+        <v>0.3</v>
+      </c>
+      <c r="W32">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>1.508946451443057</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.138481822682083</v>
+      </c>
+      <c r="C33">
+        <v>19.54963619630904</v>
+      </c>
+      <c r="D33">
+        <v>23.91413619630904</v>
+      </c>
+      <c r="E33">
+        <v>3.964500000000001</v>
+      </c>
+      <c r="F33">
+        <v>10.2145</v>
+      </c>
+      <c r="G33">
+        <v>5.85</v>
+      </c>
+      <c r="H33">
+        <v>26.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K33">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L33">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M33">
+        <v>1.5995907</v>
+      </c>
+      <c r="N33">
+        <v>-0.2392573666666671</v>
+      </c>
+      <c r="O33">
+        <v>-0.07177721000000012</v>
+      </c>
+      <c r="P33">
+        <v>-0.167480156666667</v>
+      </c>
+      <c r="Q33">
+        <v>-0.03448015666666684</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1482916741384457</v>
+      </c>
+      <c r="T33">
+        <v>0.7033700127628613</v>
+      </c>
+      <c r="U33">
+        <v>0.1566</v>
+      </c>
+      <c r="V33">
+        <v>0.2551277648713511</v>
+      </c>
+      <c r="W33">
+        <v>0.1166469920211464</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.8504258829045036</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1396598226820829</v>
+      </c>
+      <c r="C34">
+        <v>18.94082921668001</v>
+      </c>
+      <c r="D34">
+        <v>23.63482921668001</v>
+      </c>
+      <c r="E34">
+        <v>4.294</v>
+      </c>
+      <c r="F34">
+        <v>10.544</v>
+      </c>
+      <c r="G34">
+        <v>5.85</v>
+      </c>
+      <c r="H34">
+        <v>26.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K34">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L34">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M34">
+        <v>1.6511904</v>
+      </c>
+      <c r="N34">
+        <v>-0.290857066666667</v>
+      </c>
+      <c r="O34">
+        <v>-0.08725712000000009</v>
+      </c>
+      <c r="P34">
+        <v>-0.2035999466666669</v>
+      </c>
+      <c r="Q34">
+        <v>-0.0705999466666668</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1499018458169523</v>
+      </c>
+      <c r="T34">
+        <v>0.7137136894211388</v>
+      </c>
+      <c r="U34">
+        <v>0.1566</v>
+      </c>
+      <c r="V34">
+        <v>0.2471550222191214</v>
+      </c>
+      <c r="W34">
+        <v>0.1178955235204856</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.8238500740637379</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1596859025700518</v>
+      </c>
+      <c r="C35">
+        <v>14.69595969906851</v>
+      </c>
+      <c r="D35">
+        <v>19.71945969906851</v>
+      </c>
+      <c r="E35">
+        <v>4.623500000000002</v>
+      </c>
+      <c r="F35">
+        <v>10.8735</v>
+      </c>
+      <c r="G35">
+        <v>5.85</v>
+      </c>
+      <c r="H35">
+        <v>26.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K35">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L35">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M35">
+        <v>2.270386800000001</v>
+      </c>
+      <c r="N35">
+        <v>-0.9100534666666675</v>
+      </c>
+      <c r="O35">
+        <v>-0.2730160400000002</v>
+      </c>
+      <c r="P35">
+        <v>-0.6370374266666673</v>
+      </c>
+      <c r="Q35">
+        <v>-0.5040374266666672</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1539810970798454</v>
+      </c>
+      <c r="T35">
+        <v>0.7399186318098733</v>
+      </c>
+      <c r="U35">
+        <v>0.2088</v>
+      </c>
+      <c r="V35">
+        <v>0.1797491070684519</v>
+      </c>
+      <c r="W35">
+        <v>0.1712683864441073</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.599163690228173</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1613859025700518</v>
+      </c>
+      <c r="C36">
+        <v>14.09299365782238</v>
+      </c>
+      <c r="D36">
+        <v>19.44599365782238</v>
+      </c>
+      <c r="E36">
+        <v>4.953000000000001</v>
+      </c>
+      <c r="F36">
+        <v>11.203</v>
+      </c>
+      <c r="G36">
+        <v>5.85</v>
+      </c>
+      <c r="H36">
+        <v>26.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K36">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L36">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M36">
+        <v>2.3391864</v>
+      </c>
+      <c r="N36">
+        <v>-0.9788530666666673</v>
+      </c>
+      <c r="O36">
+        <v>-0.2936559200000002</v>
+      </c>
+      <c r="P36">
+        <v>-0.6851971466666671</v>
+      </c>
+      <c r="Q36">
+        <v>-0.552197146666667</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1557262652174188</v>
+      </c>
+      <c r="T36">
+        <v>0.751129520170629</v>
+      </c>
+      <c r="U36">
+        <v>0.2088</v>
+      </c>
+      <c r="V36">
+        <v>0.1744623686252621</v>
+      </c>
+      <c r="W36">
+        <v>0.1723722574310453</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5815412287508738</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1630859025700518</v>
+      </c>
+      <c r="C37">
+        <v>13.4975086302794</v>
+      </c>
+      <c r="D37">
+        <v>19.1800086302794</v>
+      </c>
+      <c r="E37">
+        <v>5.282500000000002</v>
+      </c>
+      <c r="F37">
+        <v>11.5325</v>
+      </c>
+      <c r="G37">
+        <v>5.85</v>
+      </c>
+      <c r="H37">
+        <v>26.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K37">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L37">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M37">
+        <v>2.407986000000001</v>
+      </c>
+      <c r="N37">
+        <v>-1.047652666666667</v>
+      </c>
+      <c r="O37">
+        <v>-0.3142958000000002</v>
+      </c>
+      <c r="P37">
+        <v>-0.7333568666666672</v>
+      </c>
+      <c r="Q37">
+        <v>-0.6003568666666671</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1575251308361484</v>
+      </c>
+      <c r="T37">
+        <v>0.7626853589424848</v>
+      </c>
+      <c r="U37">
+        <v>0.2088</v>
+      </c>
+      <c r="V37">
+        <v>0.1694777295216832</v>
+      </c>
+      <c r="W37">
+        <v>0.1734130500758726</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5649257650722773</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1647859025700518</v>
+      </c>
+      <c r="C38">
+        <v>12.90920177962129</v>
+      </c>
+      <c r="D38">
+        <v>18.92120177962129</v>
+      </c>
+      <c r="E38">
+        <v>5.612</v>
+      </c>
+      <c r="F38">
+        <v>11.862</v>
+      </c>
+      <c r="G38">
+        <v>5.85</v>
+      </c>
+      <c r="H38">
+        <v>26.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K38">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L38">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M38">
+        <v>2.4767856</v>
+      </c>
+      <c r="N38">
+        <v>-1.116452266666667</v>
+      </c>
+      <c r="O38">
+        <v>-0.3349356800000001</v>
+      </c>
+      <c r="P38">
+        <v>-0.7815165866666671</v>
+      </c>
+      <c r="Q38">
+        <v>-0.648516586666667</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1593802110054632</v>
+      </c>
+      <c r="T38">
+        <v>0.774602317675961</v>
+      </c>
+      <c r="U38">
+        <v>0.2088</v>
+      </c>
+      <c r="V38">
+        <v>0.1647700148127476</v>
+      </c>
+      <c r="W38">
+        <v>0.1743960209070983</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5492333827091587</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1664859025700518</v>
+      </c>
+      <c r="C39">
+        <v>12.32778639681144</v>
+      </c>
+      <c r="D39">
+        <v>18.66928639681144</v>
+      </c>
+      <c r="E39">
+        <v>5.941500000000001</v>
+      </c>
+      <c r="F39">
+        <v>12.1915</v>
+      </c>
+      <c r="G39">
+        <v>5.85</v>
+      </c>
+      <c r="H39">
+        <v>26.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K39">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L39">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M39">
+        <v>2.545585200000001</v>
+      </c>
+      <c r="N39">
+        <v>-1.185251866666667</v>
+      </c>
+      <c r="O39">
+        <v>-0.3555755600000002</v>
+      </c>
+      <c r="P39">
+        <v>-0.8296763066666673</v>
+      </c>
+      <c r="Q39">
+        <v>-0.6966763066666671</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1612941826087245</v>
+      </c>
+      <c r="T39">
+        <v>0.7868975925597065</v>
+      </c>
+      <c r="U39">
+        <v>0.2088</v>
+      </c>
+      <c r="V39">
+        <v>0.1603167711691598</v>
+      </c>
+      <c r="W39">
+        <v>0.1753258581798794</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5343892372305327</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1681859025700518</v>
+      </c>
+      <c r="C40">
+        <v>11.75299084108119</v>
+      </c>
+      <c r="D40">
+        <v>18.4239908410812</v>
+      </c>
+      <c r="E40">
+        <v>6.271000000000001</v>
+      </c>
+      <c r="F40">
+        <v>12.521</v>
+      </c>
+      <c r="G40">
+        <v>5.85</v>
+      </c>
+      <c r="H40">
+        <v>26.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K40">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L40">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M40">
+        <v>2.6143848</v>
+      </c>
+      <c r="N40">
+        <v>-1.254051466666667</v>
+      </c>
+      <c r="O40">
+        <v>-0.3762154400000001</v>
+      </c>
+      <c r="P40">
+        <v>-0.8778360266666669</v>
+      </c>
+      <c r="Q40">
+        <v>-0.7448360266666668</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1632698952314459</v>
+      </c>
+      <c r="T40">
+        <v>0.7995894892138953</v>
+      </c>
+      <c r="U40">
+        <v>0.2088</v>
+      </c>
+      <c r="V40">
+        <v>0.1560979087699714</v>
+      </c>
+      <c r="W40">
+        <v>0.17620675664883</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5203263625665713</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1698859025700518</v>
+      </c>
+      <c r="C41">
+        <v>11.18455756285855</v>
+      </c>
+      <c r="D41">
+        <v>18.18505756285855</v>
+      </c>
+      <c r="E41">
+        <v>6.600500000000002</v>
+      </c>
+      <c r="F41">
+        <v>12.8505</v>
+      </c>
+      <c r="G41">
+        <v>5.85</v>
+      </c>
+      <c r="H41">
+        <v>26.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K41">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L41">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M41">
+        <v>2.6831844</v>
+      </c>
+      <c r="N41">
+        <v>-1.322851066666667</v>
+      </c>
+      <c r="O41">
+        <v>-0.3968553200000002</v>
+      </c>
+      <c r="P41">
+        <v>-0.9259957466666671</v>
+      </c>
+      <c r="Q41">
+        <v>-0.7929957466666669</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1653103853172073</v>
+      </c>
+      <c r="T41">
+        <v>0.8126975136272379</v>
+      </c>
+      <c r="U41">
+        <v>0.2088</v>
+      </c>
+      <c r="V41">
+        <v>0.1520953982886901</v>
+      </c>
+      <c r="W41">
+        <v>0.1770424808373215</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5069846609623002</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1841972392112461</v>
+      </c>
+      <c r="C42">
+        <v>9.065116556871166</v>
+      </c>
+      <c r="D42">
+        <v>16.39511655687117</v>
+      </c>
+      <c r="E42">
+        <v>6.930000000000001</v>
+      </c>
+      <c r="F42">
+        <v>13.18</v>
+      </c>
+      <c r="G42">
+        <v>5.85</v>
+      </c>
+      <c r="H42">
+        <v>26.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K42">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L42">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M42">
+        <v>3.147384000000001</v>
+      </c>
+      <c r="N42">
+        <v>-1.787050666666667</v>
+      </c>
+      <c r="O42">
+        <v>-0.5361152000000002</v>
+      </c>
+      <c r="P42">
+        <v>-1.250935466666667</v>
+      </c>
+      <c r="Q42">
+        <v>-1.117935466666667</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1684377861411512</v>
+      </c>
+      <c r="T42">
+        <v>0.8327878079328179</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.1296632377873179</v>
+      </c>
+      <c r="W42">
+        <v>0.2078364188163885</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.4322107926243931</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1861972392112461</v>
+      </c>
+      <c r="C43">
+        <v>8.513154906373437</v>
+      </c>
+      <c r="D43">
+        <v>16.17265490637344</v>
+      </c>
+      <c r="E43">
+        <v>7.259500000000003</v>
+      </c>
+      <c r="F43">
+        <v>13.5095</v>
+      </c>
+      <c r="G43">
+        <v>5.85</v>
+      </c>
+      <c r="H43">
+        <v>26.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K43">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L43">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M43">
+        <v>3.226068600000001</v>
+      </c>
+      <c r="N43">
+        <v>-1.865735266666668</v>
+      </c>
+      <c r="O43">
+        <v>-0.5597205800000004</v>
+      </c>
+      <c r="P43">
+        <v>-1.306014686666667</v>
+      </c>
+      <c r="Q43">
+        <v>-1.173014686666667</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1706350367537131</v>
+      </c>
+      <c r="T43">
+        <v>0.8469028555248995</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.1265007197925053</v>
+      </c>
+      <c r="W43">
+        <v>0.2085916281135497</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.4216690659750176</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1881972392112461</v>
+      </c>
+      <c r="C44">
+        <v>7.967149501163027</v>
+      </c>
+      <c r="D44">
+        <v>15.95614950116303</v>
+      </c>
+      <c r="E44">
+        <v>7.589</v>
+      </c>
+      <c r="F44">
+        <v>13.839</v>
+      </c>
+      <c r="G44">
+        <v>5.85</v>
+      </c>
+      <c r="H44">
+        <v>26.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K44">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L44">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M44">
+        <v>3.3047532</v>
+      </c>
+      <c r="N44">
+        <v>-1.944419866666667</v>
+      </c>
+      <c r="O44">
+        <v>-0.5833259600000001</v>
+      </c>
+      <c r="P44">
+        <v>-1.361093906666667</v>
+      </c>
+      <c r="Q44">
+        <v>-1.228093906666667</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1729080546287771</v>
+      </c>
+      <c r="T44">
+        <v>0.8615046288960184</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.1234887978926837</v>
+      </c>
+      <c r="W44">
+        <v>0.2093108750632271</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.4116293263089459</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1901972392112461</v>
+      </c>
+      <c r="C45">
+        <v>7.426864290226664</v>
+      </c>
+      <c r="D45">
+        <v>15.74536429022667</v>
+      </c>
+      <c r="E45">
+        <v>7.918500000000002</v>
+      </c>
+      <c r="F45">
+        <v>14.1685</v>
+      </c>
+      <c r="G45">
+        <v>5.85</v>
+      </c>
+      <c r="H45">
+        <v>26.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K45">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L45">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M45">
+        <v>3.383437800000001</v>
+      </c>
+      <c r="N45">
+        <v>-2.023104466666668</v>
+      </c>
+      <c r="O45">
+        <v>-0.6069313400000003</v>
+      </c>
+      <c r="P45">
+        <v>-1.416173126666667</v>
+      </c>
+      <c r="Q45">
+        <v>-1.283173126666667</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1752608275170013</v>
+      </c>
+      <c r="T45">
+        <v>0.8766187451924398</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.1206169653835516</v>
+      </c>
+      <c r="W45">
+        <v>0.2099966686664079</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.4020565512785053</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1921972392112462</v>
+      </c>
+      <c r="C46">
+        <v>6.892075533125322</v>
+      </c>
+      <c r="D46">
+        <v>15.54007553312532</v>
+      </c>
+      <c r="E46">
+        <v>8.248000000000001</v>
+      </c>
+      <c r="F46">
+        <v>14.498</v>
+      </c>
+      <c r="G46">
+        <v>5.85</v>
+      </c>
+      <c r="H46">
+        <v>26.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K46">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L46">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M46">
+        <v>3.462122400000001</v>
+      </c>
+      <c r="N46">
+        <v>-2.101789066666667</v>
+      </c>
+      <c r="O46">
+        <v>-0.6305367200000002</v>
+      </c>
+      <c r="P46">
+        <v>-1.471252346666667</v>
+      </c>
+      <c r="Q46">
+        <v>-1.338252346666667</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1776976280083763</v>
+      </c>
+      <c r="T46">
+        <v>0.8922726513565906</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.1178756707157436</v>
+      </c>
+      <c r="W46">
+        <v>0.2106512898330805</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.392918902385812</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1941972392112462</v>
+      </c>
+      <c r="C47">
+        <v>6.362571007793955</v>
+      </c>
+      <c r="D47">
+        <v>15.34007100779396</v>
+      </c>
+      <c r="E47">
+        <v>8.577500000000002</v>
+      </c>
+      <c r="F47">
+        <v>14.8275</v>
+      </c>
+      <c r="G47">
+        <v>5.85</v>
+      </c>
+      <c r="H47">
+        <v>26.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K47">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L47">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M47">
+        <v>3.540807000000001</v>
+      </c>
+      <c r="N47">
+        <v>-2.180473666666668</v>
+      </c>
+      <c r="O47">
+        <v>-0.6541421000000003</v>
+      </c>
+      <c r="P47">
+        <v>-1.526331566666667</v>
+      </c>
+      <c r="Q47">
+        <v>-1.393331566666667</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1802230394267104</v>
+      </c>
+      <c r="T47">
+        <v>0.9084957904721649</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.1152562113665048</v>
+      </c>
+      <c r="W47">
+        <v>0.2112768167256787</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3841873712216828</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1961972392112462</v>
+      </c>
+      <c r="C48">
+        <v>5.838149278738646</v>
+      </c>
+      <c r="D48">
+        <v>15.14514927873865</v>
+      </c>
+      <c r="E48">
+        <v>8.907000000000002</v>
+      </c>
+      <c r="F48">
+        <v>15.157</v>
+      </c>
+      <c r="G48">
+        <v>5.85</v>
+      </c>
+      <c r="H48">
+        <v>26.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K48">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L48">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M48">
+        <v>3.619491600000001</v>
+      </c>
+      <c r="N48">
+        <v>-2.259158266666668</v>
+      </c>
+      <c r="O48">
+        <v>-0.6777474800000003</v>
+      </c>
+      <c r="P48">
+        <v>-1.581410786666667</v>
+      </c>
+      <c r="Q48">
+        <v>-1.448410786666667</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1828419846012791</v>
+      </c>
+      <c r="T48">
+        <v>0.9253197865920199</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.1127506415541895</v>
+      </c>
+      <c r="W48">
+        <v>0.2118751467968596</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3758354718472984</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1981972392112462</v>
+      </c>
+      <c r="C49">
+        <v>5.318619020326611</v>
+      </c>
+      <c r="D49">
+        <v>14.95511902032662</v>
+      </c>
+      <c r="E49">
+        <v>9.236500000000003</v>
+      </c>
+      <c r="F49">
+        <v>15.4865</v>
+      </c>
+      <c r="G49">
+        <v>5.85</v>
+      </c>
+      <c r="H49">
+        <v>26.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K49">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L49">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M49">
+        <v>3.698176200000001</v>
+      </c>
+      <c r="N49">
+        <v>-2.337842866666668</v>
+      </c>
+      <c r="O49">
+        <v>-0.7013528600000004</v>
+      </c>
+      <c r="P49">
+        <v>-1.636490006666667</v>
+      </c>
+      <c r="Q49">
+        <v>-1.503490006666667</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1855597578956429</v>
+      </c>
+      <c r="T49">
+        <v>0.9427786504899824</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.1103516917338876</v>
+      </c>
+      <c r="W49">
+        <v>0.2124480160139477</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3678389724462919</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2001972392112461</v>
+      </c>
+      <c r="C50">
+        <v>4.803798390390044</v>
+      </c>
+      <c r="D50">
+        <v>14.76979839039004</v>
+      </c>
+      <c r="E50">
+        <v>9.566000000000001</v>
+      </c>
+      <c r="F50">
+        <v>15.816</v>
+      </c>
+      <c r="G50">
+        <v>5.85</v>
+      </c>
+      <c r="H50">
+        <v>26.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K50">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L50">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M50">
+        <v>3.776860800000001</v>
+      </c>
+      <c r="N50">
+        <v>-2.416527466666667</v>
+      </c>
+      <c r="O50">
+        <v>-0.7249582400000002</v>
+      </c>
+      <c r="P50">
+        <v>-1.691569226666667</v>
+      </c>
+      <c r="Q50">
+        <v>-1.558569226666667</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1883820609320976</v>
+      </c>
+      <c r="T50">
+        <v>0.9609090091532514</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.1080526981560983</v>
+      </c>
+      <c r="W50">
+        <v>0.2129970156803237</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3601756605203276</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2021972392112461</v>
+      </c>
+      <c r="C51">
+        <v>4.293514449832816</v>
+      </c>
+      <c r="D51">
+        <v>14.58901444983282</v>
+      </c>
+      <c r="E51">
+        <v>9.895500000000002</v>
+      </c>
+      <c r="F51">
+        <v>16.1455</v>
+      </c>
+      <c r="G51">
+        <v>5.85</v>
+      </c>
+      <c r="H51">
+        <v>26.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K51">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L51">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M51">
+        <v>3.8555454</v>
+      </c>
+      <c r="N51">
+        <v>-2.495212066666667</v>
+      </c>
+      <c r="O51">
+        <v>-0.7485636200000002</v>
+      </c>
+      <c r="P51">
+        <v>-1.746648446666667</v>
+      </c>
+      <c r="Q51">
+        <v>-1.613648446666667</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1913150425190014</v>
+      </c>
+      <c r="T51">
+        <v>0.9797503622739032</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1058475410508718</v>
+      </c>
+      <c r="W51">
+        <v>0.2135236071970518</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3528251368362393</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2041972392112461</v>
+      </c>
+      <c r="C52">
+        <v>3.787602624346423</v>
+      </c>
+      <c r="D52">
+        <v>14.41260262434642</v>
+      </c>
+      <c r="E52">
+        <v>10.225</v>
+      </c>
+      <c r="F52">
+        <v>16.475</v>
+      </c>
+      <c r="G52">
+        <v>5.85</v>
+      </c>
+      <c r="H52">
+        <v>26.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K52">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L52">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M52">
+        <v>3.93423</v>
+      </c>
+      <c r="N52">
+        <v>-2.573896666666667</v>
+      </c>
+      <c r="O52">
+        <v>-0.7721690000000001</v>
+      </c>
+      <c r="P52">
+        <v>-1.801727666666667</v>
+      </c>
+      <c r="Q52">
+        <v>-1.668727666666667</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1943653433693815</v>
+      </c>
+      <c r="T52">
+        <v>0.9993453695193814</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1037305902298544</v>
+      </c>
+      <c r="W52">
+        <v>0.2140291350531108</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3457686340995145</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2061972392112461</v>
+      </c>
+      <c r="C53">
+        <v>3.285906204713019</v>
+      </c>
+      <c r="D53">
+        <v>14.24040620471302</v>
+      </c>
+      <c r="E53">
+        <v>10.5545</v>
+      </c>
+      <c r="F53">
+        <v>16.8045</v>
+      </c>
+      <c r="G53">
+        <v>5.85</v>
+      </c>
+      <c r="H53">
+        <v>26.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K53">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L53">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M53">
+        <v>4.0129146</v>
+      </c>
+      <c r="N53">
+        <v>-2.652581266666667</v>
+      </c>
+      <c r="O53">
+        <v>-0.7957743800000001</v>
+      </c>
+      <c r="P53">
+        <v>-1.856806886666667</v>
+      </c>
+      <c r="Q53">
+        <v>-1.723806886666667</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1975401462952872</v>
+      </c>
+      <c r="T53">
+        <v>1.019740172978961</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.1016966570880925</v>
+      </c>
+      <c r="W53">
+        <v>0.2145148382873635</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3389888569603083</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2081972392112462</v>
+      </c>
+      <c r="C54">
+        <v>2.788275882506824</v>
+      </c>
+      <c r="D54">
+        <v>14.07227588250683</v>
+      </c>
+      <c r="E54">
+        <v>10.884</v>
+      </c>
+      <c r="F54">
+        <v>17.134</v>
+      </c>
+      <c r="G54">
+        <v>5.85</v>
+      </c>
+      <c r="H54">
+        <v>26.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K54">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L54">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M54">
+        <v>4.0915992</v>
+      </c>
+      <c r="N54">
+        <v>-2.731265866666667</v>
+      </c>
+      <c r="O54">
+        <v>-0.81937976</v>
+      </c>
+      <c r="P54">
+        <v>-1.911886106666667</v>
+      </c>
+      <c r="Q54">
+        <v>-1.778886106666667</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2008472326764391</v>
+      </c>
+      <c r="T54">
+        <v>1.040984759916022</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.09974095214409075</v>
+      </c>
+      <c r="W54">
+        <v>0.2149818606279912</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3324698404803025</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2101972392112461</v>
+      </c>
+      <c r="C55">
+        <v>2.294569318302337</v>
+      </c>
+      <c r="D55">
+        <v>13.90806931830234</v>
+      </c>
+      <c r="E55">
+        <v>11.2135</v>
+      </c>
+      <c r="F55">
+        <v>17.4635</v>
+      </c>
+      <c r="G55">
+        <v>5.85</v>
+      </c>
+      <c r="H55">
+        <v>26.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K55">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L55">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M55">
+        <v>4.170283800000001</v>
+      </c>
+      <c r="N55">
+        <v>-2.809950466666668</v>
+      </c>
+      <c r="O55">
+        <v>-0.8429851400000002</v>
+      </c>
+      <c r="P55">
+        <v>-1.966965326666668</v>
+      </c>
+      <c r="Q55">
+        <v>-1.833965326666668</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2042950461376399</v>
+      </c>
+      <c r="T55">
+        <v>1.063133371829129</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.09785904738665503</v>
+      </c>
+      <c r="W55">
+        <v>0.2154312594840668</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3261968246221835</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2121972392112461</v>
+      </c>
+      <c r="C56">
+        <v>1.804650739764778</v>
+      </c>
+      <c r="D56">
+        <v>13.74765073976478</v>
+      </c>
+      <c r="E56">
+        <v>11.543</v>
+      </c>
+      <c r="F56">
+        <v>17.793</v>
+      </c>
+      <c r="G56">
+        <v>5.85</v>
+      </c>
+      <c r="H56">
+        <v>26.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K56">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L56">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M56">
+        <v>4.248968400000001</v>
+      </c>
+      <c r="N56">
+        <v>-2.888635066666668</v>
+      </c>
+      <c r="O56">
+        <v>-0.8665905200000003</v>
+      </c>
+      <c r="P56">
+        <v>-2.022044546666667</v>
+      </c>
+      <c r="Q56">
+        <v>-1.889044546666667</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2078927645319364</v>
+      </c>
+      <c r="T56">
+        <v>1.086244966868893</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.09604684280542068</v>
+      </c>
+      <c r="W56">
+        <v>0.2158640139380656</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3201561426847357</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2141972392112462</v>
+      </c>
+      <c r="C57">
+        <v>1.318390567237692</v>
+      </c>
+      <c r="D57">
+        <v>13.59089056723769</v>
+      </c>
+      <c r="E57">
+        <v>11.8725</v>
+      </c>
+      <c r="F57">
+        <v>18.1225</v>
+      </c>
+      <c r="G57">
+        <v>5.85</v>
+      </c>
+      <c r="H57">
+        <v>26.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K57">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L57">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M57">
+        <v>4.327653000000001</v>
+      </c>
+      <c r="N57">
+        <v>-2.967319666666667</v>
+      </c>
+      <c r="O57">
+        <v>-0.8901959000000003</v>
+      </c>
+      <c r="P57">
+        <v>-2.077123766666667</v>
+      </c>
+      <c r="Q57">
+        <v>-1.944123766666667</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.211650381521535</v>
+      </c>
+      <c r="T57">
+        <v>1.110383743910424</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.09430053657259486</v>
+      </c>
+      <c r="W57">
+        <v>0.2162810318664644</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3143351219086495</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2161972392112461</v>
+      </c>
+      <c r="C58">
+        <v>0.8356650646575439</v>
+      </c>
+      <c r="D58">
+        <v>13.43766506465754</v>
+      </c>
+      <c r="E58">
+        <v>12.202</v>
+      </c>
+      <c r="F58">
+        <v>18.452</v>
+      </c>
+      <c r="G58">
+        <v>5.85</v>
+      </c>
+      <c r="H58">
+        <v>26.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K58">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L58">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M58">
+        <v>4.406337600000001</v>
+      </c>
+      <c r="N58">
+        <v>-3.046004266666667</v>
+      </c>
+      <c r="O58">
+        <v>-0.9138012800000002</v>
+      </c>
+      <c r="P58">
+        <v>-2.132202986666667</v>
+      </c>
+      <c r="Q58">
+        <v>-1.999202986666667</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.215578799283388</v>
+      </c>
+      <c r="T58">
+        <v>1.135619738090206</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.09261659841951282</v>
+      </c>
+      <c r="W58">
+        <v>0.2166831562974203</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3087219947317094</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2181972392112461</v>
+      </c>
+      <c r="C59">
+        <v>0.3563560138188642</v>
+      </c>
+      <c r="D59">
+        <v>13.28785601381887</v>
+      </c>
+      <c r="E59">
+        <v>12.5315</v>
+      </c>
+      <c r="F59">
+        <v>18.7815</v>
+      </c>
+      <c r="G59">
+        <v>5.85</v>
+      </c>
+      <c r="H59">
+        <v>26.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K59">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L59">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M59">
+        <v>4.485022200000001</v>
+      </c>
+      <c r="N59">
+        <v>-3.124688866666668</v>
+      </c>
+      <c r="O59">
+        <v>-0.9374066600000004</v>
+      </c>
+      <c r="P59">
+        <v>-2.187282206666668</v>
+      </c>
+      <c r="Q59">
+        <v>-2.054282206666667</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2196899341504436</v>
+      </c>
+      <c r="T59">
+        <v>1.162029499441141</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.0909917458156617</v>
+      </c>
+      <c r="W59">
+        <v>0.21707117109922</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.303305819385539</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2201972392112461</v>
+      </c>
+      <c r="C60">
+        <v>-0.1196495898121164</v>
+      </c>
+      <c r="D60">
+        <v>13.14135041018789</v>
+      </c>
+      <c r="E60">
+        <v>12.861</v>
+      </c>
+      <c r="F60">
+        <v>19.111</v>
+      </c>
+      <c r="G60">
+        <v>5.85</v>
+      </c>
+      <c r="H60">
+        <v>26.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K60">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L60">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M60">
+        <v>4.5637068</v>
+      </c>
+      <c r="N60">
+        <v>-3.203373466666667</v>
+      </c>
+      <c r="O60">
+        <v>-0.9610120400000001</v>
+      </c>
+      <c r="P60">
+        <v>-2.242361426666667</v>
+      </c>
+      <c r="Q60">
+        <v>-2.109361426666667</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2239968373445017</v>
+      </c>
+      <c r="T60">
+        <v>1.189696868475454</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.08942292261194341</v>
+      </c>
+      <c r="W60">
+        <v>0.2174458060802679</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.298076408706478</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2221972392112461</v>
+      </c>
+      <c r="C61">
+        <v>-0.592459821380551</v>
+      </c>
+      <c r="D61">
+        <v>12.99804017861945</v>
+      </c>
+      <c r="E61">
+        <v>13.1905</v>
+      </c>
+      <c r="F61">
+        <v>19.4405</v>
+      </c>
+      <c r="G61">
+        <v>5.85</v>
+      </c>
+      <c r="H61">
+        <v>26.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K61">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L61">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M61">
+        <v>4.6423914</v>
+      </c>
+      <c r="N61">
+        <v>-3.282058066666667</v>
+      </c>
+      <c r="O61">
+        <v>-0.9846174200000001</v>
+      </c>
+      <c r="P61">
+        <v>-2.297440646666667</v>
+      </c>
+      <c r="Q61">
+        <v>-2.164440646666667</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2285138333772944</v>
+      </c>
+      <c r="T61">
+        <v>1.218713865267538</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.08790727985580878</v>
+      </c>
+      <c r="W61">
+        <v>0.2178077415704329</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2930242661860293</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2241972392112461</v>
+      </c>
+      <c r="C62">
+        <v>-1.062178092525453</v>
+      </c>
+      <c r="D62">
+        <v>12.85782190747455</v>
+      </c>
+      <c r="E62">
+        <v>13.52</v>
+      </c>
+      <c r="F62">
+        <v>19.77</v>
+      </c>
+      <c r="G62">
+        <v>5.85</v>
+      </c>
+      <c r="H62">
+        <v>26.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K62">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L62">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M62">
+        <v>4.721076</v>
+      </c>
+      <c r="N62">
+        <v>-3.360742666666667</v>
+      </c>
+      <c r="O62">
+        <v>-1.0082228</v>
+      </c>
+      <c r="P62">
+        <v>-2.352519866666667</v>
+      </c>
+      <c r="Q62">
+        <v>-2.219519866666667</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2332566792117268</v>
+      </c>
+      <c r="T62">
+        <v>1.249181711899227</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.08644215852487865</v>
+      </c>
+      <c r="W62">
+        <v>0.218157612544259</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2881405284162621</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2261972392112461</v>
+      </c>
+      <c r="C63">
+        <v>-1.528903400236427</v>
+      </c>
+      <c r="D63">
+        <v>12.72059659976358</v>
+      </c>
+      <c r="E63">
+        <v>13.8495</v>
+      </c>
+      <c r="F63">
+        <v>20.0995</v>
+      </c>
+      <c r="G63">
+        <v>5.85</v>
+      </c>
+      <c r="H63">
+        <v>26.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K63">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L63">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M63">
+        <v>4.799760600000001</v>
+      </c>
+      <c r="N63">
+        <v>-3.439427266666668</v>
+      </c>
+      <c r="O63">
+        <v>-1.03182818</v>
+      </c>
+      <c r="P63">
+        <v>-2.407599086666667</v>
+      </c>
+      <c r="Q63">
+        <v>-2.274599086666667</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2382427479094634</v>
+      </c>
+      <c r="T63">
+        <v>1.281212012204335</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.085025073958897</v>
+      </c>
+      <c r="W63">
+        <v>0.2184960123386154</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2834169131963233</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2281972392112461</v>
+      </c>
+      <c r="C64">
+        <v>-1.992730559943073</v>
+      </c>
+      <c r="D64">
+        <v>12.58626944005693</v>
+      </c>
+      <c r="E64">
+        <v>14.179</v>
+      </c>
+      <c r="F64">
+        <v>20.429</v>
+      </c>
+      <c r="G64">
+        <v>5.85</v>
+      </c>
+      <c r="H64">
+        <v>26.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K64">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L64">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M64">
+        <v>4.878445200000001</v>
+      </c>
+      <c r="N64">
+        <v>-3.518111866666668</v>
+      </c>
+      <c r="O64">
+        <v>-1.05543356</v>
+      </c>
+      <c r="P64">
+        <v>-2.462678306666668</v>
+      </c>
+      <c r="Q64">
+        <v>-2.329678306666668</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2434912412755019</v>
+      </c>
+      <c r="T64">
+        <v>1.31492811778866</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.08365370179826964</v>
+      </c>
+      <c r="W64">
+        <v>0.2188234960105732</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2788456726608988</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2301972392112461</v>
+      </c>
+      <c r="C65">
+        <v>-2.453750423990488</v>
+      </c>
+      <c r="D65">
+        <v>12.45474957600951</v>
+      </c>
+      <c r="E65">
+        <v>14.5085</v>
+      </c>
+      <c r="F65">
+        <v>20.7585</v>
+      </c>
+      <c r="G65">
+        <v>5.85</v>
+      </c>
+      <c r="H65">
+        <v>26.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K65">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L65">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M65">
+        <v>4.957129800000001</v>
+      </c>
+      <c r="N65">
+        <v>-3.596796466666667</v>
+      </c>
+      <c r="O65">
+        <v>-1.07903894</v>
+      </c>
+      <c r="P65">
+        <v>-2.517757526666667</v>
+      </c>
+      <c r="Q65">
+        <v>-2.384757526666667</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2490234369856506</v>
+      </c>
+      <c r="T65">
+        <v>1.350466715566732</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.08232586526178917</v>
+      </c>
+      <c r="W65">
+        <v>0.2191405833754848</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2744195508726306</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2321972392112461</v>
+      </c>
+      <c r="C66">
+        <v>-2.912050086558629</v>
+      </c>
+      <c r="D66">
+        <v>12.32594991344137</v>
+      </c>
+      <c r="E66">
+        <v>14.838</v>
+      </c>
+      <c r="F66">
+        <v>21.088</v>
+      </c>
+      <c r="G66">
+        <v>5.85</v>
+      </c>
+      <c r="H66">
+        <v>26.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K66">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L66">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M66">
+        <v>5.0358144</v>
+      </c>
+      <c r="N66">
+        <v>-3.675481066666667</v>
+      </c>
+      <c r="O66">
+        <v>-1.10264432</v>
+      </c>
+      <c r="P66">
+        <v>-2.572836746666667</v>
+      </c>
+      <c r="Q66">
+        <v>-2.439836746666667</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2548629769019187</v>
+      </c>
+      <c r="T66">
+        <v>1.38797967988803</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.08103952361707371</v>
+      </c>
+      <c r="W66">
+        <v>0.2194477617602428</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2701317453902458</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2341972392112461</v>
+      </c>
+      <c r="C67">
+        <v>-3.367713075996942</v>
+      </c>
+      <c r="D67">
+        <v>12.19978692400306</v>
+      </c>
+      <c r="E67">
+        <v>15.1675</v>
+      </c>
+      <c r="F67">
+        <v>21.4175</v>
+      </c>
+      <c r="G67">
+        <v>5.85</v>
+      </c>
+      <c r="H67">
+        <v>26.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K67">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L67">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M67">
+        <v>5.114499000000001</v>
+      </c>
+      <c r="N67">
+        <v>-3.754165666666668</v>
+      </c>
+      <c r="O67">
+        <v>-1.1262497</v>
+      </c>
+      <c r="P67">
+        <v>-2.627915966666667</v>
+      </c>
+      <c r="Q67">
+        <v>-2.494915966666667</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2610362048134021</v>
+      </c>
+      <c r="T67">
+        <v>1.427636242170545</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.07979276171527257</v>
+      </c>
+      <c r="W67">
+        <v>0.2197454885023929</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2659758723842419</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2361972392112461</v>
+      </c>
+      <c r="C68">
+        <v>-3.820819535466693</v>
+      </c>
+      <c r="D68">
+        <v>12.07618046453331</v>
+      </c>
+      <c r="E68">
+        <v>15.497</v>
+      </c>
+      <c r="F68">
+        <v>21.747</v>
+      </c>
+      <c r="G68">
+        <v>5.85</v>
+      </c>
+      <c r="H68">
+        <v>26.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K68">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L68">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M68">
+        <v>5.193183600000001</v>
+      </c>
+      <c r="N68">
+        <v>-3.832850266666668</v>
+      </c>
+      <c r="O68">
+        <v>-1.14985508</v>
+      </c>
+      <c r="P68">
+        <v>-2.682995186666668</v>
+      </c>
+      <c r="Q68">
+        <v>-2.549995186666668</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2675725637785021</v>
+      </c>
+      <c r="T68">
+        <v>1.469625543410855</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.07858378047716238</v>
+      </c>
+      <c r="W68">
+        <v>0.2200341932220536</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2619459349238746</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2381972392112462</v>
+      </c>
+      <c r="C69">
+        <v>-4.271446392712093</v>
+      </c>
+      <c r="D69">
+        <v>11.95505360728791</v>
+      </c>
+      <c r="E69">
+        <v>15.8265</v>
+      </c>
+      <c r="F69">
+        <v>22.0765</v>
+      </c>
+      <c r="G69">
+        <v>5.85</v>
+      </c>
+      <c r="H69">
+        <v>26.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K69">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L69">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M69">
+        <v>5.271868200000001</v>
+      </c>
+      <c r="N69">
+        <v>-3.911534866666668</v>
+      </c>
+      <c r="O69">
+        <v>-1.17346046</v>
+      </c>
+      <c r="P69">
+        <v>-2.738074406666668</v>
+      </c>
+      <c r="Q69">
+        <v>-2.605074406666668</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2745050657111841</v>
+      </c>
+      <c r="T69">
+        <v>1.514159650786942</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.07741088823123458</v>
+      </c>
+      <c r="W69">
+        <v>0.2203142798903812</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2580362941041153</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2401972392112461</v>
+      </c>
+      <c r="C70">
+        <v>-4.719667519715703</v>
+      </c>
+      <c r="D70">
+        <v>11.8363324802843</v>
+      </c>
+      <c r="E70">
+        <v>16.156</v>
+      </c>
+      <c r="F70">
+        <v>22.406</v>
+      </c>
+      <c r="G70">
+        <v>5.85</v>
+      </c>
+      <c r="H70">
+        <v>26.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K70">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L70">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M70">
+        <v>5.350552800000001</v>
+      </c>
+      <c r="N70">
+        <v>-3.990219466666668</v>
+      </c>
+      <c r="O70">
+        <v>-1.19706584</v>
+      </c>
+      <c r="P70">
+        <v>-2.793153626666667</v>
+      </c>
+      <c r="Q70">
+        <v>-2.660153626666667</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2818708490146585</v>
+      </c>
+      <c r="T70">
+        <v>1.561477139874034</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.07627249281606938</v>
+      </c>
+      <c r="W70">
+        <v>0.2205861287155226</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2542416427202312</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2421972392112461</v>
+      </c>
+      <c r="C71">
+        <v>-5.165553882934642</v>
+      </c>
+      <c r="D71">
+        <v>11.71994611706536</v>
+      </c>
+      <c r="E71">
+        <v>16.48550000000001</v>
+      </c>
+      <c r="F71">
+        <v>22.73550000000001</v>
+      </c>
+      <c r="G71">
+        <v>5.85</v>
+      </c>
+      <c r="H71">
+        <v>26.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K71">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L71">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M71">
+        <v>5.429237400000002</v>
+      </c>
+      <c r="N71">
+        <v>-4.068904066666668</v>
+      </c>
+      <c r="O71">
+        <v>-1.220671220000001</v>
+      </c>
+      <c r="P71">
+        <v>-2.848232846666668</v>
+      </c>
+      <c r="Q71">
+        <v>-2.715232846666668</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2897118441441637</v>
+      </c>
+      <c r="T71">
+        <v>1.611847370192551</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.07516709436945966</v>
+      </c>
+      <c r="W71">
+        <v>0.220850097864573</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2505569812315322</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2441972392112461</v>
+      </c>
+      <c r="C72">
+        <v>-5.609173684759355</v>
+      </c>
+      <c r="D72">
+        <v>11.60582631524065</v>
+      </c>
+      <c r="E72">
+        <v>16.815</v>
+      </c>
+      <c r="F72">
+        <v>23.065</v>
+      </c>
+      <c r="G72">
+        <v>5.85</v>
+      </c>
+      <c r="H72">
+        <v>26.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K72">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L72">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M72">
+        <v>5.507922000000002</v>
+      </c>
+      <c r="N72">
+        <v>-4.147588666666668</v>
+      </c>
+      <c r="O72">
+        <v>-1.244276600000001</v>
+      </c>
+      <c r="P72">
+        <v>-2.903312066666668</v>
+      </c>
+      <c r="Q72">
+        <v>-2.770312066666668</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2980755722823025</v>
+      </c>
+      <c r="T72">
+        <v>1.665575615865636</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07409327873561024</v>
+      </c>
+      <c r="W72">
+        <v>0.2211065250379363</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2469775957853675</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2461972392112461</v>
+      </c>
+      <c r="C73">
+        <v>-6.050592496787697</v>
+      </c>
+      <c r="D73">
+        <v>11.4939075032123</v>
+      </c>
+      <c r="E73">
+        <v>17.1445</v>
+      </c>
+      <c r="F73">
+        <v>23.3945</v>
+      </c>
+      <c r="G73">
+        <v>5.85</v>
+      </c>
+      <c r="H73">
+        <v>26.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K73">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L73">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M73">
+        <v>5.586606600000001</v>
+      </c>
+      <c r="N73">
+        <v>-4.226273266666667</v>
+      </c>
+      <c r="O73">
+        <v>-1.26788198</v>
+      </c>
+      <c r="P73">
+        <v>-2.958391286666667</v>
+      </c>
+      <c r="Q73">
+        <v>-2.825391286666667</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3070161092575542</v>
+      </c>
+      <c r="T73">
+        <v>1.723009257792037</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07304971142947489</v>
+      </c>
+      <c r="W73">
+        <v>0.2213557289106414</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2434990380982497</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2481972392112461</v>
+      </c>
+      <c r="C74">
+        <v>-6.489873385461369</v>
+      </c>
+      <c r="D74">
+        <v>11.38412661453863</v>
+      </c>
+      <c r="E74">
+        <v>17.474</v>
+      </c>
+      <c r="F74">
+        <v>23.724</v>
+      </c>
+      <c r="G74">
+        <v>5.85</v>
+      </c>
+      <c r="H74">
+        <v>26.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K74">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L74">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M74">
+        <v>5.6652912</v>
+      </c>
+      <c r="N74">
+        <v>-4.304957866666667</v>
+      </c>
+      <c r="O74">
+        <v>-1.29148736</v>
+      </c>
+      <c r="P74">
+        <v>-3.013470506666667</v>
+      </c>
+      <c r="Q74">
+        <v>-2.880470506666667</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3165952560167526</v>
+      </c>
+      <c r="T74">
+        <v>1.784545302713181</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07203513210406552</v>
+      </c>
+      <c r="W74">
+        <v>0.2215980104535492</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2401171070135517</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2501972392112461</v>
+      </c>
+      <c r="C75">
+        <v>-6.927077030570594</v>
+      </c>
+      <c r="D75">
+        <v>11.27642296942941</v>
+      </c>
+      <c r="E75">
+        <v>17.8035</v>
+      </c>
+      <c r="F75">
+        <v>24.0535</v>
+      </c>
+      <c r="G75">
+        <v>5.85</v>
+      </c>
+      <c r="H75">
+        <v>26.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K75">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L75">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M75">
+        <v>5.743975800000001</v>
+      </c>
+      <c r="N75">
+        <v>-4.383642466666668</v>
+      </c>
+      <c r="O75">
+        <v>-1.31509274</v>
+      </c>
+      <c r="P75">
+        <v>-3.068549726666668</v>
+      </c>
+      <c r="Q75">
+        <v>-2.935549726666668</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3268839692025582</v>
+      </c>
+      <c r="T75">
+        <v>1.850639573184039</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.07104834947250298</v>
+      </c>
+      <c r="W75">
+        <v>0.2218336541459663</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.23682783157501</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2521972392112461</v>
+      </c>
+      <c r="C76">
+        <v>-7.362261837094891</v>
+      </c>
+      <c r="D76">
+        <v>11.17073816290511</v>
+      </c>
+      <c r="E76">
+        <v>18.133</v>
+      </c>
+      <c r="F76">
+        <v>24.383</v>
+      </c>
+      <c r="G76">
+        <v>5.85</v>
+      </c>
+      <c r="H76">
+        <v>26.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K76">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L76">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M76">
+        <v>5.822660400000001</v>
+      </c>
+      <c r="N76">
+        <v>-4.462327066666668</v>
+      </c>
+      <c r="O76">
+        <v>-1.33869812</v>
+      </c>
+      <c r="P76">
+        <v>-3.123628946666668</v>
+      </c>
+      <c r="Q76">
+        <v>-2.990628946666668</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3379641218641951</v>
+      </c>
+      <c r="T76">
+        <v>1.921818018306503</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.07008823664179348</v>
+      </c>
+      <c r="W76">
+        <v>0.2220629290899397</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.233627455472645</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2541972392112462</v>
+      </c>
+      <c r="C77">
+        <v>-7.795484040813104</v>
+      </c>
+      <c r="D77">
+        <v>11.0670159591869</v>
+      </c>
+      <c r="E77">
+        <v>18.4625</v>
+      </c>
+      <c r="F77">
+        <v>24.7125</v>
+      </c>
+      <c r="G77">
+        <v>5.85</v>
+      </c>
+      <c r="H77">
+        <v>26.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K77">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L77">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M77">
+        <v>5.901345000000001</v>
+      </c>
+      <c r="N77">
+        <v>-4.541011666666668</v>
+      </c>
+      <c r="O77">
+        <v>-1.3623035</v>
+      </c>
+      <c r="P77">
+        <v>-3.178708166666667</v>
+      </c>
+      <c r="Q77">
+        <v>-3.045708166666667</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3499306867387629</v>
+      </c>
+      <c r="T77">
+        <v>1.998690739038763</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.06915372681990289</v>
+      </c>
+      <c r="W77">
+        <v>0.2222860900354072</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2305124227330096</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2561972392112462</v>
+      </c>
+      <c r="C78">
+        <v>-8.22679780808393</v>
+      </c>
+      <c r="D78">
+        <v>10.96520219191607</v>
+      </c>
+      <c r="E78">
+        <v>18.792</v>
+      </c>
+      <c r="F78">
+        <v>25.042</v>
+      </c>
+      <c r="G78">
+        <v>5.85</v>
+      </c>
+      <c r="H78">
+        <v>26.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K78">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L78">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M78">
+        <v>5.980029600000001</v>
+      </c>
+      <c r="N78">
+        <v>-4.619696266666668</v>
+      </c>
+      <c r="O78">
+        <v>-1.38590888</v>
+      </c>
+      <c r="P78">
+        <v>-3.233787386666667</v>
+      </c>
+      <c r="Q78">
+        <v>-3.100787386666667</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3628944653528781</v>
+      </c>
+      <c r="T78">
+        <v>2.081969519832045</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.06824380936174629</v>
+      </c>
+      <c r="W78">
+        <v>0.222503378324415</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2274793645391543</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2581972392112462</v>
+      </c>
+      <c r="C79">
+        <v>-8.656255330168865</v>
+      </c>
+      <c r="D79">
+        <v>10.86524466983114</v>
+      </c>
+      <c r="E79">
+        <v>19.1215</v>
+      </c>
+      <c r="F79">
+        <v>25.3715</v>
+      </c>
+      <c r="G79">
+        <v>5.85</v>
+      </c>
+      <c r="H79">
+        <v>26.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K79">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L79">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M79">
+        <v>6.058714200000001</v>
+      </c>
+      <c r="N79">
+        <v>-4.698380866666668</v>
+      </c>
+      <c r="O79">
+        <v>-1.40951426</v>
+      </c>
+      <c r="P79">
+        <v>-3.288866606666668</v>
+      </c>
+      <c r="Q79">
+        <v>-3.155866606666668</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3769855290638728</v>
+      </c>
+      <c r="T79">
+        <v>2.172489933737786</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.06735752612328204</v>
+      </c>
+      <c r="W79">
+        <v>0.2227150227617603</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2245250870776069</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2601972392112461</v>
+      </c>
+      <c r="C80">
+        <v>-9.083906912442789</v>
+      </c>
+      <c r="D80">
+        <v>10.76709308755722</v>
+      </c>
+      <c r="E80">
+        <v>19.451</v>
+      </c>
+      <c r="F80">
+        <v>25.701</v>
+      </c>
+      <c r="G80">
+        <v>5.85</v>
+      </c>
+      <c r="H80">
+        <v>26.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K80">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L80">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M80">
+        <v>6.137398800000001</v>
+      </c>
+      <c r="N80">
+        <v>-4.777065466666668</v>
+      </c>
+      <c r="O80">
+        <v>-1.43311964</v>
+      </c>
+      <c r="P80">
+        <v>-3.343945826666668</v>
+      </c>
+      <c r="Q80">
+        <v>-3.210945826666668</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.392357598566776</v>
+      </c>
+      <c r="T80">
+        <v>2.271239476180412</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.06649396809606047</v>
+      </c>
+      <c r="W80">
+        <v>0.2229212404186608</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2216465603202016</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2621972392112462</v>
+      </c>
+      <c r="C81">
+        <v>-9.509801058812485</v>
+      </c>
+      <c r="D81">
+        <v>10.67069894118752</v>
+      </c>
+      <c r="E81">
+        <v>19.7805</v>
+      </c>
+      <c r="F81">
+        <v>26.0305</v>
+      </c>
+      <c r="G81">
+        <v>5.85</v>
+      </c>
+      <c r="H81">
+        <v>26.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K81">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L81">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M81">
+        <v>6.216083400000001</v>
+      </c>
+      <c r="N81">
+        <v>-4.855750066666668</v>
+      </c>
+      <c r="O81">
+        <v>-1.45672502</v>
+      </c>
+      <c r="P81">
+        <v>-3.399025046666668</v>
+      </c>
+      <c r="Q81">
+        <v>-3.266025046666668</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4091936746890036</v>
+      </c>
+      <c r="T81">
+        <v>2.379393736950909</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06565227229737616</v>
+      </c>
+      <c r="W81">
+        <v>0.2231222373753866</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2188409076579205</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2641972392112461</v>
+      </c>
+      <c r="C82">
+        <v>-9.933984551640776</v>
+      </c>
+      <c r="D82">
+        <v>10.57601544835923</v>
+      </c>
+      <c r="E82">
+        <v>20.11</v>
+      </c>
+      <c r="F82">
+        <v>26.36</v>
+      </c>
+      <c r="G82">
+        <v>5.85</v>
+      </c>
+      <c r="H82">
+        <v>26.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K82">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L82">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M82">
+        <v>6.294768000000001</v>
+      </c>
+      <c r="N82">
+        <v>-4.934434666666668</v>
+      </c>
+      <c r="O82">
+        <v>-1.4803304</v>
+      </c>
+      <c r="P82">
+        <v>-3.454104266666667</v>
+      </c>
+      <c r="Q82">
+        <v>-3.321104266666667</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4277133584234537</v>
+      </c>
+      <c r="T82">
+        <v>2.498363423798454</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06483161889365896</v>
+      </c>
+      <c r="W82">
+        <v>0.2233182094081942</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2161053963121966</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2661972392112462</v>
+      </c>
+      <c r="C83">
+        <v>-10.356502527453</v>
+      </c>
+      <c r="D83">
+        <v>10.482997472547</v>
+      </c>
+      <c r="E83">
+        <v>20.4395</v>
+      </c>
+      <c r="F83">
+        <v>26.6895</v>
+      </c>
+      <c r="G83">
+        <v>5.85</v>
+      </c>
+      <c r="H83">
+        <v>26.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K83">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L83">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M83">
+        <v>6.373452600000001</v>
+      </c>
+      <c r="N83">
+        <v>-5.013119266666668</v>
+      </c>
+      <c r="O83">
+        <v>-1.50393578</v>
+      </c>
+      <c r="P83">
+        <v>-3.509183486666668</v>
+      </c>
+      <c r="Q83">
+        <v>-3.376183486666668</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.448182482551004</v>
+      </c>
+      <c r="T83">
+        <v>2.629856235577321</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06403122853694714</v>
+      </c>
+      <c r="W83">
+        <v>0.2235093426253771</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2134374284564904</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2681972392112462</v>
+      </c>
+      <c r="C84">
+        <v>-10.77739854868318</v>
+      </c>
+      <c r="D84">
+        <v>10.39160145131683</v>
+      </c>
+      <c r="E84">
+        <v>20.76900000000001</v>
+      </c>
+      <c r="F84">
+        <v>27.01900000000001</v>
+      </c>
+      <c r="G84">
+        <v>5.85</v>
+      </c>
+      <c r="H84">
+        <v>26.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K84">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L84">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M84">
+        <v>6.452137200000002</v>
+      </c>
+      <c r="N84">
+        <v>-5.091803866666669</v>
+      </c>
+      <c r="O84">
+        <v>-1.527541160000001</v>
+      </c>
+      <c r="P84">
+        <v>-3.564262706666668</v>
+      </c>
+      <c r="Q84">
+        <v>-3.431262706666668</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4709259538038375</v>
+      </c>
+      <c r="T84">
+        <v>2.77595935977606</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06325035989625265</v>
+      </c>
+      <c r="W84">
+        <v>0.2236958140567749</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2108345329875089</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2701972392112462</v>
+      </c>
+      <c r="C85">
+        <v>-11.1967146716995</v>
+      </c>
+      <c r="D85">
+        <v>10.30178532830051</v>
+      </c>
+      <c r="E85">
+        <v>21.0985</v>
+      </c>
+      <c r="F85">
+        <v>27.3485</v>
+      </c>
+      <c r="G85">
+        <v>5.85</v>
+      </c>
+      <c r="H85">
+        <v>26.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K85">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L85">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M85">
+        <v>6.530821800000002</v>
+      </c>
+      <c r="N85">
+        <v>-5.170488466666669</v>
+      </c>
+      <c r="O85">
+        <v>-1.551146540000001</v>
+      </c>
+      <c r="P85">
+        <v>-3.619341926666668</v>
+      </c>
+      <c r="Q85">
+        <v>-3.486341926666668</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4963451275570045</v>
+      </c>
+      <c r="T85">
+        <v>2.939251086821711</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06248830736738212</v>
+      </c>
+      <c r="W85">
+        <v>0.2238777922006692</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2082943578912738</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2721972392112462</v>
+      </c>
+      <c r="C86">
+        <v>-11.61449151133234</v>
+      </c>
+      <c r="D86">
+        <v>10.21350848866766</v>
+      </c>
+      <c r="E86">
+        <v>21.428</v>
+      </c>
+      <c r="F86">
+        <v>27.678</v>
+      </c>
+      <c r="G86">
+        <v>5.85</v>
+      </c>
+      <c r="H86">
+        <v>26.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K86">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L86">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M86">
+        <v>6.609506400000001</v>
+      </c>
+      <c r="N86">
+        <v>-5.249173066666668</v>
+      </c>
+      <c r="O86">
+        <v>-1.57475192</v>
+      </c>
+      <c r="P86">
+        <v>-3.674421146666667</v>
+      </c>
+      <c r="Q86">
+        <v>-3.541421146666667</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.524941698029317</v>
+      </c>
+      <c r="T86">
+        <v>3.122954279748066</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06174439894634187</v>
+      </c>
+      <c r="W86">
+        <v>0.2240554375316136</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2058146631544729</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2741972392112462</v>
+      </c>
+      <c r="C87">
+        <v>-12.03076830211281</v>
+      </c>
+      <c r="D87">
+        <v>10.12673169788719</v>
+      </c>
+      <c r="E87">
+        <v>21.7575</v>
+      </c>
+      <c r="F87">
+        <v>28.0075</v>
+      </c>
+      <c r="G87">
+        <v>5.85</v>
+      </c>
+      <c r="H87">
+        <v>26.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K87">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L87">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M87">
+        <v>6.688191000000001</v>
+      </c>
+      <c r="N87">
+        <v>-5.327857666666667</v>
+      </c>
+      <c r="O87">
+        <v>-1.5983573</v>
+      </c>
+      <c r="P87">
+        <v>-3.729500366666668</v>
+      </c>
+      <c r="Q87">
+        <v>-3.596500366666668</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5573511445646049</v>
+      </c>
+      <c r="T87">
+        <v>3.331151231731271</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0610179942528555</v>
+      </c>
+      <c r="W87">
+        <v>0.2242289029724181</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.203393314176185</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2761972392112461</v>
+      </c>
+      <c r="C88">
+        <v>-12.44558295641573</v>
+      </c>
+      <c r="D88">
+        <v>10.04141704358427</v>
+      </c>
+      <c r="E88">
+        <v>22.087</v>
+      </c>
+      <c r="F88">
+        <v>28.337</v>
+      </c>
+      <c r="G88">
+        <v>5.85</v>
+      </c>
+      <c r="H88">
+        <v>26.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K88">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L88">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M88">
+        <v>6.766875600000001</v>
+      </c>
+      <c r="N88">
+        <v>-5.406542266666668</v>
+      </c>
+      <c r="O88">
+        <v>-1.62196268</v>
+      </c>
+      <c r="P88">
+        <v>-3.784579586666668</v>
+      </c>
+      <c r="Q88">
+        <v>-3.651579586666668</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5943905120335051</v>
+      </c>
+      <c r="T88">
+        <v>3.569090605426362</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06030848269177578</v>
+      </c>
+      <c r="W88">
+        <v>0.2243983343332039</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2010282756392526</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2781972392112461</v>
+      </c>
+      <c r="C89">
+        <v>-12.85897211968819</v>
+      </c>
+      <c r="D89">
+        <v>9.957527880311812</v>
+      </c>
+      <c r="E89">
+        <v>22.4165</v>
+      </c>
+      <c r="F89">
+        <v>28.6665</v>
+      </c>
+      <c r="G89">
+        <v>5.85</v>
+      </c>
+      <c r="H89">
+        <v>26.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K89">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L89">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M89">
+        <v>6.845560200000001</v>
+      </c>
+      <c r="N89">
+        <v>-5.485226866666668</v>
+      </c>
+      <c r="O89">
+        <v>-1.64556806</v>
+      </c>
+      <c r="P89">
+        <v>-3.839658806666668</v>
+      </c>
+      <c r="Q89">
+        <v>-3.706658806666668</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6371282437283903</v>
+      </c>
+      <c r="T89">
+        <v>3.843636036613006</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.0596152817412956</v>
+      </c>
+      <c r="W89">
+        <v>0.2245638707201786</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1987176058043186</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2801972392112462</v>
+      </c>
+      <c r="C90">
+        <v>-13.27097122293269</v>
+      </c>
+      <c r="D90">
+        <v>9.875028777067318</v>
+      </c>
+      <c r="E90">
+        <v>22.746</v>
+      </c>
+      <c r="F90">
+        <v>28.996</v>
+      </c>
+      <c r="G90">
+        <v>5.85</v>
+      </c>
+      <c r="H90">
+        <v>26.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K90">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L90">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M90">
+        <v>6.924244800000001</v>
+      </c>
+      <c r="N90">
+        <v>-5.563911466666668</v>
+      </c>
+      <c r="O90">
+        <v>-1.66917344</v>
+      </c>
+      <c r="P90">
+        <v>-3.894738026666667</v>
+      </c>
+      <c r="Q90">
+        <v>-3.761738026666667</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6869889307057562</v>
+      </c>
+      <c r="T90">
+        <v>4.16393903966409</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.05893783535787179</v>
+      </c>
+      <c r="W90">
+        <v>0.2247256449165402</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.196459451192906</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2821972392112461</v>
+      </c>
+      <c r="C91">
+        <v>-13.68161453260265</v>
+      </c>
+      <c r="D91">
+        <v>9.793885467397349</v>
+      </c>
+      <c r="E91">
+        <v>23.0755</v>
+      </c>
+      <c r="F91">
+        <v>29.3255</v>
+      </c>
+      <c r="G91">
+        <v>5.85</v>
+      </c>
+      <c r="H91">
+        <v>26.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K91">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L91">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M91">
+        <v>7.002929400000001</v>
+      </c>
+      <c r="N91">
+        <v>-5.642596066666668</v>
+      </c>
+      <c r="O91">
+        <v>-1.69277882</v>
+      </c>
+      <c r="P91">
+        <v>-3.949817246666668</v>
+      </c>
+      <c r="Q91">
+        <v>-3.816817246666668</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.745915197133552</v>
+      </c>
+      <c r="T91">
+        <v>4.542478952360825</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.05827561248868222</v>
+      </c>
+      <c r="W91">
+        <v>0.2248837837377027</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1942520416289407</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2841972392112462</v>
+      </c>
+      <c r="C92">
+        <v>-14.0909351980582</v>
+      </c>
+      <c r="D92">
+        <v>9.714064801941801</v>
+      </c>
+      <c r="E92">
+        <v>23.405</v>
+      </c>
+      <c r="F92">
+        <v>29.655</v>
+      </c>
+      <c r="G92">
+        <v>5.85</v>
+      </c>
+      <c r="H92">
+        <v>26.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K92">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L92">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M92">
+        <v>7.081614000000002</v>
+      </c>
+      <c r="N92">
+        <v>-5.721280666666669</v>
+      </c>
+      <c r="O92">
+        <v>-1.7163842</v>
+      </c>
+      <c r="P92">
+        <v>-4.004896466666668</v>
+      </c>
+      <c r="Q92">
+        <v>-3.871896466666668</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8166267168469077</v>
+      </c>
+      <c r="T92">
+        <v>4.996726847596909</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0576281056832524</v>
+      </c>
+      <c r="W92">
+        <v>0.2250384083628393</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1920936856108414</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2861972392112461</v>
+      </c>
+      <c r="C93">
+        <v>-14.49896529671987</v>
+      </c>
+      <c r="D93">
+        <v>9.635534703280136</v>
+      </c>
+      <c r="E93">
+        <v>23.7345</v>
+      </c>
+      <c r="F93">
+        <v>29.9845</v>
+      </c>
+      <c r="G93">
+        <v>5.85</v>
+      </c>
+      <c r="H93">
+        <v>26.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K93">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L93">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M93">
+        <v>7.160298600000002</v>
+      </c>
+      <c r="N93">
+        <v>-5.799965266666669</v>
+      </c>
+      <c r="O93">
+        <v>-1.73998958</v>
+      </c>
+      <c r="P93">
+        <v>-4.059975686666668</v>
+      </c>
+      <c r="Q93">
+        <v>-3.926975686666668</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9030519076076751</v>
+      </c>
+      <c r="T93">
+        <v>5.551918719552121</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.05699482979662326</v>
+      </c>
+      <c r="W93">
+        <v>0.2251896346445664</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1899827659887442</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2881972392112462</v>
+      </c>
+      <c r="C94">
+        <v>-14.9057358770499</v>
+      </c>
+      <c r="D94">
+        <v>9.558264122950105</v>
+      </c>
+      <c r="E94">
+        <v>24.064</v>
+      </c>
+      <c r="F94">
+        <v>30.314</v>
+      </c>
+      <c r="G94">
+        <v>5.85</v>
+      </c>
+      <c r="H94">
+        <v>26.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K94">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L94">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M94">
+        <v>7.238983200000002</v>
+      </c>
+      <c r="N94">
+        <v>-5.878649866666668</v>
+      </c>
+      <c r="O94">
+        <v>-1.76359496</v>
+      </c>
+      <c r="P94">
+        <v>-4.115054906666668</v>
+      </c>
+      <c r="Q94">
+        <v>-3.982054906666668</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.011083396058635</v>
+      </c>
+      <c r="T94">
+        <v>6.245908559496137</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05637532077709476</v>
+      </c>
+      <c r="W94">
+        <v>0.2253375733984298</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1879177359236491</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2901972392112461</v>
+      </c>
+      <c r="C95">
+        <v>-15.31127699948178</v>
+      </c>
+      <c r="D95">
+        <v>9.482223000518221</v>
+      </c>
+      <c r="E95">
+        <v>24.3935</v>
+      </c>
+      <c r="F95">
+        <v>30.6435</v>
+      </c>
+      <c r="G95">
+        <v>5.85</v>
+      </c>
+      <c r="H95">
+        <v>26.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K95">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L95">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M95">
+        <v>7.317667800000001</v>
+      </c>
+      <c r="N95">
+        <v>-5.957334466666668</v>
+      </c>
+      <c r="O95">
+        <v>-1.78720034</v>
+      </c>
+      <c r="P95">
+        <v>-4.170134126666667</v>
+      </c>
+      <c r="Q95">
+        <v>-4.037134126666667</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.149981024067011</v>
+      </c>
+      <c r="T95">
+        <v>7.138181210852729</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05576913453217976</v>
+      </c>
+      <c r="W95">
+        <v>0.2254823306737155</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1858971151072658</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2921972392112461</v>
+      </c>
+      <c r="C96">
+        <v>-15.71561777541158</v>
+      </c>
+      <c r="D96">
+        <v>9.40738222458843</v>
+      </c>
+      <c r="E96">
+        <v>24.72300000000001</v>
+      </c>
+      <c r="F96">
+        <v>30.97300000000001</v>
+      </c>
+      <c r="G96">
+        <v>5.85</v>
+      </c>
+      <c r="H96">
+        <v>26.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K96">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L96">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M96">
+        <v>7.396352400000002</v>
+      </c>
+      <c r="N96">
+        <v>-6.036019066666669</v>
+      </c>
+      <c r="O96">
+        <v>-1.810805720000001</v>
+      </c>
+      <c r="P96">
+        <v>-4.225213346666669</v>
+      </c>
+      <c r="Q96">
+        <v>-4.092213346666669</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.335177861411514</v>
+      </c>
+      <c r="T96">
+        <v>8.327878079328187</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0551758458669438</v>
+      </c>
+      <c r="W96">
+        <v>0.2256240080069738</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.183919486223146</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2941972392112461</v>
+      </c>
+      <c r="C97">
+        <v>-16.11878640435715</v>
+      </c>
+      <c r="D97">
+        <v>9.333713595642857</v>
+      </c>
+      <c r="E97">
+        <v>25.05250000000001</v>
+      </c>
+      <c r="F97">
+        <v>31.30250000000001</v>
+      </c>
+      <c r="G97">
+        <v>5.85</v>
+      </c>
+      <c r="H97">
+        <v>26.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K97">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L97">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M97">
+        <v>7.475037000000001</v>
+      </c>
+      <c r="N97">
+        <v>-6.114703666666668</v>
+      </c>
+      <c r="O97">
+        <v>-1.8344111</v>
+      </c>
+      <c r="P97">
+        <v>-4.280292566666668</v>
+      </c>
+      <c r="Q97">
+        <v>-4.147292566666668</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.594453433693817</v>
+      </c>
+      <c r="T97">
+        <v>9.993453695193828</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05459504748939703</v>
+      </c>
+      <c r="W97">
+        <v>0.225762702659532</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1819834916313234</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2961972392112461</v>
+      </c>
+      <c r="C98">
+        <v>-16.52081020938508</v>
+      </c>
+      <c r="D98">
+        <v>9.261189790614921</v>
+      </c>
+      <c r="E98">
+        <v>25.382</v>
+      </c>
+      <c r="F98">
+        <v>31.632</v>
+      </c>
+      <c r="G98">
+        <v>5.85</v>
+      </c>
+      <c r="H98">
+        <v>26.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K98">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L98">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M98">
+        <v>7.553721600000001</v>
+      </c>
+      <c r="N98">
+        <v>-6.193388266666668</v>
+      </c>
+      <c r="O98">
+        <v>-1.85801648</v>
+      </c>
+      <c r="P98">
+        <v>-4.335371786666668</v>
+      </c>
+      <c r="Q98">
+        <v>-4.202371786666668</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.983366792117267</v>
+      </c>
+      <c r="T98">
+        <v>12.49181711899226</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05402634907804914</v>
+      </c>
+      <c r="W98">
+        <v>0.2258985078401619</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1800878302601638</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2981972392112461</v>
+      </c>
+      <c r="C99">
+        <v>-16.92171567089867</v>
+      </c>
+      <c r="D99">
+        <v>9.189784329101332</v>
+      </c>
+      <c r="E99">
+        <v>25.7115</v>
+      </c>
+      <c r="F99">
+        <v>31.9615</v>
+      </c>
+      <c r="G99">
+        <v>5.85</v>
+      </c>
+      <c r="H99">
+        <v>26.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K99">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L99">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M99">
+        <v>7.632406200000001</v>
+      </c>
+      <c r="N99">
+        <v>-6.272072866666668</v>
+      </c>
+      <c r="O99">
+        <v>-1.88162186</v>
+      </c>
+      <c r="P99">
+        <v>-4.390451006666668</v>
+      </c>
+      <c r="Q99">
+        <v>-4.257451006666668</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.631555722823023</v>
+      </c>
+      <c r="T99">
+        <v>16.65575615865635</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05346937640714142</v>
+      </c>
+      <c r="W99">
+        <v>0.2260315129139746</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1782312546904714</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3001972392112462</v>
+      </c>
+      <c r="C100">
+        <v>-17.32152845887479</v>
+      </c>
+      <c r="D100">
+        <v>9.119471541125211</v>
+      </c>
+      <c r="E100">
+        <v>26.041</v>
+      </c>
+      <c r="F100">
+        <v>32.291</v>
+      </c>
+      <c r="G100">
+        <v>5.85</v>
+      </c>
+      <c r="H100">
+        <v>26.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K100">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L100">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M100">
+        <v>7.711090800000001</v>
+      </c>
+      <c r="N100">
+        <v>-6.350757466666668</v>
+      </c>
+      <c r="O100">
+        <v>-1.90522724</v>
+      </c>
+      <c r="P100">
+        <v>-4.445530226666667</v>
+      </c>
+      <c r="Q100">
+        <v>-4.312530226666667</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.927933584234534</v>
+      </c>
+      <c r="T100">
+        <v>24.98363423798452</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05292377052543589</v>
+      </c>
+      <c r="W100">
+        <v>0.2261618035985259</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1764125684181197</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3021972392112462</v>
+      </c>
+      <c r="C101">
+        <v>-17.72027346363212</v>
+      </c>
+      <c r="D101">
+        <v>9.050226536367882</v>
+      </c>
+      <c r="E101">
+        <v>26.3705</v>
+      </c>
+      <c r="F101">
+        <v>32.6205</v>
+      </c>
+      <c r="G101">
+        <v>5.85</v>
+      </c>
+      <c r="H101">
+        <v>26.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.493333333333333</v>
+      </c>
+      <c r="K101">
+        <v>0.1330000000000001</v>
+      </c>
+      <c r="L101">
+        <v>1.360333333333333</v>
+      </c>
+      <c r="M101">
+        <v>7.789775400000001</v>
+      </c>
+      <c r="N101">
+        <v>-6.429442066666668</v>
+      </c>
+      <c r="O101">
+        <v>-1.92883262</v>
+      </c>
+      <c r="P101">
+        <v>-4.500609446666667</v>
+      </c>
+      <c r="Q101">
+        <v>-4.367609446666667</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.817067168469068</v>
+      </c>
+      <c r="T101">
+        <v>49.96726847596904</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05238918698477493</v>
+      </c>
+      <c r="W101">
+        <v>0.2262894621480358</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1746306232825831</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/nigeria/nigeria_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_real_estate_general_diversified.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1213841303367995</v>
+        <v>0.121051477945789</v>
       </c>
       <c r="C2">
-        <v>21.97673928809369</v>
+        <v>21.84531220559723</v>
       </c>
       <c r="D2">
-        <v>18.65673928809369</v>
+        <v>18.73921220559723</v>
       </c>
       <c r="E2">
-        <v>-2.19</v>
+        <v>-1.9761</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2139</v>
       </c>
       <c r="G2">
         <v>3.32</v>
@@ -1439,28 +1439,28 @@
         <v>0.7025</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01075917</v>
       </c>
       <c r="N2">
-        <v>0.7025</v>
+        <v>0.69174083</v>
       </c>
       <c r="O2">
-        <v>0.21075</v>
+        <v>0.207522249</v>
       </c>
       <c r="P2">
-        <v>0.49175</v>
+        <v>0.484218581</v>
       </c>
       <c r="Q2">
-        <v>0.61175</v>
+        <v>0.604218581</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1213841303367995</v>
+        <v>0.1219185635816051</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5307323119301448</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>65.29314064188966</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.121051477945789</v>
+        <v>0.1207188255547786</v>
       </c>
       <c r="C3">
-        <v>21.84531220559723</v>
+        <v>21.71461751080166</v>
       </c>
       <c r="D3">
-        <v>18.73921220559723</v>
+        <v>18.82241751080166</v>
       </c>
       <c r="E3">
-        <v>-1.9761</v>
+        <v>-1.7622</v>
       </c>
       <c r="F3">
-        <v>0.2139</v>
+        <v>0.4278</v>
       </c>
       <c r="G3">
         <v>3.32</v>
@@ -1521,28 +1521,28 @@
         <v>0.7025</v>
       </c>
       <c r="M3">
-        <v>0.01075917</v>
+        <v>0.02151834</v>
       </c>
       <c r="N3">
-        <v>0.69174083</v>
+        <v>0.68098166</v>
       </c>
       <c r="O3">
-        <v>0.207522249</v>
+        <v>0.204294498</v>
       </c>
       <c r="P3">
-        <v>0.484218581</v>
+        <v>0.4766871620000001</v>
       </c>
       <c r="Q3">
-        <v>0.604218581</v>
+        <v>0.596687162</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1219185635816051</v>
+        <v>0.1224639036273251</v>
       </c>
       <c r="T3">
-        <v>0.5307323119301448</v>
+        <v>0.534534664071785</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>65.29314064188966</v>
+        <v>32.64657032094483</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1207188255547786</v>
+        <v>0.1203861731637683</v>
       </c>
       <c r="C4">
-        <v>21.71461751080166</v>
+        <v>21.58466500299725</v>
       </c>
       <c r="D4">
-        <v>18.82241751080166</v>
+        <v>18.90636500299725</v>
       </c>
       <c r="E4">
-        <v>-1.7622</v>
+        <v>-1.5483</v>
       </c>
       <c r="F4">
-        <v>0.4278</v>
+        <v>0.6417</v>
       </c>
       <c r="G4">
         <v>3.32</v>
@@ -1603,28 +1603,28 @@
         <v>0.7025</v>
       </c>
       <c r="M4">
-        <v>0.02151834</v>
+        <v>0.03227751</v>
       </c>
       <c r="N4">
-        <v>0.68098166</v>
+        <v>0.67022249</v>
       </c>
       <c r="O4">
-        <v>0.204294498</v>
+        <v>0.201066747</v>
       </c>
       <c r="P4">
-        <v>0.4766871620000001</v>
+        <v>0.469155743</v>
       </c>
       <c r="Q4">
-        <v>0.596687162</v>
+        <v>0.5891557430000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1224639036273251</v>
+        <v>0.1230204877976993</v>
       </c>
       <c r="T4">
-        <v>0.534534664071785</v>
+        <v>0.5384154152266549</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>32.64657032094483</v>
+        <v>21.76438021396322</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1203861731637683</v>
+        <v>0.1200535207727579</v>
       </c>
       <c r="C5">
-        <v>21.58466500299725</v>
+        <v>21.45546465707573</v>
       </c>
       <c r="D5">
-        <v>18.90636500299725</v>
+        <v>18.99106465707573</v>
       </c>
       <c r="E5">
-        <v>-1.5483</v>
+        <v>-1.3344</v>
       </c>
       <c r="F5">
-        <v>0.6417</v>
+        <v>0.8556</v>
       </c>
       <c r="G5">
         <v>3.32</v>
@@ -1685,28 +1685,28 @@
         <v>0.7025</v>
       </c>
       <c r="M5">
-        <v>0.03227751</v>
+        <v>0.04303668</v>
       </c>
       <c r="N5">
-        <v>0.67022249</v>
+        <v>0.65946332</v>
       </c>
       <c r="O5">
-        <v>0.201066747</v>
+        <v>0.197838996</v>
       </c>
       <c r="P5">
-        <v>0.469155743</v>
+        <v>0.461624324</v>
       </c>
       <c r="Q5">
-        <v>0.5891557430000001</v>
+        <v>0.581624324</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1230204877976993</v>
+        <v>0.1235886674716228</v>
       </c>
       <c r="T5">
-        <v>0.5384154152266549</v>
+        <v>0.542377015363918</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>21.76438021396322</v>
+        <v>16.32328516047242</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1200535207727579</v>
+        <v>0.1197208683817475</v>
       </c>
       <c r="C6">
-        <v>21.45546465707573</v>
+        <v>21.32702662748149</v>
       </c>
       <c r="D6">
-        <v>18.99106465707573</v>
+        <v>19.0765266274815</v>
       </c>
       <c r="E6">
-        <v>-1.3344</v>
+        <v>-1.1205</v>
       </c>
       <c r="F6">
-        <v>0.8556</v>
+        <v>1.0695</v>
       </c>
       <c r="G6">
         <v>3.32</v>
@@ -1767,28 +1767,28 @@
         <v>0.7025</v>
       </c>
       <c r="M6">
-        <v>0.04303668</v>
+        <v>0.05379585000000001</v>
       </c>
       <c r="N6">
-        <v>0.65946332</v>
+        <v>0.64870415</v>
       </c>
       <c r="O6">
-        <v>0.197838996</v>
+        <v>0.194611245</v>
       </c>
       <c r="P6">
-        <v>0.461624324</v>
+        <v>0.454092905</v>
       </c>
       <c r="Q6">
-        <v>0.581624324</v>
+        <v>0.574092905</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1235886674716228</v>
+        <v>0.1241688088228921</v>
       </c>
       <c r="T6">
-        <v>0.542377015363918</v>
+        <v>0.546422017609334</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.32328516047242</v>
+        <v>13.05862812837793</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1197208683817475</v>
+        <v>0.1194512159907371</v>
       </c>
       <c r="C7">
-        <v>21.32702662748149</v>
+        <v>21.18296975156408</v>
       </c>
       <c r="D7">
-        <v>19.0765266274815</v>
+        <v>19.14636975156408</v>
       </c>
       <c r="E7">
-        <v>-1.1205</v>
+        <v>-0.9065999999999999</v>
       </c>
       <c r="F7">
-        <v>1.0695</v>
+        <v>1.2834</v>
       </c>
       <c r="G7">
         <v>3.32</v>
@@ -1849,45 +1849,45 @@
         <v>0.7025</v>
       </c>
       <c r="M7">
-        <v>0.05379585000000001</v>
+        <v>0.06648012</v>
       </c>
       <c r="N7">
-        <v>0.64870415</v>
+        <v>0.63601988</v>
       </c>
       <c r="O7">
-        <v>0.194611245</v>
+        <v>0.190805964</v>
       </c>
       <c r="P7">
-        <v>0.454092905</v>
+        <v>0.445213916</v>
       </c>
       <c r="Q7">
-        <v>0.574092905</v>
+        <v>0.565213916</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1241688088228921</v>
+        <v>0.1247612936071671</v>
       </c>
       <c r="T7">
-        <v>0.546422017609334</v>
+        <v>0.5505530837323119</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.05862812837793</v>
+        <v>10.56706877183735</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1194512159907371</v>
+        <v>0.1192123635997267</v>
       </c>
       <c r="C8">
-        <v>21.18296975156408</v>
+        <v>21.03136383896419</v>
       </c>
       <c r="D8">
-        <v>19.14636975156408</v>
+        <v>19.20866383896418</v>
       </c>
       <c r="E8">
-        <v>-0.9065999999999999</v>
+        <v>-0.6927000000000001</v>
       </c>
       <c r="F8">
-        <v>1.2834</v>
+        <v>1.4973</v>
       </c>
       <c r="G8">
         <v>3.32</v>
@@ -1931,45 +1931,45 @@
         <v>0.7025</v>
       </c>
       <c r="M8">
-        <v>0.06648012</v>
+        <v>0.08010554999999998</v>
       </c>
       <c r="N8">
-        <v>0.63601988</v>
+        <v>0.62239445</v>
       </c>
       <c r="O8">
-        <v>0.190805964</v>
+        <v>0.186718335</v>
       </c>
       <c r="P8">
-        <v>0.445213916</v>
+        <v>0.435676115</v>
       </c>
       <c r="Q8">
-        <v>0.565213916</v>
+        <v>0.555676115</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1247612936071671</v>
+        <v>0.1253665199997061</v>
       </c>
       <c r="T8">
-        <v>0.5505530837323119</v>
+        <v>0.554772989986967</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.56706877183735</v>
+        <v>8.769679504104275</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1192123635997267</v>
+        <v>0.1189021112087163</v>
       </c>
       <c r="C9">
-        <v>21.03136383896419</v>
+        <v>20.89898725580694</v>
       </c>
       <c r="D9">
-        <v>19.20866383896419</v>
+        <v>19.29018725580694</v>
       </c>
       <c r="E9">
-        <v>-0.6926999999999999</v>
+        <v>-0.4787999999999999</v>
       </c>
       <c r="F9">
-        <v>1.4973</v>
+        <v>1.7112</v>
       </c>
       <c r="G9">
         <v>3.32</v>
@@ -2013,28 +2013,28 @@
         <v>0.7025</v>
       </c>
       <c r="M9">
-        <v>0.08010555</v>
+        <v>0.0915492</v>
       </c>
       <c r="N9">
-        <v>0.62239445</v>
+        <v>0.6109508</v>
       </c>
       <c r="O9">
-        <v>0.186718335</v>
+        <v>0.18328524</v>
       </c>
       <c r="P9">
-        <v>0.435676115</v>
+        <v>0.42766556</v>
       </c>
       <c r="Q9">
-        <v>0.555676115</v>
+        <v>0.54766556</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1253665199997061</v>
+        <v>0.1259849034877351</v>
       </c>
       <c r="T9">
-        <v>0.554772989986967</v>
+        <v>0.5590846333341145</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.769679504104273</v>
+        <v>7.673469566091239</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1189021112087163</v>
+        <v>0.1186422588177059</v>
       </c>
       <c r="C10">
-        <v>20.89898725580694</v>
+        <v>20.75390172371085</v>
       </c>
       <c r="D10">
-        <v>19.29018725580694</v>
+        <v>19.35900172371085</v>
       </c>
       <c r="E10">
-        <v>-0.4787999999999999</v>
+        <v>-0.2648999999999999</v>
       </c>
       <c r="F10">
-        <v>1.7112</v>
+        <v>1.9251</v>
       </c>
       <c r="G10">
         <v>3.32</v>
@@ -2095,45 +2095,45 @@
         <v>0.7025</v>
       </c>
       <c r="M10">
-        <v>0.0915492</v>
+        <v>0.10453293</v>
       </c>
       <c r="N10">
-        <v>0.6109508</v>
+        <v>0.59796707</v>
       </c>
       <c r="O10">
-        <v>0.18328524</v>
+        <v>0.179390121</v>
       </c>
       <c r="P10">
-        <v>0.42766556</v>
+        <v>0.418576949</v>
       </c>
       <c r="Q10">
-        <v>0.54766556</v>
+        <v>0.5385769490000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1259849034877351</v>
+        <v>0.1266168778216548</v>
       </c>
       <c r="T10">
-        <v>0.5590846333341145</v>
+        <v>0.5634910380735069</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>7.673469566091239</v>
+        <v>6.720370317755371</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1186422588177059</v>
+        <v>0.1184076064266955</v>
       </c>
       <c r="C11">
-        <v>20.75390172371085</v>
+        <v>20.60256591313404</v>
       </c>
       <c r="D11">
-        <v>19.35900172371085</v>
+        <v>19.42156591313404</v>
       </c>
       <c r="E11">
-        <v>-0.2648999999999999</v>
+        <v>-0.05100000000000016</v>
       </c>
       <c r="F11">
-        <v>1.9251</v>
+        <v>2.139</v>
       </c>
       <c r="G11">
         <v>3.32</v>
@@ -2177,45 +2177,45 @@
         <v>0.7025</v>
       </c>
       <c r="M11">
-        <v>0.10453293</v>
+        <v>0.1182867</v>
       </c>
       <c r="N11">
-        <v>0.59796707</v>
+        <v>0.5842133</v>
       </c>
       <c r="O11">
-        <v>0.179390121</v>
+        <v>0.17526399</v>
       </c>
       <c r="P11">
-        <v>0.418576949</v>
+        <v>0.40894931</v>
       </c>
       <c r="Q11">
-        <v>0.5385769490000001</v>
+        <v>0.52894931</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1266168778216548</v>
+        <v>0.1272628960296616</v>
       </c>
       <c r="T11">
-        <v>0.5634910380735069</v>
+        <v>0.5679953629182192</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.720370317755371</v>
+        <v>5.938960170500995</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1184076064266955</v>
+        <v>0.1181099540356851</v>
       </c>
       <c r="C12">
-        <v>20.60256591313404</v>
+        <v>20.46861169111582</v>
       </c>
       <c r="D12">
-        <v>19.42156591313404</v>
+        <v>19.50151169111582</v>
       </c>
       <c r="E12">
-        <v>-0.05099999999999971</v>
+        <v>0.1629</v>
       </c>
       <c r="F12">
-        <v>2.139</v>
+        <v>2.3529</v>
       </c>
       <c r="G12">
         <v>3.32</v>
@@ -2259,28 +2259,28 @@
         <v>0.7025</v>
       </c>
       <c r="M12">
-        <v>0.1182867</v>
+        <v>0.13011537</v>
       </c>
       <c r="N12">
-        <v>0.5842133</v>
+        <v>0.5723846299999999</v>
       </c>
       <c r="O12">
-        <v>0.17526399</v>
+        <v>0.171715389</v>
       </c>
       <c r="P12">
-        <v>0.40894931</v>
+        <v>0.400669241</v>
       </c>
       <c r="Q12">
-        <v>0.52894931</v>
+        <v>0.520669241</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1272628960296616</v>
+        <v>0.1279234315007698</v>
       </c>
       <c r="T12">
-        <v>0.5679953629182192</v>
+        <v>0.5726009085459587</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.938960170500994</v>
+        <v>5.399054700455449</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1181099540356851</v>
+        <v>0.1178123016446747</v>
       </c>
       <c r="C13">
-        <v>20.46861169111582</v>
+        <v>20.33531835762427</v>
       </c>
       <c r="D13">
-        <v>19.50151169111582</v>
+        <v>19.58211835762427</v>
       </c>
       <c r="E13">
-        <v>0.1629</v>
+        <v>0.3768000000000002</v>
       </c>
       <c r="F13">
-        <v>2.3529</v>
+        <v>2.5668</v>
       </c>
       <c r="G13">
         <v>3.32</v>
@@ -2341,28 +2341,28 @@
         <v>0.7025</v>
       </c>
       <c r="M13">
-        <v>0.13011537</v>
+        <v>0.14194404</v>
       </c>
       <c r="N13">
-        <v>0.5723846299999999</v>
+        <v>0.56055596</v>
       </c>
       <c r="O13">
-        <v>0.171715389</v>
+        <v>0.168166788</v>
       </c>
       <c r="P13">
-        <v>0.400669241</v>
+        <v>0.392389172</v>
       </c>
       <c r="Q13">
-        <v>0.520669241</v>
+        <v>0.512389172</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1279234315007698</v>
+        <v>0.1285989791416758</v>
       </c>
       <c r="T13">
-        <v>0.5726009085459587</v>
+        <v>0.5773111256652378</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.399054700455449</v>
+        <v>4.949133475417494</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1178123016446747</v>
+        <v>0.1175146492536643</v>
       </c>
       <c r="C14">
-        <v>20.33531835762427</v>
+        <v>20.20269414173331</v>
       </c>
       <c r="D14">
-        <v>19.58211835762427</v>
+        <v>19.66339414173331</v>
       </c>
       <c r="E14">
-        <v>0.3768000000000002</v>
+        <v>0.5907</v>
       </c>
       <c r="F14">
-        <v>2.5668</v>
+        <v>2.7807</v>
       </c>
       <c r="G14">
         <v>3.32</v>
@@ -2423,28 +2423,28 @@
         <v>0.7025</v>
       </c>
       <c r="M14">
-        <v>0.14194404</v>
+        <v>0.15377271</v>
       </c>
       <c r="N14">
-        <v>0.56055596</v>
+        <v>0.54872729</v>
       </c>
       <c r="O14">
-        <v>0.168166788</v>
+        <v>0.164618187</v>
       </c>
       <c r="P14">
-        <v>0.392389172</v>
+        <v>0.384109103</v>
       </c>
       <c r="Q14">
-        <v>0.512389172</v>
+        <v>0.504109103</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1285989791416758</v>
+        <v>0.1292900566134072</v>
       </c>
       <c r="T14">
-        <v>0.5773111256652378</v>
+        <v>0.5821296236378335</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.949133475417494</v>
+        <v>4.56843090038538</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1175146492536643</v>
+        <v>0.1174619968626539</v>
       </c>
       <c r="C15">
-        <v>20.20269414173331</v>
+        <v>20.0032414745215</v>
       </c>
       <c r="D15">
-        <v>19.66339414173331</v>
+        <v>19.6778414745215</v>
       </c>
       <c r="E15">
-        <v>0.5907</v>
+        <v>0.8046000000000002</v>
       </c>
       <c r="F15">
-        <v>2.7807</v>
+        <v>2.9946</v>
       </c>
       <c r="G15">
         <v>3.32</v>
@@ -2505,45 +2505,45 @@
         <v>0.7025</v>
       </c>
       <c r="M15">
-        <v>0.15377271</v>
+        <v>0.17308788</v>
       </c>
       <c r="N15">
-        <v>0.54872729</v>
+        <v>0.5294121199999999</v>
       </c>
       <c r="O15">
-        <v>0.164618187</v>
+        <v>0.158823636</v>
       </c>
       <c r="P15">
-        <v>0.384109103</v>
+        <v>0.370588484</v>
       </c>
       <c r="Q15">
-        <v>0.504109103</v>
+        <v>0.490588484</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1292900566134072</v>
+        <v>0.1299972056542487</v>
       </c>
       <c r="T15">
-        <v>0.5821296236378335</v>
+        <v>0.5870601797028153</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.56843090038538</v>
+        <v>4.05863195042888</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1174619968626539</v>
+        <v>0.1175493444716435</v>
       </c>
       <c r="C16">
-        <v>20.0032414745215</v>
+        <v>19.76538568209535</v>
       </c>
       <c r="D16">
-        <v>19.6778414745215</v>
+        <v>19.65388568209535</v>
       </c>
       <c r="E16">
-        <v>0.8046000000000002</v>
+        <v>1.0185</v>
       </c>
       <c r="F16">
-        <v>2.9946</v>
+        <v>3.2085</v>
       </c>
       <c r="G16">
         <v>3.32</v>
@@ -2587,45 +2587,45 @@
         <v>0.7025</v>
       </c>
       <c r="M16">
-        <v>0.17308788</v>
+        <v>0.19668105</v>
       </c>
       <c r="N16">
-        <v>0.5294121199999999</v>
+        <v>0.50581895</v>
       </c>
       <c r="O16">
-        <v>0.158823636</v>
+        <v>0.151745685</v>
       </c>
       <c r="P16">
-        <v>0.370588484</v>
+        <v>0.354073265</v>
       </c>
       <c r="Q16">
-        <v>0.490588484</v>
+        <v>0.474073265</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1299972056542487</v>
+        <v>0.1307209934960512</v>
       </c>
       <c r="T16">
-        <v>0.5870601797028153</v>
+        <v>0.592106748851679</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.05863195042888</v>
+        <v>3.57177267459168</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1175493444716435</v>
+        <v>0.1176072920806331</v>
       </c>
       <c r="C17">
-        <v>19.76538568209535</v>
+        <v>19.53562523603711</v>
       </c>
       <c r="D17">
-        <v>19.65388568209535</v>
+        <v>19.63802523603711</v>
       </c>
       <c r="E17">
-        <v>1.0185</v>
+        <v>1.2324</v>
       </c>
       <c r="F17">
-        <v>3.2085</v>
+        <v>3.4224</v>
       </c>
       <c r="G17">
         <v>3.32</v>
@@ -2669,45 +2669,45 @@
         <v>0.7025</v>
       </c>
       <c r="M17">
-        <v>0.19668105</v>
+        <v>0.21937584</v>
       </c>
       <c r="N17">
-        <v>0.50581895</v>
+        <v>0.48312416</v>
       </c>
       <c r="O17">
-        <v>0.151745685</v>
+        <v>0.144937248</v>
       </c>
       <c r="P17">
-        <v>0.354073265</v>
+        <v>0.3381869120000001</v>
       </c>
       <c r="Q17">
-        <v>0.474073265</v>
+        <v>0.4581869120000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1307209934960512</v>
+        <v>0.1314620143817061</v>
       </c>
       <c r="T17">
-        <v>0.592106748851679</v>
+        <v>0.597273474408849</v>
       </c>
       <c r="U17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.57177267459168</v>
+        <v>3.202266940607498</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1176072920806331</v>
+        <v>0.1173712396896227</v>
       </c>
       <c r="C18">
-        <v>19.53562523603711</v>
+        <v>19.38649430852757</v>
       </c>
       <c r="D18">
-        <v>19.63802523603711</v>
+        <v>19.70279430852757</v>
       </c>
       <c r="E18">
-        <v>1.2324</v>
+        <v>1.4463</v>
       </c>
       <c r="F18">
-        <v>3.4224</v>
+        <v>3.6363</v>
       </c>
       <c r="G18">
         <v>3.32</v>
@@ -2751,28 +2751,28 @@
         <v>0.7025</v>
       </c>
       <c r="M18">
-        <v>0.21937584</v>
+        <v>0.23308683</v>
       </c>
       <c r="N18">
-        <v>0.48312416</v>
+        <v>0.46941317</v>
       </c>
       <c r="O18">
-        <v>0.144937248</v>
+        <v>0.140823951</v>
       </c>
       <c r="P18">
-        <v>0.3381869120000001</v>
+        <v>0.328589219</v>
       </c>
       <c r="Q18">
-        <v>0.4581869120000001</v>
+        <v>0.448589219</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1314620143817061</v>
+        <v>0.1322208911923165</v>
       </c>
       <c r="T18">
-        <v>0.597273474408849</v>
+        <v>0.6025646993770352</v>
       </c>
       <c r="U18">
         <v>0.0641</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.202266940607498</v>
+        <v>3.013898297042351</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1173712396896227</v>
+        <v>0.1181179872986123</v>
       </c>
       <c r="C19">
-        <v>19.38649430852757</v>
+        <v>18.96914541441559</v>
       </c>
       <c r="D19">
-        <v>19.70279430852757</v>
+        <v>19.49934541441559</v>
       </c>
       <c r="E19">
-        <v>1.4463</v>
+        <v>1.660200000000001</v>
       </c>
       <c r="F19">
-        <v>3.6363</v>
+        <v>3.850200000000001</v>
       </c>
       <c r="G19">
         <v>3.32</v>
@@ -2833,45 +2833,45 @@
         <v>0.7025</v>
       </c>
       <c r="M19">
-        <v>0.23308683</v>
+        <v>0.2768293800000001</v>
       </c>
       <c r="N19">
-        <v>0.46941317</v>
+        <v>0.4256706199999999</v>
       </c>
       <c r="O19">
-        <v>0.140823951</v>
+        <v>0.127701186</v>
       </c>
       <c r="P19">
-        <v>0.328589219</v>
+        <v>0.297969434</v>
       </c>
       <c r="Q19">
-        <v>0.448589219</v>
+        <v>0.417969434</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1322208911923165</v>
+        <v>0.1329982771934296</v>
       </c>
       <c r="T19">
-        <v>0.6025646993770352</v>
+        <v>0.6079849786127379</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.013898297042351</v>
+        <v>2.537664174228905</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1181179872986123</v>
+        <v>0.1184552349076019</v>
       </c>
       <c r="C20">
-        <v>18.96914541441559</v>
+        <v>18.66473428158067</v>
       </c>
       <c r="D20">
-        <v>19.49934541441559</v>
+        <v>19.40883428158067</v>
       </c>
       <c r="E20">
-        <v>1.6602</v>
+        <v>1.8741</v>
       </c>
       <c r="F20">
-        <v>3.8502</v>
+        <v>4.0641</v>
       </c>
       <c r="G20">
         <v>3.32</v>
@@ -2915,45 +2915,45 @@
         <v>0.7025</v>
       </c>
       <c r="M20">
-        <v>0.27682938</v>
+        <v>0.30805878</v>
       </c>
       <c r="N20">
-        <v>0.42567062</v>
+        <v>0.39444122</v>
       </c>
       <c r="O20">
-        <v>0.127701186</v>
+        <v>0.118332366</v>
       </c>
       <c r="P20">
-        <v>0.297969434</v>
+        <v>0.276108854</v>
       </c>
       <c r="Q20">
-        <v>0.417969434</v>
+        <v>0.396108854</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1329982771934296</v>
+        <v>0.1337948579106196</v>
       </c>
       <c r="T20">
-        <v>0.6079849786127379</v>
+        <v>0.6135390919036433</v>
       </c>
       <c r="U20">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.537664174228906</v>
+        <v>2.280408953122517</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1184552349076019</v>
+        <v>0.1183010825165915</v>
       </c>
       <c r="C21">
-        <v>18.66473428158067</v>
+        <v>18.49210150280521</v>
       </c>
       <c r="D21">
-        <v>19.40883428158067</v>
+        <v>19.4501015028052</v>
       </c>
       <c r="E21">
-        <v>1.8741</v>
+        <v>2.088000000000001</v>
       </c>
       <c r="F21">
-        <v>4.0641</v>
+        <v>4.278</v>
       </c>
       <c r="G21">
         <v>3.32</v>
@@ -2997,28 +2997,28 @@
         <v>0.7025</v>
       </c>
       <c r="M21">
-        <v>0.30805878</v>
+        <v>0.3242724000000001</v>
       </c>
       <c r="N21">
-        <v>0.39444122</v>
+        <v>0.3782275999999999</v>
       </c>
       <c r="O21">
-        <v>0.118332366</v>
+        <v>0.11346828</v>
       </c>
       <c r="P21">
-        <v>0.276108854</v>
+        <v>0.26475932</v>
       </c>
       <c r="Q21">
-        <v>0.396108854</v>
+        <v>0.38475932</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1337948579106196</v>
+        <v>0.1346113531457394</v>
       </c>
       <c r="T21">
-        <v>0.6135390919036433</v>
+        <v>0.6192320580268215</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.280408953122517</v>
+        <v>2.166388505466391</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1183010825165915</v>
+        <v>0.1181469301255811</v>
       </c>
       <c r="C22">
-        <v>18.49210150280521</v>
+        <v>18.3196445833457</v>
       </c>
       <c r="D22">
-        <v>19.4501015028052</v>
+        <v>19.4915445833457</v>
       </c>
       <c r="E22">
-        <v>2.088000000000001</v>
+        <v>2.3019</v>
       </c>
       <c r="F22">
-        <v>4.278</v>
+        <v>4.4919</v>
       </c>
       <c r="G22">
         <v>3.32</v>
@@ -3079,28 +3079,28 @@
         <v>0.7025</v>
       </c>
       <c r="M22">
-        <v>0.3242724000000001</v>
+        <v>0.3404860200000001</v>
       </c>
       <c r="N22">
-        <v>0.3782275999999999</v>
+        <v>0.36201398</v>
       </c>
       <c r="O22">
-        <v>0.11346828</v>
+        <v>0.108604194</v>
       </c>
       <c r="P22">
-        <v>0.26475932</v>
+        <v>0.253409786</v>
       </c>
       <c r="Q22">
-        <v>0.38475932</v>
+        <v>0.373409786</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1346113531457394</v>
+        <v>0.1354485191463052</v>
       </c>
       <c r="T22">
-        <v>0.6192320580268215</v>
+        <v>0.6250691498746369</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.166388505466391</v>
+        <v>2.06322714806323</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1181469301255811</v>
+        <v>0.1201795777345707</v>
       </c>
       <c r="C23">
-        <v>18.31964458334571</v>
+        <v>17.57307899556519</v>
       </c>
       <c r="D23">
-        <v>19.49154458334571</v>
+        <v>18.95887899556519</v>
       </c>
       <c r="E23">
-        <v>2.3019</v>
+        <v>2.5158</v>
       </c>
       <c r="F23">
-        <v>4.4919</v>
+        <v>4.7058</v>
       </c>
       <c r="G23">
         <v>3.32</v>
@@ -3161,45 +3161,45 @@
         <v>0.7025</v>
       </c>
       <c r="M23">
-        <v>0.3404860200000001</v>
+        <v>0.423522</v>
       </c>
       <c r="N23">
-        <v>0.36201398</v>
+        <v>0.278978</v>
       </c>
       <c r="O23">
-        <v>0.108604194</v>
+        <v>0.0836934</v>
       </c>
       <c r="P23">
-        <v>0.253409786</v>
+        <v>0.1952846</v>
       </c>
       <c r="Q23">
-        <v>0.373409786</v>
+        <v>0.3152846</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1354485191463052</v>
+        <v>0.1363071509417573</v>
       </c>
       <c r="T23">
-        <v>0.6250691498746368</v>
+        <v>0.6310559107441911</v>
       </c>
       <c r="U23">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.06322714806323</v>
+        <v>1.658709582973258</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1201795777345707</v>
+        <v>0.1201248253435603</v>
       </c>
       <c r="C24">
-        <v>17.57307899556519</v>
+        <v>17.37314531100671</v>
       </c>
       <c r="D24">
-        <v>18.95887899556519</v>
+        <v>18.97284531100671</v>
       </c>
       <c r="E24">
-        <v>2.5158</v>
+        <v>2.729700000000001</v>
       </c>
       <c r="F24">
-        <v>4.7058</v>
+        <v>4.919700000000001</v>
       </c>
       <c r="G24">
         <v>3.32</v>
@@ -3243,28 +3243,28 @@
         <v>0.7025</v>
       </c>
       <c r="M24">
-        <v>0.423522</v>
+        <v>0.442773</v>
       </c>
       <c r="N24">
-        <v>0.278978</v>
+        <v>0.259727</v>
       </c>
       <c r="O24">
-        <v>0.0836934</v>
+        <v>0.07791809999999999</v>
       </c>
       <c r="P24">
-        <v>0.1952846</v>
+        <v>0.1818089</v>
       </c>
       <c r="Q24">
-        <v>0.3152846</v>
+        <v>0.3018089</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1363071509417573</v>
+        <v>0.1371880848617666</v>
       </c>
       <c r="T24">
-        <v>0.6310559107441911</v>
+        <v>0.6371981718960715</v>
       </c>
       <c r="U24">
         <v>0.09</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.658709582973258</v>
+        <v>1.586591775017899</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1201248253435603</v>
+        <v>0.1200700729525499</v>
       </c>
       <c r="C25">
-        <v>17.37314531100671</v>
+        <v>17.17323221856922</v>
       </c>
       <c r="D25">
-        <v>18.97284531100671</v>
+        <v>18.98683221856922</v>
       </c>
       <c r="E25">
-        <v>2.729700000000001</v>
+        <v>2.9436</v>
       </c>
       <c r="F25">
-        <v>4.919700000000001</v>
+        <v>5.1336</v>
       </c>
       <c r="G25">
         <v>3.32</v>
@@ -3325,28 +3325,28 @@
         <v>0.7025</v>
       </c>
       <c r="M25">
-        <v>0.442773</v>
+        <v>0.462024</v>
       </c>
       <c r="N25">
-        <v>0.259727</v>
+        <v>0.240476</v>
       </c>
       <c r="O25">
-        <v>0.07791809999999999</v>
+        <v>0.07214280000000001</v>
       </c>
       <c r="P25">
-        <v>0.1818089</v>
+        <v>0.1683332</v>
       </c>
       <c r="Q25">
-        <v>0.3018089</v>
+        <v>0.2883332</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1371880848617666</v>
+        <v>0.1380922012533551</v>
       </c>
       <c r="T25">
-        <v>0.6371981718960715</v>
+        <v>0.6435020714993172</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.586591775017899</v>
+        <v>1.520483784392153</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1200700729525499</v>
+        <v>0.1317084362818983</v>
       </c>
       <c r="C26">
-        <v>17.17323221856922</v>
+        <v>14.38710926356184</v>
       </c>
       <c r="D26">
-        <v>18.98683221856922</v>
+        <v>16.41460926356184</v>
       </c>
       <c r="E26">
-        <v>2.9436</v>
+        <v>3.1575</v>
       </c>
       <c r="F26">
-        <v>5.1336</v>
+        <v>5.3475</v>
       </c>
       <c r="G26">
         <v>3.32</v>
@@ -3407,45 +3407,45 @@
         <v>0.7025</v>
       </c>
       <c r="M26">
-        <v>0.462024</v>
+        <v>0.7850130000000001</v>
       </c>
       <c r="N26">
-        <v>0.240476</v>
+        <v>-0.08251300000000006</v>
       </c>
       <c r="O26">
-        <v>0.07214280000000001</v>
+        <v>-0.02475390000000002</v>
       </c>
       <c r="P26">
-        <v>0.1683332</v>
+        <v>-0.05775910000000004</v>
       </c>
       <c r="Q26">
-        <v>0.2883332</v>
+        <v>0.06224089999999995</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1380922012533551</v>
+        <v>0.1398148949396793</v>
       </c>
       <c r="T26">
-        <v>0.6435020714993172</v>
+        <v>0.6555134542668084</v>
       </c>
       <c r="U26">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.3</v>
+        <v>0.2684668916310939</v>
       </c>
       <c r="W26">
-        <v>0.063</v>
+        <v>0.1073890603085554</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.520483784392153</v>
+        <v>0.8948896387703132</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1317084362818983</v>
+        <v>0.1327184362818983</v>
       </c>
       <c r="C27">
-        <v>14.38710926356184</v>
+        <v>13.9824700364728</v>
       </c>
       <c r="D27">
-        <v>16.41460926356184</v>
+        <v>16.2238700364728</v>
       </c>
       <c r="E27">
-        <v>3.1575</v>
+        <v>3.3714</v>
       </c>
       <c r="F27">
-        <v>5.3475</v>
+        <v>5.5614</v>
       </c>
       <c r="G27">
         <v>3.32</v>
@@ -3489,37 +3489,37 @@
         <v>0.7025</v>
       </c>
       <c r="M27">
-        <v>0.7850130000000001</v>
+        <v>0.8164135200000001</v>
       </c>
       <c r="N27">
-        <v>-0.08251300000000006</v>
+        <v>-0.1139135200000001</v>
       </c>
       <c r="O27">
-        <v>-0.02475390000000002</v>
+        <v>-0.03417405600000003</v>
       </c>
       <c r="P27">
-        <v>-0.05775910000000004</v>
+        <v>-0.07973946400000007</v>
       </c>
       <c r="Q27">
-        <v>0.06224089999999995</v>
+        <v>0.04026053599999993</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1398148949396793</v>
+        <v>0.1410853664929182</v>
       </c>
       <c r="T27">
-        <v>0.6555134542668084</v>
+        <v>0.6643717441893329</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.2684668916310939</v>
+        <v>0.2581412419529749</v>
       </c>
       <c r="W27">
-        <v>0.1073890603085554</v>
+        <v>0.1089048656813033</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8948896387703132</v>
+        <v>0.8604708065099166</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1327184362818983</v>
+        <v>0.1337284362818983</v>
       </c>
       <c r="C28">
-        <v>13.9824700364728</v>
+        <v>13.58221270510501</v>
       </c>
       <c r="D28">
-        <v>16.2238700364728</v>
+        <v>16.03751270510501</v>
       </c>
       <c r="E28">
-        <v>3.3714</v>
+        <v>3.585300000000001</v>
       </c>
       <c r="F28">
-        <v>5.5614</v>
+        <v>5.775300000000001</v>
       </c>
       <c r="G28">
         <v>3.32</v>
@@ -3571,37 +3571,37 @@
         <v>0.7025</v>
       </c>
       <c r="M28">
-        <v>0.8164135200000001</v>
+        <v>0.8478140400000002</v>
       </c>
       <c r="N28">
-        <v>-0.1139135200000001</v>
+        <v>-0.1453140400000001</v>
       </c>
       <c r="O28">
-        <v>-0.03417405600000003</v>
+        <v>-0.04359421200000004</v>
       </c>
       <c r="P28">
-        <v>-0.07973946400000007</v>
+        <v>-0.1017198280000001</v>
       </c>
       <c r="Q28">
-        <v>0.04026053599999993</v>
+        <v>0.0182801719999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1410853664929182</v>
+        <v>0.1423906454859719</v>
       </c>
       <c r="T28">
-        <v>0.6643717441893329</v>
+        <v>0.6734727269864469</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.2581412419529749</v>
+        <v>0.2485804552139759</v>
       </c>
       <c r="W28">
-        <v>0.1089048656813033</v>
+        <v>0.1103083891745884</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.8604708065099166</v>
+        <v>0.8286015173799196</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1337284362818983</v>
+        <v>0.1512226782795585</v>
       </c>
       <c r="C29">
-        <v>13.58221270510501</v>
+        <v>10.70698657601863</v>
       </c>
       <c r="D29">
-        <v>16.03751270510501</v>
+        <v>13.37618657601863</v>
       </c>
       <c r="E29">
-        <v>3.585300000000001</v>
+        <v>3.7992</v>
       </c>
       <c r="F29">
-        <v>5.775300000000001</v>
+        <v>5.9892</v>
       </c>
       <c r="G29">
         <v>3.32</v>
@@ -3653,45 +3653,45 @@
         <v>0.7025</v>
       </c>
       <c r="M29">
-        <v>0.8478140400000002</v>
+        <v>1.20263136</v>
       </c>
       <c r="N29">
-        <v>-0.1453140400000001</v>
+        <v>-0.50013136</v>
       </c>
       <c r="O29">
-        <v>-0.04359421200000004</v>
+        <v>-0.150039408</v>
       </c>
       <c r="P29">
-        <v>-0.1017198280000001</v>
+        <v>-0.350091952</v>
       </c>
       <c r="Q29">
-        <v>0.0182801719999999</v>
+        <v>-0.230091952</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1423906454859719</v>
+        <v>0.1456269627811384</v>
       </c>
       <c r="T29">
-        <v>0.6734727269864469</v>
+        <v>0.6960377634162505</v>
       </c>
       <c r="U29">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.2485804552139759</v>
+        <v>0.1752407321226016</v>
       </c>
       <c r="W29">
-        <v>0.1103083891745884</v>
+        <v>0.1656116609897816</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.8286015173799196</v>
+        <v>0.5841357737420052</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1512226782795585</v>
+        <v>0.1527726782795585</v>
       </c>
       <c r="C30">
-        <v>10.70698657601863</v>
+        <v>10.29926989753325</v>
       </c>
       <c r="D30">
-        <v>13.37618657601863</v>
+        <v>13.18236989753325</v>
       </c>
       <c r="E30">
-        <v>3.7992</v>
+        <v>4.013100000000001</v>
       </c>
       <c r="F30">
-        <v>5.9892</v>
+        <v>6.203100000000001</v>
       </c>
       <c r="G30">
         <v>3.32</v>
@@ -3735,37 +3735,37 @@
         <v>0.7025</v>
       </c>
       <c r="M30">
-        <v>1.20263136</v>
+        <v>1.24558248</v>
       </c>
       <c r="N30">
-        <v>-0.50013136</v>
+        <v>-0.5430824800000001</v>
       </c>
       <c r="O30">
-        <v>-0.150039408</v>
+        <v>-0.162924744</v>
       </c>
       <c r="P30">
-        <v>-0.350091952</v>
+        <v>-0.3801577360000001</v>
       </c>
       <c r="Q30">
-        <v>-0.230091952</v>
+        <v>-0.2601577360000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1456269627811384</v>
+        <v>0.1470329763414361</v>
       </c>
       <c r="T30">
-        <v>0.6960377634162505</v>
+        <v>0.7058411121967609</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.1752407321226016</v>
+        <v>0.1691979482563049</v>
       </c>
       <c r="W30">
-        <v>0.1656116609897816</v>
+        <v>0.166825051990134</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5841357737420052</v>
+        <v>0.5639931608543498</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1527726782795585</v>
+        <v>0.1543226782795585</v>
       </c>
       <c r="C31">
-        <v>10.29926989753325</v>
+        <v>9.89708968122177</v>
       </c>
       <c r="D31">
-        <v>13.18236989753325</v>
+        <v>12.99408968122177</v>
       </c>
       <c r="E31">
-        <v>4.0131</v>
+        <v>4.227</v>
       </c>
       <c r="F31">
-        <v>6.2031</v>
+        <v>6.417</v>
       </c>
       <c r="G31">
         <v>3.32</v>
@@ -3817,37 +3817,37 @@
         <v>0.7025</v>
       </c>
       <c r="M31">
-        <v>1.24558248</v>
+        <v>1.2885336</v>
       </c>
       <c r="N31">
-        <v>-0.5430824800000001</v>
+        <v>-0.5860336</v>
       </c>
       <c r="O31">
-        <v>-0.162924744</v>
+        <v>-0.17581008</v>
       </c>
       <c r="P31">
-        <v>-0.3801577360000001</v>
+        <v>-0.4102235200000001</v>
       </c>
       <c r="Q31">
-        <v>-0.2601577360000001</v>
+        <v>-0.2902235200000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1470329763414361</v>
+        <v>0.1484791617177423</v>
       </c>
       <c r="T31">
-        <v>0.7058411121967609</v>
+        <v>0.7159245566567147</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1691979482563049</v>
+        <v>0.1635580166477615</v>
       </c>
       <c r="W31">
-        <v>0.166825051990134</v>
+        <v>0.1679575502571295</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5639931608543498</v>
+        <v>0.5451933888258715</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1543226782795585</v>
+        <v>0.1558726782795585</v>
       </c>
       <c r="C32">
-        <v>9.89708968122177</v>
+        <v>9.500212040260397</v>
       </c>
       <c r="D32">
-        <v>12.99408968122177</v>
+        <v>12.8111120402604</v>
       </c>
       <c r="E32">
-        <v>4.227</v>
+        <v>4.440900000000001</v>
       </c>
       <c r="F32">
-        <v>6.417</v>
+        <v>6.6309</v>
       </c>
       <c r="G32">
         <v>3.32</v>
@@ -3899,37 +3899,37 @@
         <v>0.7025</v>
       </c>
       <c r="M32">
-        <v>1.2885336</v>
+        <v>1.33148472</v>
       </c>
       <c r="N32">
-        <v>-0.5860336</v>
+        <v>-0.6289847200000002</v>
       </c>
       <c r="O32">
-        <v>-0.17581008</v>
+        <v>-0.188695416</v>
       </c>
       <c r="P32">
-        <v>-0.4102235200000001</v>
+        <v>-0.4402893040000001</v>
       </c>
       <c r="Q32">
-        <v>-0.2902235200000001</v>
+        <v>-0.3202893040000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1484791617177423</v>
+        <v>0.1499672655107531</v>
       </c>
       <c r="T32">
-        <v>0.7159245566567147</v>
+        <v>0.726300274869131</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1635580166477615</v>
+        <v>0.1582819515946078</v>
       </c>
       <c r="W32">
-        <v>0.1679575502571295</v>
+        <v>0.1690169841198027</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5451933888258715</v>
+        <v>0.5276065053153595</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1558726782795585</v>
+        <v>0.1574226782795585</v>
       </c>
       <c r="C33">
-        <v>9.500212040260397</v>
+        <v>9.108416078897857</v>
       </c>
       <c r="D33">
-        <v>12.8111120402604</v>
+        <v>12.63321607889786</v>
       </c>
       <c r="E33">
-        <v>4.440900000000001</v>
+        <v>4.6548</v>
       </c>
       <c r="F33">
-        <v>6.6309</v>
+        <v>6.8448</v>
       </c>
       <c r="G33">
         <v>3.32</v>
@@ -3981,37 +3981,37 @@
         <v>0.7025</v>
       </c>
       <c r="M33">
-        <v>1.33148472</v>
+        <v>1.37443584</v>
       </c>
       <c r="N33">
-        <v>-0.6289847200000002</v>
+        <v>-0.6719358400000001</v>
       </c>
       <c r="O33">
-        <v>-0.188695416</v>
+        <v>-0.201580752</v>
       </c>
       <c r="P33">
-        <v>-0.4402893040000001</v>
+        <v>-0.470355088</v>
       </c>
       <c r="Q33">
-        <v>-0.3202893040000001</v>
+        <v>-0.350355088</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1499672655107531</v>
+        <v>0.1514991370623818</v>
       </c>
       <c r="T33">
-        <v>0.726300274869131</v>
+        <v>0.7369811612642652</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1582819515946078</v>
+        <v>0.1533356406072764</v>
       </c>
       <c r="W33">
-        <v>0.1690169841198027</v>
+        <v>0.1700102033660589</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5276065053153595</v>
+        <v>0.5111188020242545</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1574226782795585</v>
+        <v>0.1710731664038303</v>
       </c>
       <c r="C34">
-        <v>9.108416078897857</v>
+        <v>7.517927851691664</v>
       </c>
       <c r="D34">
-        <v>12.63321607889786</v>
+        <v>11.25662785169166</v>
       </c>
       <c r="E34">
-        <v>4.6548</v>
+        <v>4.8687</v>
       </c>
       <c r="F34">
-        <v>6.8448</v>
+        <v>7.058700000000001</v>
       </c>
       <c r="G34">
         <v>3.32</v>
@@ -4063,45 +4063,45 @@
         <v>0.7025</v>
       </c>
       <c r="M34">
-        <v>1.37443584</v>
+        <v>1.66444146</v>
       </c>
       <c r="N34">
-        <v>-0.6719358400000001</v>
+        <v>-0.9619414600000004</v>
       </c>
       <c r="O34">
-        <v>-0.201580752</v>
+        <v>-0.2885824380000001</v>
       </c>
       <c r="P34">
-        <v>-0.470355088</v>
+        <v>-0.6733590220000003</v>
       </c>
       <c r="Q34">
-        <v>-0.350355088</v>
+        <v>-0.5533590220000003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1514991370623818</v>
+        <v>0.1538983601890917</v>
       </c>
       <c r="T34">
-        <v>0.7369811612642652</v>
+        <v>0.7537096066915083</v>
       </c>
       <c r="U34">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.1533356406072764</v>
+        <v>0.1266190521353631</v>
       </c>
       <c r="W34">
-        <v>0.1700102033660589</v>
+        <v>0.2059432275064814</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.5111188020242545</v>
+        <v>0.4220635071178772</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1710731664038303</v>
+        <v>0.1729731664038303</v>
       </c>
       <c r="C35">
-        <v>7.517927851691664</v>
+        <v>7.135850920008616</v>
       </c>
       <c r="D35">
-        <v>11.25662785169166</v>
+        <v>11.08845092000862</v>
       </c>
       <c r="E35">
-        <v>4.8687</v>
+        <v>5.082600000000001</v>
       </c>
       <c r="F35">
-        <v>7.058700000000001</v>
+        <v>7.272600000000001</v>
       </c>
       <c r="G35">
         <v>3.32</v>
@@ -4145,37 +4145,37 @@
         <v>0.7025</v>
       </c>
       <c r="M35">
-        <v>1.66444146</v>
+        <v>1.71487908</v>
       </c>
       <c r="N35">
-        <v>-0.9619414600000004</v>
+        <v>-1.01237908</v>
       </c>
       <c r="O35">
-        <v>-0.2885824380000001</v>
+        <v>-0.303713724</v>
       </c>
       <c r="P35">
-        <v>-0.6733590220000003</v>
+        <v>-0.708665356</v>
       </c>
       <c r="Q35">
-        <v>-0.5533590220000003</v>
+        <v>-0.588665356</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1538983601890917</v>
+        <v>0.1555362141313507</v>
       </c>
       <c r="T35">
-        <v>0.7537096066915083</v>
+        <v>0.7651294492171372</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.1266190521353631</v>
+        <v>0.122894962366676</v>
       </c>
       <c r="W35">
-        <v>0.2059432275064814</v>
+        <v>0.2068213678739378</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.4220635071178772</v>
+        <v>0.4096498745555868</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1729731664038303</v>
+        <v>0.1748731664038303</v>
       </c>
       <c r="C36">
-        <v>7.135850920008616</v>
+        <v>6.758725229224048</v>
       </c>
       <c r="D36">
-        <v>11.08845092000862</v>
+        <v>10.92522522922405</v>
       </c>
       <c r="E36">
-        <v>5.082600000000001</v>
+        <v>5.296500000000002</v>
       </c>
       <c r="F36">
-        <v>7.272600000000001</v>
+        <v>7.486500000000001</v>
       </c>
       <c r="G36">
         <v>3.32</v>
@@ -4227,37 +4227,37 @@
         <v>0.7025</v>
       </c>
       <c r="M36">
-        <v>1.71487908</v>
+        <v>1.7653167</v>
       </c>
       <c r="N36">
-        <v>-1.01237908</v>
+        <v>-1.0628167</v>
       </c>
       <c r="O36">
-        <v>-0.303713724</v>
+        <v>-0.3188450100000001</v>
       </c>
       <c r="P36">
-        <v>-0.708665356</v>
+        <v>-0.7439716900000003</v>
       </c>
       <c r="Q36">
-        <v>-0.588665356</v>
+        <v>-0.6239716900000003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1555362141313507</v>
+        <v>0.1572244635795253</v>
       </c>
       <c r="T36">
-        <v>0.7651294492171372</v>
+        <v>0.7769006715127856</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.122894962366676</v>
+        <v>0.1193836777276281</v>
       </c>
       <c r="W36">
-        <v>0.2068213678739378</v>
+        <v>0.2076493287918253</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4096498745555868</v>
+        <v>0.397945592425427</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1748731664038303</v>
+        <v>0.1767731664038303</v>
       </c>
       <c r="C37">
-        <v>6.758725229224048</v>
+        <v>6.38633529952713</v>
       </c>
       <c r="D37">
-        <v>10.92522522922405</v>
+        <v>10.76673529952713</v>
       </c>
       <c r="E37">
-        <v>5.296500000000002</v>
+        <v>5.510400000000001</v>
       </c>
       <c r="F37">
-        <v>7.486500000000001</v>
+        <v>7.700400000000001</v>
       </c>
       <c r="G37">
         <v>3.32</v>
@@ -4309,37 +4309,37 @@
         <v>0.7025</v>
       </c>
       <c r="M37">
-        <v>1.7653167</v>
+        <v>1.81575432</v>
       </c>
       <c r="N37">
-        <v>-1.0628167</v>
+        <v>-1.11325432</v>
       </c>
       <c r="O37">
-        <v>-0.3188450100000001</v>
+        <v>-0.3339762960000001</v>
       </c>
       <c r="P37">
-        <v>-0.7439716900000003</v>
+        <v>-0.7792780240000001</v>
       </c>
       <c r="Q37">
-        <v>-0.6239716900000003</v>
+        <v>-0.6592780240000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1572244635795253</v>
+        <v>0.1589654708229554</v>
       </c>
       <c r="T37">
-        <v>0.7769006715127856</v>
+        <v>0.7890397445051728</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.1193836777276281</v>
+        <v>0.1160674644574162</v>
       </c>
       <c r="W37">
-        <v>0.2076493287918253</v>
+        <v>0.2084312918809413</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.397945592425427</v>
+        <v>0.3868915481913875</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1767731664038303</v>
+        <v>0.1786731664038303</v>
       </c>
       <c r="C38">
-        <v>6.386335299527131</v>
+        <v>6.018477975992529</v>
       </c>
       <c r="D38">
-        <v>10.76673529952713</v>
+        <v>10.61277797599253</v>
       </c>
       <c r="E38">
-        <v>5.510400000000001</v>
+        <v>5.724299999999999</v>
       </c>
       <c r="F38">
-        <v>7.7004</v>
+        <v>7.9143</v>
       </c>
       <c r="G38">
         <v>3.32</v>
@@ -4391,37 +4391,37 @@
         <v>0.7025</v>
       </c>
       <c r="M38">
-        <v>1.81575432</v>
+        <v>1.86619194</v>
       </c>
       <c r="N38">
-        <v>-1.11325432</v>
+        <v>-1.16369194</v>
       </c>
       <c r="O38">
-        <v>-0.3339762960000001</v>
+        <v>-0.349107582</v>
       </c>
       <c r="P38">
-        <v>-0.7792780240000001</v>
+        <v>-0.8145843580000001</v>
       </c>
       <c r="Q38">
-        <v>-0.6592780240000001</v>
+        <v>-0.6945843580000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1589654708229554</v>
+        <v>0.1607617481376054</v>
       </c>
       <c r="T38">
-        <v>0.7890397445051728</v>
+        <v>0.8015641848941437</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.1160674644574162</v>
+        <v>0.1129305059585672</v>
       </c>
       <c r="W38">
-        <v>0.2084312918809413</v>
+        <v>0.2091709866949699</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3868915481913874</v>
+        <v>0.3764350198618904</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1786731664038303</v>
+        <v>0.1805731664038303</v>
       </c>
       <c r="C39">
-        <v>6.018477975992529</v>
+        <v>5.654961559813909</v>
       </c>
       <c r="D39">
-        <v>10.61277797599253</v>
+        <v>10.46316155981391</v>
       </c>
       <c r="E39">
-        <v>5.724299999999999</v>
+        <v>5.9382</v>
       </c>
       <c r="F39">
-        <v>7.9143</v>
+        <v>8.1282</v>
       </c>
       <c r="G39">
         <v>3.32</v>
@@ -4473,37 +4473,37 @@
         <v>0.7025</v>
       </c>
       <c r="M39">
-        <v>1.86619194</v>
+        <v>1.91662956</v>
       </c>
       <c r="N39">
-        <v>-1.16369194</v>
+        <v>-1.21412956</v>
       </c>
       <c r="O39">
-        <v>-0.349107582</v>
+        <v>-0.364238868</v>
       </c>
       <c r="P39">
-        <v>-0.8145843580000001</v>
+        <v>-0.849890692</v>
       </c>
       <c r="Q39">
-        <v>-0.6945843580000001</v>
+        <v>-0.729890692</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1607617481376054</v>
+        <v>0.1626159698817604</v>
       </c>
       <c r="T39">
-        <v>0.8015641848941437</v>
+        <v>0.8144926394892107</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.1129305059585672</v>
+        <v>0.1099586505386049</v>
       </c>
       <c r="W39">
-        <v>0.2091709866949699</v>
+        <v>0.209871750202997</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3764350198618904</v>
+        <v>0.366528835128683</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1805731664038303</v>
+        <v>0.1824731664038303</v>
       </c>
       <c r="C40">
-        <v>5.654961559813909</v>
+        <v>5.295605012001836</v>
       </c>
       <c r="D40">
-        <v>10.46316155981391</v>
+        <v>10.31770501200184</v>
       </c>
       <c r="E40">
-        <v>5.9382</v>
+        <v>6.152100000000001</v>
       </c>
       <c r="F40">
-        <v>8.1282</v>
+        <v>8.3421</v>
       </c>
       <c r="G40">
         <v>3.32</v>
@@ -4555,37 +4555,37 @@
         <v>0.7025</v>
       </c>
       <c r="M40">
-        <v>1.91662956</v>
+        <v>1.96706718</v>
       </c>
       <c r="N40">
-        <v>-1.21412956</v>
+        <v>-1.26456718</v>
       </c>
       <c r="O40">
-        <v>-0.364238868</v>
+        <v>-0.3793701540000001</v>
       </c>
       <c r="P40">
-        <v>-0.849890692</v>
+        <v>-0.8851970260000002</v>
       </c>
       <c r="Q40">
-        <v>-0.729890692</v>
+        <v>-0.7651970260000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1626159698817604</v>
+        <v>0.1645309857814614</v>
       </c>
       <c r="T40">
-        <v>0.8144926394892107</v>
+        <v>0.8278449778414927</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.1099586505386049</v>
+        <v>0.1071391979606919</v>
       </c>
       <c r="W40">
-        <v>0.209871750202997</v>
+        <v>0.2105365771208688</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.366528835128683</v>
+        <v>0.357130659868973</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1824731664038303</v>
+        <v>0.1843731664038303</v>
       </c>
       <c r="C41">
-        <v>5.295605012001836</v>
+        <v>4.940237222591044</v>
       </c>
       <c r="D41">
-        <v>10.31770501200184</v>
+        <v>10.17623722259104</v>
       </c>
       <c r="E41">
-        <v>6.152100000000001</v>
+        <v>6.366000000000001</v>
       </c>
       <c r="F41">
-        <v>8.3421</v>
+        <v>8.556000000000001</v>
       </c>
       <c r="G41">
         <v>3.32</v>
@@ -4637,37 +4637,37 @@
         <v>0.7025</v>
       </c>
       <c r="M41">
-        <v>1.96706718</v>
+        <v>2.0175048</v>
       </c>
       <c r="N41">
-        <v>-1.26456718</v>
+        <v>-1.3150048</v>
       </c>
       <c r="O41">
-        <v>-0.3793701540000001</v>
+        <v>-0.39450144</v>
       </c>
       <c r="P41">
-        <v>-0.8851970260000002</v>
+        <v>-0.9205033600000001</v>
       </c>
       <c r="Q41">
-        <v>-0.7651970260000002</v>
+        <v>-0.8005033600000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1645309857814614</v>
+        <v>0.1665098355444857</v>
       </c>
       <c r="T41">
-        <v>0.8278449778414927</v>
+        <v>0.841642394138851</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.1071391979606919</v>
+        <v>0.1044607180116746</v>
       </c>
       <c r="W41">
-        <v>0.2105365771208688</v>
+        <v>0.2111681626928472</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.357130659868973</v>
+        <v>0.3482023933722488</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1843731664038303</v>
+        <v>0.1862731664038303</v>
       </c>
       <c r="C42">
-        <v>4.940237222591044</v>
+        <v>4.588696339154705</v>
       </c>
       <c r="D42">
-        <v>10.17623722259104</v>
+        <v>10.03859633915471</v>
       </c>
       <c r="E42">
-        <v>6.366000000000001</v>
+        <v>6.579900000000002</v>
       </c>
       <c r="F42">
-        <v>8.556000000000001</v>
+        <v>8.769900000000002</v>
       </c>
       <c r="G42">
         <v>3.32</v>
@@ -4719,37 +4719,37 @@
         <v>0.7025</v>
       </c>
       <c r="M42">
-        <v>2.0175048</v>
+        <v>2.067942420000001</v>
       </c>
       <c r="N42">
-        <v>-1.3150048</v>
+        <v>-1.36544242</v>
       </c>
       <c r="O42">
-        <v>-0.39450144</v>
+        <v>-0.4096327260000001</v>
       </c>
       <c r="P42">
-        <v>-0.9205033600000001</v>
+        <v>-0.9558096940000003</v>
       </c>
       <c r="Q42">
-        <v>-0.8005033600000001</v>
+        <v>-0.8358096940000003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1665098355444857</v>
+        <v>0.168555764960494</v>
       </c>
       <c r="T42">
-        <v>0.841642394138851</v>
+        <v>0.8559075194632382</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.1044607180116746</v>
+        <v>0.1019128956211459</v>
       </c>
       <c r="W42">
-        <v>0.2111681626928472</v>
+        <v>0.2117689392125338</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3482023933722488</v>
+        <v>0.3397096520704865</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1862731664038303</v>
+        <v>0.1881731664038303</v>
       </c>
       <c r="C43">
-        <v>4.588696339154705</v>
+        <v>4.240829149085377</v>
       </c>
       <c r="D43">
-        <v>10.03859633915471</v>
+        <v>9.904629149085377</v>
       </c>
       <c r="E43">
-        <v>6.579900000000002</v>
+        <v>6.793800000000001</v>
       </c>
       <c r="F43">
-        <v>8.769900000000002</v>
+        <v>8.9838</v>
       </c>
       <c r="G43">
         <v>3.32</v>
@@ -4801,37 +4801,37 @@
         <v>0.7025</v>
       </c>
       <c r="M43">
-        <v>2.067942420000001</v>
+        <v>2.11838004</v>
       </c>
       <c r="N43">
-        <v>-1.36544242</v>
+        <v>-1.41588004</v>
       </c>
       <c r="O43">
-        <v>-0.4096327260000001</v>
+        <v>-0.4247640120000001</v>
       </c>
       <c r="P43">
-        <v>-0.9558096940000003</v>
+        <v>-0.9911160280000002</v>
       </c>
       <c r="Q43">
-        <v>-0.8358096940000003</v>
+        <v>-0.8711160280000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.168555764960494</v>
+        <v>0.1706722436667094</v>
       </c>
       <c r="T43">
-        <v>0.8559075194632382</v>
+        <v>0.8706645456608804</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.1019128956211459</v>
+        <v>0.09948639810635677</v>
       </c>
       <c r="W43">
-        <v>0.2117689392125338</v>
+        <v>0.2123411073265211</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3397096520704865</v>
+        <v>0.3316213270211893</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1881731664038303</v>
+        <v>0.1900731664038303</v>
       </c>
       <c r="C44">
-        <v>4.240829149085377</v>
+        <v>3.896490510686142</v>
       </c>
       <c r="D44">
-        <v>9.904629149085377</v>
+        <v>9.774190510686141</v>
       </c>
       <c r="E44">
-        <v>6.793800000000001</v>
+        <v>7.0077</v>
       </c>
       <c r="F44">
-        <v>8.9838</v>
+        <v>9.197699999999999</v>
       </c>
       <c r="G44">
         <v>3.32</v>
@@ -4883,37 +4883,37 @@
         <v>0.7025</v>
       </c>
       <c r="M44">
-        <v>2.11838004</v>
+        <v>2.16881766</v>
       </c>
       <c r="N44">
-        <v>-1.41588004</v>
+        <v>-1.46631766</v>
       </c>
       <c r="O44">
-        <v>-0.4247640120000001</v>
+        <v>-0.4398952979999999</v>
       </c>
       <c r="P44">
-        <v>-0.9911160280000002</v>
+        <v>-1.026422362</v>
       </c>
       <c r="Q44">
-        <v>-0.8711160280000002</v>
+        <v>-0.9064223619999997</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1706722436667094</v>
+        <v>0.1728629847836692</v>
       </c>
       <c r="T44">
-        <v>0.8706645456608803</v>
+        <v>0.8859393622514219</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.09948639810635677</v>
+        <v>0.09717276094109269</v>
       </c>
       <c r="W44">
-        <v>0.2123411073265211</v>
+        <v>0.2128866629700903</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3316213270211893</v>
+        <v>0.3239092031369757</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1900731664038303</v>
+        <v>0.1919731664038303</v>
       </c>
       <c r="C45">
-        <v>3.896490510686142</v>
+        <v>3.555542828630747</v>
       </c>
       <c r="D45">
-        <v>9.774190510686141</v>
+        <v>9.647142828630747</v>
       </c>
       <c r="E45">
-        <v>7.0077</v>
+        <v>7.2216</v>
       </c>
       <c r="F45">
-        <v>9.197699999999999</v>
+        <v>9.4116</v>
       </c>
       <c r="G45">
         <v>3.32</v>
@@ -4965,37 +4965,37 @@
         <v>0.7025</v>
       </c>
       <c r="M45">
-        <v>2.16881766</v>
+        <v>2.21925528</v>
       </c>
       <c r="N45">
-        <v>-1.46631766</v>
+        <v>-1.51675528</v>
       </c>
       <c r="O45">
-        <v>-0.4398952979999999</v>
+        <v>-0.455026584</v>
       </c>
       <c r="P45">
-        <v>-1.026422362</v>
+        <v>-1.061728696</v>
       </c>
       <c r="Q45">
-        <v>-0.9064223619999997</v>
+        <v>-0.9417286959999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1728629847836692</v>
+        <v>0.1751319666548062</v>
       </c>
       <c r="T45">
-        <v>0.8859393622514219</v>
+        <v>0.9017597080059118</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.09717276094109269</v>
+        <v>0.09496428910152238</v>
       </c>
       <c r="W45">
-        <v>0.2128866629700903</v>
+        <v>0.213407420629861</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3239092031369757</v>
+        <v>0.3165476303384079</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1919731664038303</v>
+        <v>0.1938731664038303</v>
       </c>
       <c r="C46">
-        <v>3.555542828630747</v>
+        <v>3.21785556980757</v>
       </c>
       <c r="D46">
-        <v>9.647142828630747</v>
+        <v>9.52335556980757</v>
       </c>
       <c r="E46">
-        <v>7.2216</v>
+        <v>7.435500000000001</v>
       </c>
       <c r="F46">
-        <v>9.4116</v>
+        <v>9.625500000000001</v>
       </c>
       <c r="G46">
         <v>3.32</v>
@@ -5047,37 +5047,37 @@
         <v>0.7025</v>
       </c>
       <c r="M46">
-        <v>2.21925528</v>
+        <v>2.2696929</v>
       </c>
       <c r="N46">
-        <v>-1.51675528</v>
+        <v>-1.5671929</v>
       </c>
       <c r="O46">
-        <v>-0.455026584</v>
+        <v>-0.47015787</v>
       </c>
       <c r="P46">
-        <v>-1.061728696</v>
+        <v>-1.09703503</v>
       </c>
       <c r="Q46">
-        <v>-0.9417286959999999</v>
+        <v>-0.9770350300000002</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1751319666548062</v>
+        <v>0.1774834569576208</v>
       </c>
       <c r="T46">
-        <v>0.9017597080059118</v>
+        <v>0.9181553390605647</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09496428910152238</v>
+        <v>0.09285397156593297</v>
       </c>
       <c r="W46">
-        <v>0.213407420629861</v>
+        <v>0.213905033504753</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3165476303384079</v>
+        <v>0.30951323855311</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1938731664038303</v>
+        <v>0.1957731664038303</v>
       </c>
       <c r="C47">
-        <v>3.21785556980757</v>
+        <v>2.883304815965966</v>
       </c>
       <c r="D47">
-        <v>9.52335556980757</v>
+        <v>9.402704815965967</v>
       </c>
       <c r="E47">
-        <v>7.435500000000001</v>
+        <v>7.649400000000002</v>
       </c>
       <c r="F47">
-        <v>9.625500000000001</v>
+        <v>9.839400000000001</v>
       </c>
       <c r="G47">
         <v>3.32</v>
@@ -5129,37 +5129,37 @@
         <v>0.7025</v>
       </c>
       <c r="M47">
-        <v>2.2696929</v>
+        <v>2.32013052</v>
       </c>
       <c r="N47">
-        <v>-1.5671929</v>
+        <v>-1.61763052</v>
       </c>
       <c r="O47">
-        <v>-0.47015787</v>
+        <v>-0.485289156</v>
       </c>
       <c r="P47">
-        <v>-1.09703503</v>
+        <v>-1.132341364</v>
       </c>
       <c r="Q47">
-        <v>-0.9770350300000002</v>
+        <v>-1.012341364</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1774834569576208</v>
+        <v>0.179922039493873</v>
       </c>
       <c r="T47">
-        <v>0.9181553390605647</v>
+        <v>0.9351582157098344</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09285397156593297</v>
+        <v>0.09083540696667358</v>
       </c>
       <c r="W47">
-        <v>0.213905033504753</v>
+        <v>0.2143810110372584</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.30951323855311</v>
+        <v>0.3027846898889119</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1957731664038303</v>
+        <v>0.1976731664038303</v>
       </c>
       <c r="C48">
-        <v>2.883304815965966</v>
+        <v>2.551772849942212</v>
       </c>
       <c r="D48">
-        <v>9.402704815965967</v>
+        <v>9.285072849942212</v>
       </c>
       <c r="E48">
-        <v>7.649400000000002</v>
+        <v>7.863300000000001</v>
       </c>
       <c r="F48">
-        <v>9.839400000000001</v>
+        <v>10.0533</v>
       </c>
       <c r="G48">
         <v>3.32</v>
@@ -5211,37 +5211,37 @@
         <v>0.7025</v>
       </c>
       <c r="M48">
-        <v>2.32013052</v>
+        <v>2.37056814</v>
       </c>
       <c r="N48">
-        <v>-1.61763052</v>
+        <v>-1.66806814</v>
       </c>
       <c r="O48">
-        <v>-0.485289156</v>
+        <v>-0.5004204419999999</v>
       </c>
       <c r="P48">
-        <v>-1.132341364</v>
+        <v>-1.167647698</v>
       </c>
       <c r="Q48">
-        <v>-1.012341364</v>
+        <v>-1.047647698</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.179922039493873</v>
+        <v>0.1824526440126253</v>
       </c>
       <c r="T48">
-        <v>0.9351582157098344</v>
+        <v>0.9528027103458689</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09083540696667358</v>
+        <v>0.08890273873334009</v>
       </c>
       <c r="W48">
-        <v>0.2143810110372584</v>
+        <v>0.2148367342066784</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3027846898889119</v>
+        <v>0.296342462444467</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1976731664038303</v>
+        <v>0.1995731664038303</v>
       </c>
       <c r="C49">
-        <v>2.551772849942212</v>
+        <v>2.22314777256063</v>
       </c>
       <c r="D49">
-        <v>9.285072849942212</v>
+        <v>9.17034777256063</v>
       </c>
       <c r="E49">
-        <v>7.863300000000001</v>
+        <v>8.077200000000001</v>
       </c>
       <c r="F49">
-        <v>10.0533</v>
+        <v>10.2672</v>
       </c>
       <c r="G49">
         <v>3.32</v>
@@ -5293,37 +5293,37 @@
         <v>0.7025</v>
       </c>
       <c r="M49">
-        <v>2.37056814</v>
+        <v>2.42100576</v>
       </c>
       <c r="N49">
-        <v>-1.66806814</v>
+        <v>-1.71850576</v>
       </c>
       <c r="O49">
-        <v>-0.5004204419999999</v>
+        <v>-0.515551728</v>
       </c>
       <c r="P49">
-        <v>-1.167647698</v>
+        <v>-1.202954032</v>
       </c>
       <c r="Q49">
-        <v>-1.047647698</v>
+        <v>-1.082954032</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1824526440126253</v>
+        <v>0.1850805794744066</v>
       </c>
       <c r="T49">
-        <v>0.9528027103458689</v>
+        <v>0.971125839390982</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08890273873334009</v>
+        <v>0.08705059834306217</v>
       </c>
       <c r="W49">
-        <v>0.2148367342066784</v>
+        <v>0.215273468910706</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.296342462444467</v>
+        <v>0.2901686611435407</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1995731664038303</v>
+        <v>0.2014731664038303</v>
       </c>
       <c r="C50">
-        <v>2.223147772560631</v>
+        <v>1.897323147589193</v>
       </c>
       <c r="D50">
-        <v>9.170347772560632</v>
+        <v>9.058423147589192</v>
       </c>
       <c r="E50">
-        <v>8.077200000000001</v>
+        <v>8.2911</v>
       </c>
       <c r="F50">
-        <v>10.2672</v>
+        <v>10.4811</v>
       </c>
       <c r="G50">
         <v>3.32</v>
@@ -5375,37 +5375,37 @@
         <v>0.7025</v>
       </c>
       <c r="M50">
-        <v>2.42100576</v>
+        <v>2.47144338</v>
       </c>
       <c r="N50">
-        <v>-1.71850576</v>
+        <v>-1.76894338</v>
       </c>
       <c r="O50">
-        <v>-0.515551728</v>
+        <v>-0.530683014</v>
       </c>
       <c r="P50">
-        <v>-1.202954032</v>
+        <v>-1.238260366</v>
       </c>
       <c r="Q50">
-        <v>-1.082954032</v>
+        <v>-1.118260366</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1850805794744066</v>
+        <v>0.1878115712288067</v>
       </c>
       <c r="T50">
-        <v>0.9711258393909818</v>
+        <v>0.9901675225162951</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08705059834306217</v>
+        <v>0.08527405551973437</v>
       </c>
       <c r="W50">
-        <v>0.215273468910706</v>
+        <v>0.2156923777084467</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2901686611435407</v>
+        <v>0.284246851732448</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2014731664038303</v>
+        <v>0.2033731664038303</v>
       </c>
       <c r="C51">
-        <v>1.897323147589193</v>
+        <v>1.574197672381626</v>
       </c>
       <c r="D51">
-        <v>9.058423147589192</v>
+        <v>8.949197672381626</v>
       </c>
       <c r="E51">
-        <v>8.2911</v>
+        <v>8.505000000000001</v>
       </c>
       <c r="F51">
-        <v>10.4811</v>
+        <v>10.695</v>
       </c>
       <c r="G51">
         <v>3.32</v>
@@ -5457,37 +5457,37 @@
         <v>0.7025</v>
       </c>
       <c r="M51">
-        <v>2.47144338</v>
+        <v>2.521881</v>
       </c>
       <c r="N51">
-        <v>-1.76894338</v>
+        <v>-1.819381</v>
       </c>
       <c r="O51">
-        <v>-0.530683014</v>
+        <v>-0.5458143</v>
       </c>
       <c r="P51">
-        <v>-1.238260366</v>
+        <v>-1.2735667</v>
       </c>
       <c r="Q51">
-        <v>-1.118260366</v>
+        <v>-1.1535667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1878115712288067</v>
+        <v>0.1906518026533829</v>
       </c>
       <c r="T51">
-        <v>0.9901675225162951</v>
+        <v>1.009970872966621</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08527405551973437</v>
+        <v>0.08356857440933969</v>
       </c>
       <c r="W51">
-        <v>0.2156923777084467</v>
+        <v>0.2160945301542777</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.284246851732448</v>
+        <v>0.278561914697799</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2033731664038303</v>
+        <v>0.2052731664038303</v>
       </c>
       <c r="C52">
-        <v>1.574197672381626</v>
+        <v>1.25367487206381</v>
       </c>
       <c r="D52">
-        <v>8.949197672381626</v>
+        <v>8.84257487206381</v>
       </c>
       <c r="E52">
-        <v>8.505000000000001</v>
+        <v>8.718900000000001</v>
       </c>
       <c r="F52">
-        <v>10.695</v>
+        <v>10.9089</v>
       </c>
       <c r="G52">
         <v>3.32</v>
@@ -5539,37 +5539,37 @@
         <v>0.7025</v>
       </c>
       <c r="M52">
-        <v>2.521881</v>
+        <v>2.57231862</v>
       </c>
       <c r="N52">
-        <v>-1.819381</v>
+        <v>-1.86981862</v>
       </c>
       <c r="O52">
-        <v>-0.5458143</v>
+        <v>-0.560945586</v>
       </c>
       <c r="P52">
-        <v>-1.2735667</v>
+        <v>-1.308873034</v>
       </c>
       <c r="Q52">
-        <v>-1.1535667</v>
+        <v>-1.188873034</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1906518026533829</v>
+        <v>0.193607961891207</v>
       </c>
       <c r="T52">
-        <v>1.009970872966621</v>
+        <v>1.030582523435328</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08356857440933969</v>
+        <v>0.08192997491111732</v>
       </c>
       <c r="W52">
-        <v>0.2160945301542777</v>
+        <v>0.2164809119159586</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.278561914697799</v>
+        <v>0.2730999163703912</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2052731664038303</v>
+        <v>0.2071731664038303</v>
       </c>
       <c r="C53">
-        <v>1.25367487206381</v>
+        <v>0.935662815323985</v>
       </c>
       <c r="D53">
-        <v>8.84257487206381</v>
+        <v>8.738462815323985</v>
       </c>
       <c r="E53">
-        <v>8.718900000000001</v>
+        <v>8.9328</v>
       </c>
       <c r="F53">
-        <v>10.9089</v>
+        <v>11.1228</v>
       </c>
       <c r="G53">
         <v>3.32</v>
@@ -5621,37 +5621,37 @@
         <v>0.7025</v>
       </c>
       <c r="M53">
-        <v>2.57231862</v>
+        <v>2.62275624</v>
       </c>
       <c r="N53">
-        <v>-1.86981862</v>
+        <v>-1.92025624</v>
       </c>
       <c r="O53">
-        <v>-0.560945586</v>
+        <v>-0.576076872</v>
       </c>
       <c r="P53">
-        <v>-1.308873034</v>
+        <v>-1.344179368</v>
       </c>
       <c r="Q53">
-        <v>-1.188873034</v>
+        <v>-1.224179368</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.193607961891207</v>
+        <v>0.1966872944306072</v>
       </c>
       <c r="T53">
-        <v>1.030582523435328</v>
+        <v>1.052052992673564</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08192997491111732</v>
+        <v>0.08035439847051894</v>
       </c>
       <c r="W53">
-        <v>0.2164809119159586</v>
+        <v>0.2168524328406516</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2730999163703912</v>
+        <v>0.2678479949017298</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2071731664038303</v>
+        <v>0.2090731664038303</v>
       </c>
       <c r="C54">
-        <v>0.935662815323985</v>
+        <v>0.6200738500469196</v>
       </c>
       <c r="D54">
-        <v>8.738462815323985</v>
+        <v>8.63677385004692</v>
       </c>
       <c r="E54">
-        <v>8.9328</v>
+        <v>9.146700000000001</v>
       </c>
       <c r="F54">
-        <v>11.1228</v>
+        <v>11.3367</v>
       </c>
       <c r="G54">
         <v>3.32</v>
@@ -5703,37 +5703,37 @@
         <v>0.7025</v>
       </c>
       <c r="M54">
-        <v>2.62275624</v>
+        <v>2.67319386</v>
       </c>
       <c r="N54">
-        <v>-1.92025624</v>
+        <v>-1.97069386</v>
       </c>
       <c r="O54">
-        <v>-0.576076872</v>
+        <v>-0.5912081579999999</v>
       </c>
       <c r="P54">
-        <v>-1.344179368</v>
+        <v>-1.379485702</v>
       </c>
       <c r="Q54">
-        <v>-1.224179368</v>
+        <v>-1.259485702</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1966872944306072</v>
+        <v>0.1998976623972158</v>
       </c>
       <c r="T54">
-        <v>1.052052992673564</v>
+        <v>1.074437098900661</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08035439847051894</v>
+        <v>0.07883827774466008</v>
       </c>
       <c r="W54">
-        <v>0.2168524328406516</v>
+        <v>0.2172099341078091</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2678479949017298</v>
+        <v>0.262794259148867</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2090731664038303</v>
+        <v>0.2109731664038303</v>
       </c>
       <c r="C55">
-        <v>0.6200738500469196</v>
+        <v>0.3068243571942553</v>
       </c>
       <c r="D55">
-        <v>8.63677385004692</v>
+        <v>8.537424357194256</v>
       </c>
       <c r="E55">
-        <v>9.146700000000001</v>
+        <v>9.360600000000002</v>
       </c>
       <c r="F55">
-        <v>11.3367</v>
+        <v>11.5506</v>
       </c>
       <c r="G55">
         <v>3.32</v>
@@ -5785,37 +5785,37 @@
         <v>0.7025</v>
       </c>
       <c r="M55">
-        <v>2.67319386</v>
+        <v>2.72363148</v>
       </c>
       <c r="N55">
-        <v>-1.97069386</v>
+        <v>-2.02113148</v>
       </c>
       <c r="O55">
-        <v>-0.5912081579999999</v>
+        <v>-0.6063394440000001</v>
       </c>
       <c r="P55">
-        <v>-1.379485702</v>
+        <v>-1.414792036</v>
       </c>
       <c r="Q55">
-        <v>-1.259485702</v>
+        <v>-1.294792036</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1998976623972158</v>
+        <v>0.203247611579764</v>
       </c>
       <c r="T55">
-        <v>1.074437098900661</v>
+        <v>1.097794427137632</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07883827774466008</v>
+        <v>0.07737830963827749</v>
       </c>
       <c r="W55">
-        <v>0.2172099341078091</v>
+        <v>0.2175541945872942</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.262794259148867</v>
+        <v>0.2579276987942584</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2109731664038303</v>
+        <v>0.2128731664038303</v>
       </c>
       <c r="C56">
-        <v>0.3068243571942553</v>
+        <v>-0.004165478521564125</v>
       </c>
       <c r="D56">
-        <v>8.537424357194256</v>
+        <v>8.440334521478437</v>
       </c>
       <c r="E56">
-        <v>9.360600000000002</v>
+        <v>9.574500000000002</v>
       </c>
       <c r="F56">
-        <v>11.5506</v>
+        <v>11.7645</v>
       </c>
       <c r="G56">
         <v>3.32</v>
@@ -5867,37 +5867,37 @@
         <v>0.7025</v>
       </c>
       <c r="M56">
-        <v>2.72363148</v>
+        <v>2.774069100000001</v>
       </c>
       <c r="N56">
-        <v>-2.02113148</v>
+        <v>-2.0715691</v>
       </c>
       <c r="O56">
-        <v>-0.6063394440000001</v>
+        <v>-0.6214707300000001</v>
       </c>
       <c r="P56">
-        <v>-1.414792036</v>
+        <v>-1.450098370000001</v>
       </c>
       <c r="Q56">
-        <v>-1.294792036</v>
+        <v>-1.33009837</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.203247611579764</v>
+        <v>0.2067464473926477</v>
       </c>
       <c r="T56">
-        <v>1.097794427137632</v>
+        <v>1.122189858851802</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07737830963827749</v>
+        <v>0.07597143128121789</v>
       </c>
       <c r="W56">
-        <v>0.2175541945872942</v>
+        <v>0.2178859365038888</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2579276987942584</v>
+        <v>0.2532381042707263</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2128731664038303</v>
+        <v>0.2147731664038303</v>
       </c>
       <c r="C57">
-        <v>-0.004165478521564125</v>
+        <v>-0.3129718824915457</v>
       </c>
       <c r="D57">
-        <v>8.440334521478437</v>
+        <v>8.345428117508455</v>
       </c>
       <c r="E57">
-        <v>9.574500000000002</v>
+        <v>9.788400000000001</v>
       </c>
       <c r="F57">
-        <v>11.7645</v>
+        <v>11.9784</v>
       </c>
       <c r="G57">
         <v>3.32</v>
@@ -5949,37 +5949,37 @@
         <v>0.7025</v>
       </c>
       <c r="M57">
-        <v>2.774069100000001</v>
+        <v>2.82450672</v>
       </c>
       <c r="N57">
-        <v>-2.0715691</v>
+        <v>-2.12200672</v>
       </c>
       <c r="O57">
-        <v>-0.6214707300000001</v>
+        <v>-0.6366020160000001</v>
       </c>
       <c r="P57">
-        <v>-1.450098370000001</v>
+        <v>-1.485404704</v>
       </c>
       <c r="Q57">
-        <v>-1.33009837</v>
+        <v>-1.365404704</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2067464473926477</v>
+        <v>0.210404321197026</v>
       </c>
       <c r="T57">
-        <v>1.122189858851802</v>
+        <v>1.147694173825706</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07597143128121789</v>
+        <v>0.07461479857976758</v>
       </c>
       <c r="W57">
-        <v>0.2178859365038888</v>
+        <v>0.2182058304948908</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2532381042707263</v>
+        <v>0.2487159952658919</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2147731664038303</v>
+        <v>0.2166731664038303</v>
       </c>
       <c r="C58">
-        <v>-0.3129718824915457</v>
+        <v>-0.619667689796902</v>
       </c>
       <c r="D58">
-        <v>8.345428117508455</v>
+        <v>8.252632310203099</v>
       </c>
       <c r="E58">
-        <v>9.788400000000001</v>
+        <v>10.0023</v>
       </c>
       <c r="F58">
-        <v>11.9784</v>
+        <v>12.1923</v>
       </c>
       <c r="G58">
         <v>3.32</v>
@@ -6031,37 +6031,37 @@
         <v>0.7025</v>
       </c>
       <c r="M58">
-        <v>2.82450672</v>
+        <v>2.87494434</v>
       </c>
       <c r="N58">
-        <v>-2.12200672</v>
+        <v>-2.17244434</v>
       </c>
       <c r="O58">
-        <v>-0.6366020160000001</v>
+        <v>-0.651733302</v>
       </c>
       <c r="P58">
-        <v>-1.485404704</v>
+        <v>-1.520711038</v>
       </c>
       <c r="Q58">
-        <v>-1.365404704</v>
+        <v>-1.400711038</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.210404321197026</v>
+        <v>0.2142323286667243</v>
       </c>
       <c r="T58">
-        <v>1.147694173825706</v>
+        <v>1.174384736007699</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07461479857976758</v>
+        <v>0.07330576702573657</v>
       </c>
       <c r="W58">
-        <v>0.2182058304948908</v>
+        <v>0.2185145001353313</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2487159952658919</v>
+        <v>0.2443525567524553</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2166731664038303</v>
+        <v>0.2185731664038303</v>
       </c>
       <c r="C59">
-        <v>-0.619667689796902</v>
+        <v>-0.9243225316265438</v>
       </c>
       <c r="D59">
-        <v>8.252632310203099</v>
+        <v>8.161877468373458</v>
       </c>
       <c r="E59">
-        <v>10.0023</v>
+        <v>10.2162</v>
       </c>
       <c r="F59">
-        <v>12.1923</v>
+        <v>12.4062</v>
       </c>
       <c r="G59">
         <v>3.32</v>
@@ -6113,37 +6113,37 @@
         <v>0.7025</v>
       </c>
       <c r="M59">
-        <v>2.87494434</v>
+        <v>2.925381960000001</v>
       </c>
       <c r="N59">
-        <v>-2.17244434</v>
+        <v>-2.22288196</v>
       </c>
       <c r="O59">
-        <v>-0.651733302</v>
+        <v>-0.6668645880000001</v>
       </c>
       <c r="P59">
-        <v>-1.520711038</v>
+        <v>-1.556017372</v>
       </c>
       <c r="Q59">
-        <v>-1.400711038</v>
+        <v>-1.436017372</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2142323286667243</v>
+        <v>0.2182426222064082</v>
       </c>
       <c r="T59">
-        <v>1.174384736007699</v>
+        <v>1.202346277341216</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07330576702573657</v>
+        <v>0.07204187449081007</v>
       </c>
       <c r="W59">
-        <v>0.2185145001353313</v>
+        <v>0.218812525995067</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2443525567524553</v>
+        <v>0.2401395816360336</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2185731664038303</v>
+        <v>0.2204731664038303</v>
       </c>
       <c r="C60">
-        <v>-0.924322531626542</v>
+        <v>-1.227003009528094</v>
       </c>
       <c r="D60">
-        <v>8.161877468373458</v>
+        <v>8.073096990471905</v>
       </c>
       <c r="E60">
-        <v>10.2162</v>
+        <v>10.4301</v>
       </c>
       <c r="F60">
-        <v>12.4062</v>
+        <v>12.6201</v>
       </c>
       <c r="G60">
         <v>3.32</v>
@@ -6195,37 +6195,37 @@
         <v>0.7025</v>
       </c>
       <c r="M60">
-        <v>2.92538196</v>
+        <v>2.97581958</v>
       </c>
       <c r="N60">
-        <v>-2.22288196</v>
+        <v>-2.27331958</v>
       </c>
       <c r="O60">
-        <v>-0.666864588</v>
+        <v>-0.6819958739999999</v>
       </c>
       <c r="P60">
-        <v>-1.556017372</v>
+        <v>-1.591323706</v>
       </c>
       <c r="Q60">
-        <v>-1.436017372</v>
+        <v>-1.471323706</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2182426222064082</v>
+        <v>0.2224485398211986</v>
       </c>
       <c r="T60">
-        <v>1.202346277341215</v>
+        <v>1.231671796300757</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07204187449081008</v>
+        <v>0.07082082577062686</v>
       </c>
       <c r="W60">
-        <v>0.218812525995067</v>
+        <v>0.2191004492832862</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2401395816360337</v>
+        <v>0.2360694192354229</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2204731664038303</v>
+        <v>0.2223731664038303</v>
       </c>
       <c r="C61">
-        <v>-1.227003009528094</v>
+        <v>-1.527772858408847</v>
       </c>
       <c r="D61">
-        <v>8.073096990471905</v>
+        <v>7.986227141591153</v>
       </c>
       <c r="E61">
-        <v>10.4301</v>
+        <v>10.644</v>
       </c>
       <c r="F61">
-        <v>12.6201</v>
+        <v>12.834</v>
       </c>
       <c r="G61">
         <v>3.32</v>
@@ -6277,37 +6277,37 @@
         <v>0.7025</v>
       </c>
       <c r="M61">
-        <v>2.97581958</v>
+        <v>3.0262572</v>
       </c>
       <c r="N61">
-        <v>-2.27331958</v>
+        <v>-2.3237572</v>
       </c>
       <c r="O61">
-        <v>-0.6819958739999999</v>
+        <v>-0.6971271599999999</v>
       </c>
       <c r="P61">
-        <v>-1.591323706</v>
+        <v>-1.62663004</v>
       </c>
       <c r="Q61">
-        <v>-1.471323706</v>
+        <v>-1.50663004</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2224485398211986</v>
+        <v>0.2268647533167286</v>
       </c>
       <c r="T61">
-        <v>1.231671796300757</v>
+        <v>1.262463591208276</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07082082577062686</v>
+        <v>0.06964047867444975</v>
       </c>
       <c r="W61">
-        <v>0.2191004492832862</v>
+        <v>0.2193787751285647</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2360694192354229</v>
+        <v>0.2321349289148326</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2223731664038303</v>
+        <v>0.2242731664038303</v>
       </c>
       <c r="C62">
-        <v>-1.527772858408847</v>
+        <v>-1.826693099124974</v>
       </c>
       <c r="D62">
-        <v>7.986227141591153</v>
+        <v>7.901206900875026</v>
       </c>
       <c r="E62">
-        <v>10.644</v>
+        <v>10.8579</v>
       </c>
       <c r="F62">
-        <v>12.834</v>
+        <v>13.0479</v>
       </c>
       <c r="G62">
         <v>3.32</v>
@@ -6359,37 +6359,37 @@
         <v>0.7025</v>
       </c>
       <c r="M62">
-        <v>3.0262572</v>
+        <v>3.07669482</v>
       </c>
       <c r="N62">
-        <v>-2.3237572</v>
+        <v>-2.37419482</v>
       </c>
       <c r="O62">
-        <v>-0.6971271599999999</v>
+        <v>-0.712258446</v>
       </c>
       <c r="P62">
-        <v>-1.62663004</v>
+        <v>-1.661936374</v>
       </c>
       <c r="Q62">
-        <v>-1.50663004</v>
+        <v>-1.541936374</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2268647533167286</v>
+        <v>0.2315074392992088</v>
       </c>
       <c r="T62">
-        <v>1.262463591208276</v>
+        <v>1.294834452521309</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06964047867444975</v>
+        <v>0.06849883148306532</v>
       </c>
       <c r="W62">
-        <v>0.2193787751285647</v>
+        <v>0.2196479755362932</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2321349289148326</v>
+        <v>0.2283294382768845</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2242731664038303</v>
+        <v>0.2261731664038303</v>
       </c>
       <c r="C63">
-        <v>-1.826693099124974</v>
+        <v>-2.123822181426787</v>
       </c>
       <c r="D63">
-        <v>7.901206900875026</v>
+        <v>7.817977818573214</v>
       </c>
       <c r="E63">
-        <v>10.8579</v>
+        <v>11.0718</v>
       </c>
       <c r="F63">
-        <v>13.0479</v>
+        <v>13.2618</v>
       </c>
       <c r="G63">
         <v>3.32</v>
@@ -6441,37 +6441,37 @@
         <v>0.7025</v>
       </c>
       <c r="M63">
-        <v>3.07669482</v>
+        <v>3.12713244</v>
       </c>
       <c r="N63">
-        <v>-2.37419482</v>
+        <v>-2.42463244</v>
       </c>
       <c r="O63">
-        <v>-0.712258446</v>
+        <v>-0.7273897320000001</v>
       </c>
       <c r="P63">
-        <v>-1.661936374</v>
+        <v>-1.697242708</v>
       </c>
       <c r="Q63">
-        <v>-1.541936374</v>
+        <v>-1.577242708</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2315074392992088</v>
+        <v>0.2363944771755038</v>
       </c>
       <c r="T63">
-        <v>1.294834452521309</v>
+        <v>1.328909043377133</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06849883148306532</v>
+        <v>0.06739401162043522</v>
       </c>
       <c r="W63">
-        <v>0.2196479755362932</v>
+        <v>0.2199084920599014</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2283294382768845</v>
+        <v>0.2246467054014508</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2261731664038303</v>
+        <v>0.2280731664038303</v>
       </c>
       <c r="C64">
-        <v>-2.123822181426787</v>
+        <v>-2.419216117963662</v>
       </c>
       <c r="D64">
-        <v>7.817977818573214</v>
+        <v>7.736483882036338</v>
       </c>
       <c r="E64">
-        <v>11.0718</v>
+        <v>11.2857</v>
       </c>
       <c r="F64">
-        <v>13.2618</v>
+        <v>13.4757</v>
       </c>
       <c r="G64">
         <v>3.32</v>
@@ -6523,37 +6523,37 @@
         <v>0.7025</v>
       </c>
       <c r="M64">
-        <v>3.12713244</v>
+        <v>3.17757006</v>
       </c>
       <c r="N64">
-        <v>-2.42463244</v>
+        <v>-2.47507006</v>
       </c>
       <c r="O64">
-        <v>-0.7273897320000001</v>
+        <v>-0.7425210179999999</v>
       </c>
       <c r="P64">
-        <v>-1.697242708</v>
+        <v>-1.732549042</v>
       </c>
       <c r="Q64">
-        <v>-1.577242708</v>
+        <v>-1.612549042</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2363944771755038</v>
+        <v>0.2415456792613282</v>
       </c>
       <c r="T64">
-        <v>1.328909043377133</v>
+        <v>1.364825504008947</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06739401162043522</v>
+        <v>0.06632426540423786</v>
       </c>
       <c r="W64">
-        <v>0.2199084920599014</v>
+        <v>0.2201607382176807</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2246467054014508</v>
+        <v>0.2210808846807929</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2280731664038303</v>
+        <v>0.2299731664038303</v>
       </c>
       <c r="C65">
-        <v>-2.419216117963662</v>
+        <v>-2.712928609994334</v>
       </c>
       <c r="D65">
-        <v>7.736483882036338</v>
+        <v>7.656671390005667</v>
       </c>
       <c r="E65">
-        <v>11.2857</v>
+        <v>11.4996</v>
       </c>
       <c r="F65">
-        <v>13.4757</v>
+        <v>13.6896</v>
       </c>
       <c r="G65">
         <v>3.32</v>
@@ -6605,37 +6605,37 @@
         <v>0.7025</v>
       </c>
       <c r="M65">
-        <v>3.17757006</v>
+        <v>3.22800768</v>
       </c>
       <c r="N65">
-        <v>-2.47507006</v>
+        <v>-2.52550768</v>
       </c>
       <c r="O65">
-        <v>-0.7425210179999999</v>
+        <v>-0.7576523039999999</v>
       </c>
       <c r="P65">
-        <v>-1.732549042</v>
+        <v>-1.767855376</v>
       </c>
       <c r="Q65">
-        <v>-1.612549042</v>
+        <v>-1.647855376</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2415456792613282</v>
+        <v>0.2469830592408096</v>
       </c>
       <c r="T65">
-        <v>1.364825504008947</v>
+        <v>1.402737323564752</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06632426540423786</v>
+        <v>0.06528794875729663</v>
       </c>
       <c r="W65">
-        <v>0.2201607382176807</v>
+        <v>0.2204051016830295</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2210808846807929</v>
+        <v>0.2176264958576555</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2299731664038303</v>
+        <v>0.2318731664038303</v>
       </c>
       <c r="C66">
-        <v>-2.712928609994334</v>
+        <v>-3.005011165395356</v>
       </c>
       <c r="D66">
-        <v>7.656671390005667</v>
+        <v>7.578488834604646</v>
       </c>
       <c r="E66">
-        <v>11.4996</v>
+        <v>11.7135</v>
       </c>
       <c r="F66">
-        <v>13.6896</v>
+        <v>13.9035</v>
       </c>
       <c r="G66">
         <v>3.32</v>
@@ -6687,37 +6687,37 @@
         <v>0.7025</v>
       </c>
       <c r="M66">
-        <v>3.22800768</v>
+        <v>3.2784453</v>
       </c>
       <c r="N66">
-        <v>-2.52550768</v>
+        <v>-2.5759453</v>
       </c>
       <c r="O66">
-        <v>-0.7576523039999999</v>
+        <v>-0.7727835900000001</v>
       </c>
       <c r="P66">
-        <v>-1.767855376</v>
+        <v>-1.80316171</v>
       </c>
       <c r="Q66">
-        <v>-1.647855376</v>
+        <v>-1.68316171</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2469830592408096</v>
+        <v>0.2527311466476899</v>
       </c>
       <c r="T66">
-        <v>1.402737323564752</v>
+        <v>1.442815532809459</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06528794875729663</v>
+        <v>0.06428351877641514</v>
       </c>
       <c r="W66">
-        <v>0.2204051016830295</v>
+        <v>0.2206419462725213</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2176264958576555</v>
+        <v>0.2142783959213839</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2318731664038303</v>
+        <v>0.2337731664038303</v>
       </c>
       <c r="C67">
-        <v>-3.005011165395356</v>
+        <v>-3.29551320951273</v>
       </c>
       <c r="D67">
-        <v>7.578488834604646</v>
+        <v>7.501886790487272</v>
       </c>
       <c r="E67">
-        <v>11.7135</v>
+        <v>11.9274</v>
       </c>
       <c r="F67">
-        <v>13.9035</v>
+        <v>14.1174</v>
       </c>
       <c r="G67">
         <v>3.32</v>
@@ -6769,37 +6769,37 @@
         <v>0.7025</v>
       </c>
       <c r="M67">
-        <v>3.2784453</v>
+        <v>3.328882920000001</v>
       </c>
       <c r="N67">
-        <v>-2.5759453</v>
+        <v>-2.626382920000001</v>
       </c>
       <c r="O67">
-        <v>-0.7727835900000001</v>
+        <v>-0.7879148760000002</v>
       </c>
       <c r="P67">
-        <v>-1.80316171</v>
+        <v>-1.838468044</v>
       </c>
       <c r="Q67">
-        <v>-1.68316171</v>
+        <v>-1.718468044</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2527311466476899</v>
+        <v>0.2588173568432102</v>
       </c>
       <c r="T67">
-        <v>1.442815532809459</v>
+        <v>1.485251283774443</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06428351877641514</v>
+        <v>0.06330952606768157</v>
       </c>
       <c r="W67">
-        <v>0.2206419462725213</v>
+        <v>0.2208716137532407</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2142783959213839</v>
+        <v>0.2110317535589387</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2337731664038303</v>
+        <v>0.2356731664038303</v>
       </c>
       <c r="C68">
-        <v>-3.29551320951273</v>
+        <v>-3.584482189357992</v>
       </c>
       <c r="D68">
-        <v>7.501886790487272</v>
+        <v>7.426817810642008</v>
       </c>
       <c r="E68">
-        <v>11.9274</v>
+        <v>12.1413</v>
       </c>
       <c r="F68">
-        <v>14.1174</v>
+        <v>14.3313</v>
       </c>
       <c r="G68">
         <v>3.32</v>
@@ -6851,37 +6851,37 @@
         <v>0.7025</v>
       </c>
       <c r="M68">
-        <v>3.328882920000001</v>
+        <v>3.37932054</v>
       </c>
       <c r="N68">
-        <v>-2.626382920000001</v>
+        <v>-2.67682054</v>
       </c>
       <c r="O68">
-        <v>-0.7879148760000002</v>
+        <v>-0.803046162</v>
       </c>
       <c r="P68">
-        <v>-1.838468044</v>
+        <v>-1.873774378</v>
       </c>
       <c r="Q68">
-        <v>-1.718468044</v>
+        <v>-1.753774378</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2588173568432102</v>
+        <v>0.2652724282627014</v>
       </c>
       <c r="T68">
-        <v>1.485251283774443</v>
+        <v>1.530258898434275</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06330952606768157</v>
+        <v>0.06236460776816394</v>
       </c>
       <c r="W68">
-        <v>0.2208716137532407</v>
+        <v>0.2210944254882669</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2110317535589387</v>
+        <v>0.2078820258938798</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2356731664038303</v>
+        <v>0.2375731664038303</v>
       </c>
       <c r="C69">
-        <v>-3.584482189357992</v>
+        <v>-3.871963671610342</v>
       </c>
       <c r="D69">
-        <v>7.426817810642008</v>
+        <v>7.35323632838966</v>
       </c>
       <c r="E69">
-        <v>12.1413</v>
+        <v>12.3552</v>
       </c>
       <c r="F69">
-        <v>14.3313</v>
+        <v>14.5452</v>
       </c>
       <c r="G69">
         <v>3.32</v>
@@ -6933,37 +6933,37 @@
         <v>0.7025</v>
       </c>
       <c r="M69">
-        <v>3.37932054</v>
+        <v>3.42975816</v>
       </c>
       <c r="N69">
-        <v>-2.67682054</v>
+        <v>-2.72725816</v>
       </c>
       <c r="O69">
-        <v>-0.803046162</v>
+        <v>-0.818177448</v>
       </c>
       <c r="P69">
-        <v>-1.873774378</v>
+        <v>-1.909080712</v>
       </c>
       <c r="Q69">
-        <v>-1.753774378</v>
+        <v>-1.789080712</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2652724282627014</v>
+        <v>0.2721309416459108</v>
       </c>
       <c r="T69">
-        <v>1.530258898434275</v>
+        <v>1.578079489010346</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06236460776816394</v>
+        <v>0.061447481183338</v>
       </c>
       <c r="W69">
-        <v>0.2210944254882669</v>
+        <v>0.2213106839369689</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2078820258938798</v>
+        <v>0.2048249372777934</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2375731664038303</v>
+        <v>0.2394731664038303</v>
       </c>
       <c r="C70">
-        <v>-3.871963671610342</v>
+        <v>-4.158001434850133</v>
       </c>
       <c r="D70">
-        <v>7.35323632838966</v>
+        <v>7.281098565149868</v>
       </c>
       <c r="E70">
-        <v>12.3552</v>
+        <v>12.5691</v>
       </c>
       <c r="F70">
-        <v>14.5452</v>
+        <v>14.7591</v>
       </c>
       <c r="G70">
         <v>3.32</v>
@@ -7015,37 +7015,37 @@
         <v>0.7025</v>
       </c>
       <c r="M70">
-        <v>3.42975816</v>
+        <v>3.480195780000001</v>
       </c>
       <c r="N70">
-        <v>-2.72725816</v>
+        <v>-2.777695780000001</v>
       </c>
       <c r="O70">
-        <v>-0.818177448</v>
+        <v>-0.8333087340000002</v>
       </c>
       <c r="P70">
-        <v>-1.909080712</v>
+        <v>-1.944387046000001</v>
       </c>
       <c r="Q70">
-        <v>-1.789080712</v>
+        <v>-1.824387046</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2721309416459108</v>
+        <v>0.2794319397635208</v>
       </c>
       <c r="T70">
-        <v>1.578079489010346</v>
+        <v>1.628985278978422</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.061447481183338</v>
+        <v>0.06055693797778237</v>
       </c>
       <c r="W70">
-        <v>0.2213106839369689</v>
+        <v>0.2215206740248389</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2048249372777934</v>
+        <v>0.2018564599259413</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2394731664038303</v>
+        <v>0.2413731664038303</v>
       </c>
       <c r="C71">
-        <v>-4.158001434850133</v>
+        <v>-4.442637556416111</v>
       </c>
       <c r="D71">
-        <v>7.281098565149868</v>
+        <v>7.210362443583891</v>
       </c>
       <c r="E71">
-        <v>12.5691</v>
+        <v>12.783</v>
       </c>
       <c r="F71">
-        <v>14.7591</v>
+        <v>14.973</v>
       </c>
       <c r="G71">
         <v>3.32</v>
@@ -7097,37 +7097,37 @@
         <v>0.7025</v>
       </c>
       <c r="M71">
-        <v>3.480195780000001</v>
+        <v>3.530633400000001</v>
       </c>
       <c r="N71">
-        <v>-2.777695780000001</v>
+        <v>-2.8281334</v>
       </c>
       <c r="O71">
-        <v>-0.8333087340000002</v>
+        <v>-0.8484400200000001</v>
       </c>
       <c r="P71">
-        <v>-1.944387046000001</v>
+        <v>-1.979693380000001</v>
       </c>
       <c r="Q71">
-        <v>-1.824387046</v>
+        <v>-1.85969338</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2794319397635208</v>
+        <v>0.2872196710889715</v>
       </c>
       <c r="T71">
-        <v>1.628985278978422</v>
+        <v>1.683284788277702</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06055693797778237</v>
+        <v>0.05969183886381405</v>
       </c>
       <c r="W71">
-        <v>0.2215206740248389</v>
+        <v>0.2217246643959127</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2018564599259413</v>
+        <v>0.1989727962127136</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2413731664038303</v>
+        <v>0.2432731664038303</v>
       </c>
       <c r="C72">
-        <v>-4.442637556416111</v>
+        <v>-4.725912494248394</v>
       </c>
       <c r="D72">
-        <v>7.210362443583891</v>
+        <v>7.140987505751608</v>
       </c>
       <c r="E72">
-        <v>12.783</v>
+        <v>12.9969</v>
       </c>
       <c r="F72">
-        <v>14.973</v>
+        <v>15.1869</v>
       </c>
       <c r="G72">
         <v>3.32</v>
@@ -7179,37 +7179,37 @@
         <v>0.7025</v>
       </c>
       <c r="M72">
-        <v>3.530633400000001</v>
+        <v>3.58107102</v>
       </c>
       <c r="N72">
-        <v>-2.8281334</v>
+        <v>-2.87857102</v>
       </c>
       <c r="O72">
-        <v>-0.8484400200000001</v>
+        <v>-0.8635713060000001</v>
       </c>
       <c r="P72">
-        <v>-1.979693380000001</v>
+        <v>-2.014999714</v>
       </c>
       <c r="Q72">
-        <v>-1.85969338</v>
+        <v>-1.894999714</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2872196710889715</v>
+        <v>0.2955444873334188</v>
       </c>
       <c r="T72">
-        <v>1.683284788277702</v>
+        <v>1.741329091321761</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05969183886381405</v>
+        <v>0.05885110873897161</v>
       </c>
       <c r="W72">
-        <v>0.2217246643959127</v>
+        <v>0.2219229085593505</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1989727962127136</v>
+        <v>0.1961703624632387</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2432731664038303</v>
+        <v>0.2451731664038303</v>
       </c>
       <c r="C73">
-        <v>-4.725912494248391</v>
+        <v>-5.00786516405174</v>
       </c>
       <c r="D73">
-        <v>7.140987505751609</v>
+        <v>7.07293483594826</v>
       </c>
       <c r="E73">
-        <v>12.9969</v>
+        <v>13.2108</v>
       </c>
       <c r="F73">
-        <v>15.1869</v>
+        <v>15.4008</v>
       </c>
       <c r="G73">
         <v>3.32</v>
@@ -7261,37 +7261,37 @@
         <v>0.7025</v>
       </c>
       <c r="M73">
-        <v>3.58107102</v>
+        <v>3.63150864</v>
       </c>
       <c r="N73">
-        <v>-2.87857102</v>
+        <v>-2.92900864</v>
       </c>
       <c r="O73">
-        <v>-0.863571306</v>
+        <v>-0.878702592</v>
       </c>
       <c r="P73">
-        <v>-2.014999714</v>
+        <v>-2.050306048</v>
       </c>
       <c r="Q73">
-        <v>-1.894999714</v>
+        <v>-1.930306048</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2955444873334187</v>
+        <v>0.3044639333096122</v>
       </c>
       <c r="T73">
-        <v>1.741329091321761</v>
+        <v>1.803519416011823</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05885110873897161</v>
+        <v>0.05803373222870811</v>
       </c>
       <c r="W73">
-        <v>0.2219229085593505</v>
+        <v>0.2221156459404706</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1961703624632387</v>
+        <v>0.1934457740956937</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2451731664038303</v>
+        <v>0.2470731664038303</v>
       </c>
       <c r="C74">
-        <v>-5.00786516405174</v>
+        <v>-5.288533012088367</v>
       </c>
       <c r="D74">
-        <v>7.07293483594826</v>
+        <v>7.006166987911634</v>
       </c>
       <c r="E74">
-        <v>13.2108</v>
+        <v>13.4247</v>
       </c>
       <c r="F74">
-        <v>15.4008</v>
+        <v>15.6147</v>
       </c>
       <c r="G74">
         <v>3.32</v>
@@ -7343,37 +7343,37 @@
         <v>0.7025</v>
       </c>
       <c r="M74">
-        <v>3.63150864</v>
+        <v>3.681946260000001</v>
       </c>
       <c r="N74">
-        <v>-2.92900864</v>
+        <v>-2.97944626</v>
       </c>
       <c r="O74">
-        <v>-0.878702592</v>
+        <v>-0.8938338780000001</v>
       </c>
       <c r="P74">
-        <v>-2.050306048</v>
+        <v>-2.085612382</v>
       </c>
       <c r="Q74">
-        <v>-1.930306048</v>
+        <v>-1.965612382</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3044639333096122</v>
+        <v>0.314044078987746</v>
       </c>
       <c r="T74">
-        <v>1.803519416011823</v>
+        <v>1.870316431419668</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05803373222870811</v>
+        <v>0.05723874959543813</v>
       </c>
       <c r="W74">
-        <v>0.2221156459404706</v>
+        <v>0.2223031028453957</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1934457740956937</v>
+        <v>0.1907958319847938</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2470731664038303</v>
+        <v>0.2489731664038303</v>
       </c>
       <c r="C75">
-        <v>-5.288533012088367</v>
+        <v>-5.567952083886331</v>
       </c>
       <c r="D75">
-        <v>7.006166987911634</v>
+        <v>6.940647916113669</v>
       </c>
       <c r="E75">
-        <v>13.4247</v>
+        <v>13.6386</v>
       </c>
       <c r="F75">
-        <v>15.6147</v>
+        <v>15.8286</v>
       </c>
       <c r="G75">
         <v>3.32</v>
@@ -7425,37 +7425,37 @@
         <v>0.7025</v>
       </c>
       <c r="M75">
-        <v>3.681946260000001</v>
+        <v>3.73238388</v>
       </c>
       <c r="N75">
-        <v>-2.97944626</v>
+        <v>-3.02988388</v>
       </c>
       <c r="O75">
-        <v>-0.8938338780000001</v>
+        <v>-0.9089651639999999</v>
       </c>
       <c r="P75">
-        <v>-2.085612382</v>
+        <v>-2.120918716</v>
       </c>
       <c r="Q75">
-        <v>-1.965612382</v>
+        <v>-2.000918716</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.314044078987746</v>
+        <v>0.3243611589488132</v>
       </c>
       <c r="T75">
-        <v>1.870316431419668</v>
+        <v>1.942251678781963</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05723874959543813</v>
+        <v>0.05646525297928358</v>
       </c>
       <c r="W75">
-        <v>0.2223031028453957</v>
+        <v>0.2224854933474849</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1907958319847938</v>
+        <v>0.1882175099309453</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2489731664038303</v>
+        <v>0.2508731664038303</v>
       </c>
       <c r="C76">
-        <v>-5.567952083886331</v>
+        <v>-5.84615708912845</v>
       </c>
       <c r="D76">
-        <v>6.940647916113669</v>
+        <v>6.876342910871551</v>
       </c>
       <c r="E76">
-        <v>13.6386</v>
+        <v>13.8525</v>
       </c>
       <c r="F76">
-        <v>15.8286</v>
+        <v>16.0425</v>
       </c>
       <c r="G76">
         <v>3.32</v>
@@ -7507,37 +7507,37 @@
         <v>0.7025</v>
       </c>
       <c r="M76">
-        <v>3.73238388</v>
+        <v>3.7828215</v>
       </c>
       <c r="N76">
-        <v>-3.02988388</v>
+        <v>-3.0803215</v>
       </c>
       <c r="O76">
-        <v>-0.9089651639999999</v>
+        <v>-0.92409645</v>
       </c>
       <c r="P76">
-        <v>-2.120918716</v>
+        <v>-2.15622505</v>
       </c>
       <c r="Q76">
-        <v>-2.000918716</v>
+        <v>-2.03622505</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3243611589488132</v>
+        <v>0.3355036053067657</v>
       </c>
       <c r="T76">
-        <v>1.942251678781963</v>
+        <v>2.019941745933242</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05646525297928358</v>
+        <v>0.05571238293955979</v>
       </c>
       <c r="W76">
-        <v>0.2224854933474849</v>
+        <v>0.2226630201028518</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1882175099309453</v>
+        <v>0.185707943131866</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2508731664038303</v>
+        <v>0.2527731664038303</v>
       </c>
       <c r="C77">
-        <v>-5.84615708912845</v>
+        <v>-6.123181462967155</v>
       </c>
       <c r="D77">
-        <v>6.876342910871551</v>
+        <v>6.813218537032845</v>
       </c>
       <c r="E77">
-        <v>13.8525</v>
+        <v>14.0664</v>
       </c>
       <c r="F77">
-        <v>16.0425</v>
+        <v>16.2564</v>
       </c>
       <c r="G77">
         <v>3.32</v>
@@ -7589,37 +7589,37 @@
         <v>0.7025</v>
       </c>
       <c r="M77">
-        <v>3.7828215</v>
+        <v>3.83325912</v>
       </c>
       <c r="N77">
-        <v>-3.0803215</v>
+        <v>-3.13075912</v>
       </c>
       <c r="O77">
-        <v>-0.92409645</v>
+        <v>-0.939227736</v>
       </c>
       <c r="P77">
-        <v>-2.15622505</v>
+        <v>-2.191531384</v>
       </c>
       <c r="Q77">
-        <v>-2.03622505</v>
+        <v>-2.071531384</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3355036053067657</v>
+        <v>0.3475745888612143</v>
       </c>
       <c r="T77">
-        <v>2.019941745933242</v>
+        <v>2.104105985347128</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05571238293955979</v>
+        <v>0.05497932526930243</v>
       </c>
       <c r="W77">
-        <v>0.2226630201028518</v>
+        <v>0.2228358751014985</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.185707943131866</v>
+        <v>0.1832644175643414</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2527731664038303</v>
+        <v>0.2546731664038303</v>
       </c>
       <c r="C78">
-        <v>-6.123181462967155</v>
+        <v>-6.399057423992877</v>
       </c>
       <c r="D78">
-        <v>6.813218537032845</v>
+        <v>6.751242576007125</v>
       </c>
       <c r="E78">
-        <v>14.0664</v>
+        <v>14.2803</v>
       </c>
       <c r="F78">
-        <v>16.2564</v>
+        <v>16.4703</v>
       </c>
       <c r="G78">
         <v>3.32</v>
@@ -7671,37 +7671,37 @@
         <v>0.7025</v>
       </c>
       <c r="M78">
-        <v>3.83325912</v>
+        <v>3.88369674</v>
       </c>
       <c r="N78">
-        <v>-3.13075912</v>
+        <v>-3.18119674</v>
       </c>
       <c r="O78">
-        <v>-0.939227736</v>
+        <v>-0.954359022</v>
       </c>
       <c r="P78">
-        <v>-2.191531384</v>
+        <v>-2.226837718000001</v>
       </c>
       <c r="Q78">
-        <v>-2.071531384</v>
+        <v>-2.106837718</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3475745888612143</v>
+        <v>0.3606952231595281</v>
       </c>
       <c r="T78">
-        <v>2.104105985347128</v>
+        <v>2.195588854275264</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05497932526930243</v>
+        <v>0.05426530805801278</v>
       </c>
       <c r="W78">
-        <v>0.2228358751014985</v>
+        <v>0.2230042403599206</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1832644175643414</v>
+        <v>0.1808843601933759</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2546731664038303</v>
+        <v>0.2565731664038303</v>
       </c>
       <c r="C79">
-        <v>-6.399057423992877</v>
+        <v>-6.673816029067096</v>
       </c>
       <c r="D79">
-        <v>6.751242576007125</v>
+        <v>6.690383970932905</v>
       </c>
       <c r="E79">
-        <v>14.2803</v>
+        <v>14.4942</v>
       </c>
       <c r="F79">
-        <v>16.4703</v>
+        <v>16.6842</v>
       </c>
       <c r="G79">
         <v>3.32</v>
@@ -7753,37 +7753,37 @@
         <v>0.7025</v>
       </c>
       <c r="M79">
-        <v>3.88369674</v>
+        <v>3.93413436</v>
       </c>
       <c r="N79">
-        <v>-3.18119674</v>
+        <v>-3.23163436</v>
       </c>
       <c r="O79">
-        <v>-0.954359022</v>
+        <v>-0.969490308</v>
       </c>
       <c r="P79">
-        <v>-2.226837718000001</v>
+        <v>-2.262144052</v>
       </c>
       <c r="Q79">
-        <v>-2.106837718</v>
+        <v>-2.142144052</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3606952231595281</v>
+        <v>0.3750086423940521</v>
       </c>
       <c r="T79">
-        <v>2.195588854275264</v>
+        <v>2.295388347651412</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05426530805801278</v>
+        <v>0.05356959898034595</v>
       </c>
       <c r="W79">
-        <v>0.2230042403599206</v>
+        <v>0.2231682885604344</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1808843601933759</v>
+        <v>0.1785653299344866</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2565731664038303</v>
+        <v>0.2584731664038303</v>
       </c>
       <c r="C80">
-        <v>-6.673816029067096</v>
+        <v>-6.947487225216189</v>
       </c>
       <c r="D80">
-        <v>6.690383970932905</v>
+        <v>6.63061277478381</v>
       </c>
       <c r="E80">
-        <v>14.4942</v>
+        <v>14.7081</v>
       </c>
       <c r="F80">
-        <v>16.6842</v>
+        <v>16.8981</v>
       </c>
       <c r="G80">
         <v>3.32</v>
@@ -7835,37 +7835,37 @@
         <v>0.7025</v>
       </c>
       <c r="M80">
-        <v>3.93413436</v>
+        <v>3.98457198</v>
       </c>
       <c r="N80">
-        <v>-3.23163436</v>
+        <v>-3.28207198</v>
       </c>
       <c r="O80">
-        <v>-0.969490308</v>
+        <v>-0.9846215939999999</v>
       </c>
       <c r="P80">
-        <v>-2.262144052</v>
+        <v>-2.297450386</v>
       </c>
       <c r="Q80">
-        <v>-2.142144052</v>
+        <v>-2.177450386</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3750086423940521</v>
+        <v>0.3906852444128164</v>
       </c>
       <c r="T80">
-        <v>2.295388347651412</v>
+        <v>2.404692554682432</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05356959898034595</v>
+        <v>0.05289150279072132</v>
       </c>
       <c r="W80">
-        <v>0.2231682885604344</v>
+        <v>0.2233281836419479</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1785653299344866</v>
+        <v>0.1763050093024044</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2584731664038303</v>
+        <v>0.2603731664038303</v>
       </c>
       <c r="C81">
-        <v>-6.947487225216189</v>
+        <v>-7.220099898768202</v>
       </c>
       <c r="D81">
-        <v>6.63061277478381</v>
+        <v>6.571900101231799</v>
       </c>
       <c r="E81">
-        <v>14.7081</v>
+        <v>14.922</v>
       </c>
       <c r="F81">
-        <v>16.8981</v>
+        <v>17.112</v>
       </c>
       <c r="G81">
         <v>3.32</v>
@@ -7917,37 +7917,37 @@
         <v>0.7025</v>
       </c>
       <c r="M81">
-        <v>3.98457198</v>
+        <v>4.0350096</v>
       </c>
       <c r="N81">
-        <v>-3.28207198</v>
+        <v>-3.3325096</v>
       </c>
       <c r="O81">
-        <v>-0.9846215939999999</v>
+        <v>-0.9997528800000001</v>
       </c>
       <c r="P81">
-        <v>-2.297450386</v>
+        <v>-2.33275672</v>
       </c>
       <c r="Q81">
-        <v>-2.177450386</v>
+        <v>-2.21275672</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3906852444128164</v>
+        <v>0.4079295066334573</v>
       </c>
       <c r="T81">
-        <v>2.404692554682432</v>
+        <v>2.524927182416553</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05289150279072132</v>
+        <v>0.0522303590058373</v>
       </c>
       <c r="W81">
-        <v>0.2233281836419479</v>
+        <v>0.2234840813464236</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1763050093024044</v>
+        <v>0.1741011966861243</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2603731664038303</v>
+        <v>0.2622731664038303</v>
       </c>
       <c r="C82">
-        <v>-7.220099898768202</v>
+        <v>-7.491681921901945</v>
       </c>
       <c r="D82">
-        <v>6.571900101231799</v>
+        <v>6.514218078098057</v>
       </c>
       <c r="E82">
-        <v>14.922</v>
+        <v>15.1359</v>
       </c>
       <c r="F82">
-        <v>17.112</v>
+        <v>17.3259</v>
       </c>
       <c r="G82">
         <v>3.32</v>
@@ -7999,37 +7999,37 @@
         <v>0.7025</v>
       </c>
       <c r="M82">
-        <v>4.0350096</v>
+        <v>4.085447220000001</v>
       </c>
       <c r="N82">
-        <v>-3.3325096</v>
+        <v>-3.382947220000001</v>
       </c>
       <c r="O82">
-        <v>-0.9997528800000001</v>
+        <v>-1.014884166</v>
       </c>
       <c r="P82">
-        <v>-2.33275672</v>
+        <v>-2.368063054</v>
       </c>
       <c r="Q82">
-        <v>-2.21275672</v>
+        <v>-2.248063054</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4079295066334573</v>
+        <v>0.4269889543510076</v>
       </c>
       <c r="T82">
-        <v>2.524927182416553</v>
+        <v>2.657818086754267</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0522303590058373</v>
+        <v>0.05158553975885165</v>
       </c>
       <c r="W82">
-        <v>0.2234840813464236</v>
+        <v>0.2236361297248628</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1741011966861243</v>
+        <v>0.1719517991961722</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2622731664038303</v>
+        <v>0.2641731664038303</v>
       </c>
       <c r="C83">
-        <v>-7.491681921901945</v>
+        <v>-7.762260196766075</v>
       </c>
       <c r="D83">
-        <v>6.514218078098057</v>
+        <v>6.457539803233929</v>
       </c>
       <c r="E83">
-        <v>15.1359</v>
+        <v>15.3498</v>
       </c>
       <c r="F83">
-        <v>17.3259</v>
+        <v>17.5398</v>
       </c>
       <c r="G83">
         <v>3.32</v>
@@ -8081,37 +8081,37 @@
         <v>0.7025</v>
       </c>
       <c r="M83">
-        <v>4.085447220000001</v>
+        <v>4.135884840000001</v>
       </c>
       <c r="N83">
-        <v>-3.382947220000001</v>
+        <v>-3.433384840000001</v>
       </c>
       <c r="O83">
-        <v>-1.014884166</v>
+        <v>-1.030015452</v>
       </c>
       <c r="P83">
-        <v>-2.368063054</v>
+        <v>-2.403369388000001</v>
       </c>
       <c r="Q83">
-        <v>-2.248063054</v>
+        <v>-2.283369388000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4269889543510076</v>
+        <v>0.4481661184816192</v>
       </c>
       <c r="T83">
-        <v>2.657818086754267</v>
+        <v>2.805474647129504</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05158553975885165</v>
+        <v>0.05095644781057297</v>
       </c>
       <c r="W83">
-        <v>0.2236361297248628</v>
+        <v>0.2237844696062669</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1719517991961722</v>
+        <v>0.1698548260352433</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2641731664038303</v>
+        <v>0.2660731664038303</v>
       </c>
       <c r="C84">
-        <v>-7.762260196766075</v>
+        <v>-8.031860697314791</v>
       </c>
       <c r="D84">
-        <v>6.457539803233929</v>
+        <v>6.401839302685212</v>
       </c>
       <c r="E84">
-        <v>15.3498</v>
+        <v>15.5637</v>
       </c>
       <c r="F84">
-        <v>17.5398</v>
+        <v>17.7537</v>
       </c>
       <c r="G84">
         <v>3.32</v>
@@ -8163,37 +8163,37 @@
         <v>0.7025</v>
       </c>
       <c r="M84">
-        <v>4.135884840000001</v>
+        <v>4.18632246</v>
       </c>
       <c r="N84">
-        <v>-3.433384840000001</v>
+        <v>-3.48382246</v>
       </c>
       <c r="O84">
-        <v>-1.030015452</v>
+        <v>-1.045146738</v>
       </c>
       <c r="P84">
-        <v>-2.403369388000001</v>
+        <v>-2.438675722</v>
       </c>
       <c r="Q84">
-        <v>-2.283369388000001</v>
+        <v>-2.318675722</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4481661184816192</v>
+        <v>0.4718347136864204</v>
       </c>
       <c r="T84">
-        <v>2.805474647129504</v>
+        <v>2.970502567548887</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05095644781057297</v>
+        <v>0.0503425147044215</v>
       </c>
       <c r="W84">
-        <v>0.2237844696062669</v>
+        <v>0.2239292350326974</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1698548260352433</v>
+        <v>0.1678083823480717</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2660731664038303</v>
+        <v>0.2679731664038303</v>
       </c>
       <c r="C85">
-        <v>-8.031860697314791</v>
+        <v>-8.300508508996932</v>
       </c>
       <c r="D85">
-        <v>6.401839302685212</v>
+        <v>6.347091491003068</v>
       </c>
       <c r="E85">
-        <v>15.5637</v>
+        <v>15.7776</v>
       </c>
       <c r="F85">
-        <v>17.7537</v>
+        <v>17.9676</v>
       </c>
       <c r="G85">
         <v>3.32</v>
@@ -8245,37 +8245,37 @@
         <v>0.7025</v>
       </c>
       <c r="M85">
-        <v>4.18632246</v>
+        <v>4.236760080000001</v>
       </c>
       <c r="N85">
-        <v>-3.48382246</v>
+        <v>-3.534260080000001</v>
       </c>
       <c r="O85">
-        <v>-1.045146738</v>
+        <v>-1.060278024</v>
       </c>
       <c r="P85">
-        <v>-2.438675722</v>
+        <v>-2.473982056000001</v>
       </c>
       <c r="Q85">
-        <v>-2.318675722</v>
+        <v>-2.353982056</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4718347136864204</v>
+        <v>0.4984618832918217</v>
       </c>
       <c r="T85">
-        <v>2.970502567548887</v>
+        <v>3.156158978020693</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0503425147044215</v>
+        <v>0.04974319905317839</v>
       </c>
       <c r="W85">
-        <v>0.2239292350326974</v>
+        <v>0.2240705536632606</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1678083823480717</v>
+        <v>0.1658106635105946</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2679731664038303</v>
+        <v>0.2698731664038303</v>
       </c>
       <c r="C86">
-        <v>-8.300508508996932</v>
+        <v>-8.568227866425797</v>
       </c>
       <c r="D86">
-        <v>6.347091491003068</v>
+        <v>6.293272133574202</v>
       </c>
       <c r="E86">
-        <v>15.7776</v>
+        <v>15.9915</v>
       </c>
       <c r="F86">
-        <v>17.9676</v>
+        <v>18.1815</v>
       </c>
       <c r="G86">
         <v>3.32</v>
@@ -8327,37 +8327,37 @@
         <v>0.7025</v>
       </c>
       <c r="M86">
-        <v>4.236760080000001</v>
+        <v>4.2871977</v>
       </c>
       <c r="N86">
-        <v>-3.534260080000001</v>
+        <v>-3.5846977</v>
       </c>
       <c r="O86">
-        <v>-1.060278024</v>
+        <v>-1.07540931</v>
       </c>
       <c r="P86">
-        <v>-2.473982056000001</v>
+        <v>-2.50928839</v>
       </c>
       <c r="Q86">
-        <v>-2.353982056</v>
+        <v>-2.38928839</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4984618832918215</v>
+        <v>0.5286393421779428</v>
       </c>
       <c r="T86">
-        <v>3.156158978020691</v>
+        <v>3.366569576555404</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04974319905317839</v>
+        <v>0.04915798494667041</v>
       </c>
       <c r="W86">
-        <v>0.2240705536632606</v>
+        <v>0.2242085471495751</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1658106635105946</v>
+        <v>0.1638599498222347</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2698731664038303</v>
+        <v>0.2717731664038303</v>
       </c>
       <c r="C87">
-        <v>-8.568227866425797</v>
+        <v>-8.835042189148622</v>
       </c>
       <c r="D87">
-        <v>6.293272133574202</v>
+        <v>6.240357810851378</v>
       </c>
       <c r="E87">
-        <v>15.9915</v>
+        <v>16.2054</v>
       </c>
       <c r="F87">
-        <v>18.1815</v>
+        <v>18.3954</v>
       </c>
       <c r="G87">
         <v>3.32</v>
@@ -8409,37 +8409,37 @@
         <v>0.7025</v>
       </c>
       <c r="M87">
-        <v>4.2871977</v>
+        <v>4.33763532</v>
       </c>
       <c r="N87">
-        <v>-3.5846977</v>
+        <v>-3.635135319999999</v>
       </c>
       <c r="O87">
-        <v>-1.07540931</v>
+        <v>-1.090540596</v>
       </c>
       <c r="P87">
-        <v>-2.50928839</v>
+        <v>-2.544594724</v>
       </c>
       <c r="Q87">
-        <v>-2.38928839</v>
+        <v>-2.424594723999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5286393421779428</v>
+        <v>0.5631278666192244</v>
       </c>
       <c r="T87">
-        <v>3.366569576555404</v>
+        <v>3.607038832023647</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04915798494667041</v>
+        <v>0.04858638047054634</v>
       </c>
       <c r="W87">
-        <v>0.2242085471495751</v>
+        <v>0.2243433314850452</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1638599498222347</v>
+        <v>0.1619546015684878</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2717731664038303</v>
+        <v>0.2736731664038303</v>
       </c>
       <c r="C88">
-        <v>-8.835042189148622</v>
+        <v>-9.100974115626556</v>
       </c>
       <c r="D88">
-        <v>6.240357810851378</v>
+        <v>6.188325884373445</v>
       </c>
       <c r="E88">
-        <v>16.2054</v>
+        <v>16.4193</v>
       </c>
       <c r="F88">
-        <v>18.3954</v>
+        <v>18.6093</v>
       </c>
       <c r="G88">
         <v>3.32</v>
@@ -8491,37 +8491,37 @@
         <v>0.7025</v>
       </c>
       <c r="M88">
-        <v>4.33763532</v>
+        <v>4.388072940000001</v>
       </c>
       <c r="N88">
-        <v>-3.635135319999999</v>
+        <v>-3.685572940000001</v>
       </c>
       <c r="O88">
-        <v>-1.090540596</v>
+        <v>-1.105671882</v>
       </c>
       <c r="P88">
-        <v>-2.544594724</v>
+        <v>-2.579901058</v>
       </c>
       <c r="Q88">
-        <v>-2.424594723999999</v>
+        <v>-2.459901058</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5631278666192244</v>
+        <v>0.6029223178976264</v>
       </c>
       <c r="T88">
-        <v>3.607038832023647</v>
+        <v>3.884503357563927</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04858638047054634</v>
+        <v>0.04802791632720672</v>
       </c>
       <c r="W88">
-        <v>0.2243433314850452</v>
+        <v>0.2244750173300447</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1619546015684878</v>
+        <v>0.1600930544240224</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2736731664038303</v>
+        <v>0.2755731664038303</v>
       </c>
       <c r="C89">
-        <v>-9.100974115626556</v>
+        <v>-9.366045535528759</v>
       </c>
       <c r="D89">
-        <v>6.188325884373445</v>
+        <v>6.137154464471241</v>
       </c>
       <c r="E89">
-        <v>16.4193</v>
+        <v>16.6332</v>
       </c>
       <c r="F89">
-        <v>18.6093</v>
+        <v>18.8232</v>
       </c>
       <c r="G89">
         <v>3.32</v>
@@ -8573,37 +8573,37 @@
         <v>0.7025</v>
       </c>
       <c r="M89">
-        <v>4.388072940000001</v>
+        <v>4.43851056</v>
       </c>
       <c r="N89">
-        <v>-3.685572940000001</v>
+        <v>-3.73601056</v>
       </c>
       <c r="O89">
-        <v>-1.105671882</v>
+        <v>-1.120803168</v>
       </c>
       <c r="P89">
-        <v>-2.579901058</v>
+        <v>-2.615207392</v>
       </c>
       <c r="Q89">
-        <v>-2.459901058</v>
+        <v>-2.495207392</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6029223178976264</v>
+        <v>0.6493491777224286</v>
       </c>
       <c r="T89">
-        <v>3.884503357563927</v>
+        <v>4.208211970694255</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04802791632720672</v>
+        <v>0.04748214455076119</v>
       </c>
       <c r="W89">
-        <v>0.2244750173300447</v>
+        <v>0.2246037103149305</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1600930544240224</v>
+        <v>0.158273815169204</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2755731664038303</v>
+        <v>0.2774731664038303</v>
       </c>
       <c r="C90">
-        <v>-9.366045535528759</v>
+        <v>-9.63027762043742</v>
       </c>
       <c r="D90">
-        <v>6.137154464471241</v>
+        <v>6.086822379562582</v>
       </c>
       <c r="E90">
-        <v>16.6332</v>
+        <v>16.8471</v>
       </c>
       <c r="F90">
-        <v>18.8232</v>
+        <v>19.0371</v>
       </c>
       <c r="G90">
         <v>3.32</v>
@@ -8655,37 +8655,37 @@
         <v>0.7025</v>
       </c>
       <c r="M90">
-        <v>4.43851056</v>
+        <v>4.48894818</v>
       </c>
       <c r="N90">
-        <v>-3.73601056</v>
+        <v>-3.78644818</v>
       </c>
       <c r="O90">
-        <v>-1.120803168</v>
+        <v>-1.135934454</v>
       </c>
       <c r="P90">
-        <v>-2.615207392</v>
+        <v>-2.650513726</v>
       </c>
       <c r="Q90">
-        <v>-2.495207392</v>
+        <v>-2.530513726</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6493491777224286</v>
+        <v>0.7042172847881041</v>
       </c>
       <c r="T90">
-        <v>4.208211970694255</v>
+        <v>4.590776695302824</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04748214455076119</v>
+        <v>0.0469486373086178</v>
       </c>
       <c r="W90">
-        <v>0.2246037103149305</v>
+        <v>0.2247295113226279</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.158273815169204</v>
+        <v>0.1564954576953927</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2774731664038303</v>
+        <v>0.2793731664038303</v>
       </c>
       <c r="C91">
-        <v>-9.63027762043742</v>
+        <v>-9.893690853054107</v>
       </c>
       <c r="D91">
-        <v>6.086822379562582</v>
+        <v>6.037309146945895</v>
       </c>
       <c r="E91">
-        <v>16.8471</v>
+        <v>17.061</v>
       </c>
       <c r="F91">
-        <v>19.0371</v>
+        <v>19.251</v>
       </c>
       <c r="G91">
         <v>3.32</v>
@@ -8737,37 +8737,37 @@
         <v>0.7025</v>
       </c>
       <c r="M91">
-        <v>4.48894818</v>
+        <v>4.539385800000001</v>
       </c>
       <c r="N91">
-        <v>-3.78644818</v>
+        <v>-3.836885800000001</v>
       </c>
       <c r="O91">
-        <v>-1.135934454</v>
+        <v>-1.15106574</v>
       </c>
       <c r="P91">
-        <v>-2.650513726</v>
+        <v>-2.68582006</v>
       </c>
       <c r="Q91">
-        <v>-2.530513726</v>
+        <v>-2.56582006</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7042172847881041</v>
+        <v>0.7700590132669145</v>
       </c>
       <c r="T91">
-        <v>4.590776695302824</v>
+        <v>5.049854364833107</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0469486373086178</v>
+        <v>0.04642698578296649</v>
       </c>
       <c r="W91">
-        <v>0.2247295113226279</v>
+        <v>0.2248525167523765</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1564954576953927</v>
+        <v>0.154756619276555</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2793731664038303</v>
+        <v>0.2812731664038303</v>
       </c>
       <c r="C92">
-        <v>-9.893690853054107</v>
+        <v>-10.15630505499219</v>
       </c>
       <c r="D92">
-        <v>6.037309146945895</v>
+        <v>5.988594945007807</v>
       </c>
       <c r="E92">
-        <v>17.061</v>
+        <v>17.2749</v>
       </c>
       <c r="F92">
-        <v>19.251</v>
+        <v>19.4649</v>
       </c>
       <c r="G92">
         <v>3.32</v>
@@ -8819,37 +8819,37 @@
         <v>0.7025</v>
       </c>
       <c r="M92">
-        <v>4.539385800000001</v>
+        <v>4.58982342</v>
       </c>
       <c r="N92">
-        <v>-3.836885800000001</v>
+        <v>-3.88732342</v>
       </c>
       <c r="O92">
-        <v>-1.15106574</v>
+        <v>-1.166197026</v>
       </c>
       <c r="P92">
-        <v>-2.68582006</v>
+        <v>-2.721126394</v>
       </c>
       <c r="Q92">
-        <v>-2.56582006</v>
+        <v>-2.601126394</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7700590132669145</v>
+        <v>0.8505322369632384</v>
       </c>
       <c r="T92">
-        <v>5.049854364833107</v>
+        <v>5.610949294259008</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04642698578296649</v>
+        <v>0.04591679912601081</v>
       </c>
       <c r="W92">
-        <v>0.2248525167523765</v>
+        <v>0.2249728187660867</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.154756619276555</v>
+        <v>0.1530559970867028</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2812731664038303</v>
+        <v>0.2831731664038303</v>
       </c>
       <c r="C93">
-        <v>-10.15630505499219</v>
+        <v>-10.41813941323452</v>
       </c>
       <c r="D93">
-        <v>5.988594945007807</v>
+        <v>5.940660586765487</v>
       </c>
       <c r="E93">
-        <v>17.2749</v>
+        <v>17.4888</v>
       </c>
       <c r="F93">
-        <v>19.4649</v>
+        <v>19.6788</v>
       </c>
       <c r="G93">
         <v>3.32</v>
@@ -8901,37 +8901,37 @@
         <v>0.7025</v>
       </c>
       <c r="M93">
-        <v>4.58982342</v>
+        <v>4.64026104</v>
       </c>
       <c r="N93">
-        <v>-3.88732342</v>
+        <v>-3.93776104</v>
       </c>
       <c r="O93">
-        <v>-1.166197026</v>
+        <v>-1.181328312</v>
       </c>
       <c r="P93">
-        <v>-2.721126394</v>
+        <v>-2.756432728</v>
       </c>
       <c r="Q93">
-        <v>-2.601126394</v>
+        <v>-2.636432728</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8505322369632384</v>
+        <v>0.9511237665836434</v>
       </c>
       <c r="T93">
-        <v>5.610949294259008</v>
+        <v>6.312317956041386</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04591679912601081</v>
+        <v>0.04541770348333679</v>
       </c>
       <c r="W93">
-        <v>0.2249728187660867</v>
+        <v>0.2250905055186292</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1530559970867028</v>
+        <v>0.151392344944456</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2831731664038303</v>
+        <v>0.2850731664038303</v>
       </c>
       <c r="C94">
-        <v>-10.41813941323452</v>
+        <v>-10.67921250533045</v>
       </c>
       <c r="D94">
-        <v>5.940660586765487</v>
+        <v>5.89348749466955</v>
       </c>
       <c r="E94">
-        <v>17.4888</v>
+        <v>17.7027</v>
       </c>
       <c r="F94">
-        <v>19.6788</v>
+        <v>19.8927</v>
       </c>
       <c r="G94">
         <v>3.32</v>
@@ -8983,37 +8983,37 @@
         <v>0.7025</v>
       </c>
       <c r="M94">
-        <v>4.64026104</v>
+        <v>4.690698660000001</v>
       </c>
       <c r="N94">
-        <v>-3.93776104</v>
+        <v>-3.988198660000001</v>
       </c>
       <c r="O94">
-        <v>-1.181328312</v>
+        <v>-1.196459598</v>
       </c>
       <c r="P94">
-        <v>-2.756432728</v>
+        <v>-2.791739062</v>
       </c>
       <c r="Q94">
-        <v>-2.636432728</v>
+        <v>-2.671739062</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9511237665836434</v>
+        <v>1.08045573323845</v>
       </c>
       <c r="T94">
-        <v>6.312317956041386</v>
+        <v>7.214077664047299</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04541770348333679</v>
+        <v>0.04492934108029015</v>
       </c>
       <c r="W94">
-        <v>0.2250905055186292</v>
+        <v>0.2252056613732676</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.151392344944456</v>
+        <v>0.1497644702676338</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2850731664038303</v>
+        <v>0.2869731664038303</v>
       </c>
       <c r="C95">
-        <v>-10.67921250533045</v>
+        <v>-10.93954232340201</v>
       </c>
       <c r="D95">
-        <v>5.89348749466955</v>
+        <v>5.847057676597989</v>
       </c>
       <c r="E95">
-        <v>17.7027</v>
+        <v>17.9166</v>
       </c>
       <c r="F95">
-        <v>19.8927</v>
+        <v>20.1066</v>
       </c>
       <c r="G95">
         <v>3.32</v>
@@ -9065,37 +9065,37 @@
         <v>0.7025</v>
       </c>
       <c r="M95">
-        <v>4.690698660000001</v>
+        <v>4.74113628</v>
       </c>
       <c r="N95">
-        <v>-3.988198660000001</v>
+        <v>-4.03863628</v>
       </c>
       <c r="O95">
-        <v>-1.196459598</v>
+        <v>-1.211590884</v>
       </c>
       <c r="P95">
-        <v>-2.791739062</v>
+        <v>-2.827045396</v>
       </c>
       <c r="Q95">
-        <v>-2.671739062</v>
+        <v>-2.707045396</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.08045573323845</v>
+        <v>1.252898355444859</v>
       </c>
       <c r="T95">
-        <v>7.214077664047299</v>
+        <v>8.416423941388517</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04492934108029015</v>
+        <v>0.04445136936667005</v>
       </c>
       <c r="W95">
-        <v>0.2252056613732676</v>
+        <v>0.2253183671033392</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1497644702676338</v>
+        <v>0.1481712312222334</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2869731664038303</v>
+        <v>0.2888731664038303</v>
       </c>
       <c r="C96">
-        <v>-10.93954232340201</v>
+        <v>-11.19914629702401</v>
       </c>
       <c r="D96">
-        <v>5.847057676597989</v>
+        <v>5.801353702975992</v>
       </c>
       <c r="E96">
-        <v>17.9166</v>
+        <v>18.1305</v>
       </c>
       <c r="F96">
-        <v>20.1066</v>
+        <v>20.3205</v>
       </c>
       <c r="G96">
         <v>3.32</v>
@@ -9147,37 +9147,37 @@
         <v>0.7025</v>
       </c>
       <c r="M96">
-        <v>4.74113628</v>
+        <v>4.7915739</v>
       </c>
       <c r="N96">
-        <v>-4.03863628</v>
+        <v>-4.089073900000001</v>
       </c>
       <c r="O96">
-        <v>-1.211590884</v>
+        <v>-1.22672217</v>
       </c>
       <c r="P96">
-        <v>-2.827045396</v>
+        <v>-2.86235173</v>
       </c>
       <c r="Q96">
-        <v>-2.707045396</v>
+        <v>-2.74235173</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.252898355444859</v>
+        <v>1.494318026533831</v>
       </c>
       <c r="T96">
-        <v>8.416423941388517</v>
+        <v>10.09970872966622</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04445136936667005</v>
+        <v>0.04398346021544194</v>
       </c>
       <c r="W96">
-        <v>0.2253183671033392</v>
+        <v>0.2254287000811988</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1481712312222334</v>
+        <v>0.1466115340514731</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2888731664038303</v>
+        <v>0.2907731664038303</v>
       </c>
       <c r="C97">
-        <v>-11.19914629702401</v>
+        <v>-11.45804131503951</v>
       </c>
       <c r="D97">
-        <v>5.801353702975992</v>
+        <v>5.756358684960491</v>
       </c>
       <c r="E97">
-        <v>18.1305</v>
+        <v>18.3444</v>
       </c>
       <c r="F97">
-        <v>20.3205</v>
+        <v>20.5344</v>
       </c>
       <c r="G97">
         <v>3.32</v>
@@ -9229,37 +9229,37 @@
         <v>0.7025</v>
       </c>
       <c r="M97">
-        <v>4.7915739</v>
+        <v>4.842011520000001</v>
       </c>
       <c r="N97">
-        <v>-4.089073900000001</v>
+        <v>-4.139511520000001</v>
       </c>
       <c r="O97">
-        <v>-1.22672217</v>
+        <v>-1.241853456</v>
       </c>
       <c r="P97">
-        <v>-2.86235173</v>
+        <v>-2.897658064000001</v>
       </c>
       <c r="Q97">
-        <v>-2.74235173</v>
+        <v>-2.777658064000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.494318026533831</v>
+        <v>1.856447533167289</v>
       </c>
       <c r="T97">
-        <v>10.09970872966622</v>
+        <v>12.62463591208279</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04398346021544194</v>
+        <v>0.04352529917153108</v>
       </c>
       <c r="W97">
-        <v>0.2254287000811988</v>
+        <v>0.225536734455353</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1466115340514731</v>
+        <v>0.1450843305717702</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2907731664038303</v>
+        <v>0.2926731664038303</v>
       </c>
       <c r="C98">
-        <v>-11.45804131503951</v>
+        <v>-11.71624374636789</v>
       </c>
       <c r="D98">
-        <v>5.756358684960492</v>
+        <v>5.712056253632112</v>
       </c>
       <c r="E98">
-        <v>18.3444</v>
+        <v>18.5583</v>
       </c>
       <c r="F98">
-        <v>20.5344</v>
+        <v>20.7483</v>
       </c>
       <c r="G98">
         <v>3.32</v>
@@ -9311,37 +9311,37 @@
         <v>0.7025</v>
       </c>
       <c r="M98">
-        <v>4.842011520000001</v>
+        <v>4.89244914</v>
       </c>
       <c r="N98">
-        <v>-4.139511520000001</v>
+        <v>-4.18994914</v>
       </c>
       <c r="O98">
-        <v>-1.241853456</v>
+        <v>-1.256984742</v>
       </c>
       <c r="P98">
-        <v>-2.897658064000001</v>
+        <v>-2.932964398</v>
       </c>
       <c r="Q98">
-        <v>-2.777658064000001</v>
+        <v>-2.812964398</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.856447533167285</v>
+        <v>2.459996710889713</v>
       </c>
       <c r="T98">
-        <v>12.62463591208275</v>
+        <v>16.83284788277701</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04352529917153108</v>
+        <v>0.04307658474708231</v>
       </c>
       <c r="W98">
-        <v>0.225536734455353</v>
+        <v>0.225642541316638</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1450843305717702</v>
+        <v>0.1435886158236076</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2926731664038303</v>
+        <v>0.2945731664038302</v>
       </c>
       <c r="C99">
-        <v>-11.71624374636789</v>
+        <v>-11.97376945985936</v>
       </c>
       <c r="D99">
-        <v>5.712056253632112</v>
+        <v>5.668430540140638</v>
       </c>
       <c r="E99">
-        <v>18.5583</v>
+        <v>18.7722</v>
       </c>
       <c r="F99">
-        <v>20.7483</v>
+        <v>20.9622</v>
       </c>
       <c r="G99">
         <v>3.32</v>
@@ -9393,37 +9393,37 @@
         <v>0.7025</v>
       </c>
       <c r="M99">
-        <v>4.89244914</v>
+        <v>4.94288676</v>
       </c>
       <c r="N99">
-        <v>-4.18994914</v>
+        <v>-4.240386760000001</v>
       </c>
       <c r="O99">
-        <v>-1.256984742</v>
+        <v>-1.272116028</v>
       </c>
       <c r="P99">
-        <v>-2.932964398</v>
+        <v>-2.968270732000001</v>
       </c>
       <c r="Q99">
-        <v>-2.812964398</v>
+        <v>-2.848270732</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.459996710889713</v>
+        <v>3.667095066334569</v>
       </c>
       <c r="T99">
-        <v>16.83284788277701</v>
+        <v>25.24927182416551</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04307658474708231</v>
+        <v>0.04263702775986718</v>
       </c>
       <c r="W99">
-        <v>0.225642541316638</v>
+        <v>0.2257461888542233</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1435886158236076</v>
+        <v>0.142123425866224</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2945731664038302</v>
+        <v>0.2964731664038303</v>
       </c>
       <c r="C100">
-        <v>-11.97376945985936</v>
+        <v>-12.2306338432466</v>
       </c>
       <c r="D100">
-        <v>5.668430540140638</v>
+        <v>5.625466156753397</v>
       </c>
       <c r="E100">
-        <v>18.7722</v>
+        <v>18.9861</v>
       </c>
       <c r="F100">
-        <v>20.9622</v>
+        <v>21.1761</v>
       </c>
       <c r="G100">
         <v>3.32</v>
@@ -9475,37 +9475,37 @@
         <v>0.7025</v>
       </c>
       <c r="M100">
-        <v>4.94288676</v>
+        <v>4.993324380000001</v>
       </c>
       <c r="N100">
-        <v>-4.240386760000001</v>
+        <v>-4.290824380000001</v>
       </c>
       <c r="O100">
-        <v>-1.272116028</v>
+        <v>-1.287247314</v>
       </c>
       <c r="P100">
-        <v>-2.968270732000001</v>
+        <v>-3.003577066000001</v>
       </c>
       <c r="Q100">
-        <v>-2.848270732</v>
+        <v>-2.883577066000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.667095066334569</v>
+        <v>7.288390132669138</v>
       </c>
       <c r="T100">
-        <v>25.24927182416551</v>
+        <v>50.49854364833102</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04263702775986718</v>
+        <v>0.04220635071178772</v>
       </c>
       <c r="W100">
-        <v>0.2257461888542233</v>
+        <v>0.2258477425021605</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.142123425866224</v>
+        <v>0.140687835705959</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2964731664038303</v>
-      </c>
-      <c r="C101">
-        <v>-12.2306338432466</v>
-      </c>
-      <c r="D101">
-        <v>5.625466156753397</v>
-      </c>
-      <c r="E101">
-        <v>18.9861</v>
-      </c>
-      <c r="F101">
-        <v>21.1761</v>
-      </c>
-      <c r="G101">
-        <v>3.32</v>
-      </c>
-      <c r="H101">
-        <v>19.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.8225</v>
-      </c>
-      <c r="K101">
-        <v>0.12</v>
-      </c>
-      <c r="L101">
-        <v>0.7025</v>
-      </c>
-      <c r="M101">
-        <v>4.993324380000001</v>
-      </c>
-      <c r="N101">
-        <v>-4.290824380000001</v>
-      </c>
-      <c r="O101">
-        <v>-1.287247314</v>
-      </c>
-      <c r="P101">
-        <v>-3.003577066000001</v>
-      </c>
-      <c r="Q101">
-        <v>-2.883577066000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.288390132669138</v>
-      </c>
-      <c r="T101">
-        <v>50.49854364833102</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04220635071178772</v>
-      </c>
-      <c r="W101">
-        <v>0.2258477425021605</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.140687835705959</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
